--- a/DataSets/tit.xlsx
+++ b/DataSets/tit.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,84 +429,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>survived</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>pclass</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>sibsp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>parch</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>fare</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>embarked</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>who</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>adult_male</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>deck</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>embark_town</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>alone</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="1" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -554,7 +566,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
@@ -618,7 +630,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="1" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
@@ -678,7 +690,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="n">
+      <c r="A5" s="1" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
@@ -742,7 +754,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="n">
+      <c r="A6" s="1" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
@@ -802,7 +814,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="n">
+      <c r="A7" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
@@ -860,7 +872,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="n">
+      <c r="A8" s="1" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
@@ -924,7 +936,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="n">
+      <c r="A9" s="1" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
@@ -984,7 +996,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" s="1" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
@@ -1044,7 +1056,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="1" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
@@ -1104,7 +1116,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="n">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
@@ -1168,7 +1180,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
@@ -1232,7 +1244,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="n">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
@@ -1292,7 +1304,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="n">
+      <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
@@ -1352,7 +1364,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="n">
+      <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
@@ -1412,7 +1424,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="n">
+      <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
@@ -1472,7 +1484,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
@@ -1532,7 +1544,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="n">
+      <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
@@ -1590,7 +1602,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="n">
+      <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
@@ -1650,7 +1662,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="n">
+      <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
@@ -1708,7 +1720,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
@@ -1768,7 +1780,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="n">
+      <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
@@ -1832,7 +1844,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
@@ -1892,7 +1904,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="n">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
@@ -1956,7 +1968,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="n">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="n">
+      <c r="A27" s="1" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
@@ -2076,7 +2088,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="n">
+      <c r="A28" s="1" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
@@ -2134,7 +2146,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="n">
+      <c r="A29" s="1" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
@@ -2198,7 +2210,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="n">
+      <c r="A30" s="1" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="n">
@@ -2256,7 +2268,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="n">
+      <c r="A31" s="1" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="n">
@@ -2314,7 +2326,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="n">
+      <c r="A32" s="1" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="n">
@@ -2374,7 +2386,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="n">
+      <c r="A33" s="1" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="n">
@@ -2436,7 +2448,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="n">
+      <c r="A34" s="1" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="n">
@@ -2494,7 +2506,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n">
+      <c r="A35" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="n">
@@ -2554,7 +2566,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="1" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
@@ -2614,7 +2626,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="n">
+      <c r="A37" s="1" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="n">
@@ -2674,7 +2686,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n">
+      <c r="A38" s="1" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="n">
@@ -2732,7 +2744,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="1" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="n">
@@ -2792,7 +2804,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="n">
+      <c r="A40" s="1" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="n">
@@ -2852,7 +2864,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="n">
+      <c r="A41" s="1" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="n">
@@ -2912,7 +2924,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="1" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
@@ -2972,7 +2984,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="n">
+      <c r="A43" s="1" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="n">
@@ -3032,7 +3044,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="n">
+      <c r="A44" s="1" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="n">
@@ -3090,7 +3102,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="1" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="n">
@@ -3150,7 +3162,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="n">
+      <c r="A46" s="1" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="n">
@@ -3210,7 +3222,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="n">
+      <c r="A47" s="1" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="n">
@@ -3268,7 +3280,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="n">
+      <c r="A48" s="1" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="n">
@@ -3326,7 +3338,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="n">
+      <c r="A49" s="1" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
@@ -3384,7 +3396,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="n">
+      <c r="A50" s="1" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
@@ -3442,7 +3454,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="n">
+      <c r="A51" s="1" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="n">
@@ -3502,7 +3514,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="n">
+      <c r="A52" s="1" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="n">
@@ -3562,7 +3574,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="n">
+      <c r="A53" s="1" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="n">
@@ -3622,7 +3634,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="n">
+      <c r="A54" s="1" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="n">
@@ -3686,7 +3698,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="n">
+      <c r="A55" s="1" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="n">
@@ -3746,7 +3758,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="n">
+      <c r="A56" s="1" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
@@ -3810,7 +3822,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="n">
+      <c r="A57" s="1" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="n">
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="n">
+      <c r="A58" s="1" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="n">
@@ -3932,7 +3944,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="n">
+      <c r="A59" s="1" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
@@ -3992,7 +4004,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="n">
+      <c r="A60" s="1" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="n">
@@ -4052,7 +4064,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="n">
+      <c r="A61" s="1" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
@@ -4112,7 +4124,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="n">
+      <c r="A62" s="1" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
@@ -4172,7 +4184,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="n">
+      <c r="A63" s="1" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="n">
@@ -4228,7 +4240,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="n">
+      <c r="A64" s="1" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
@@ -4292,7 +4304,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="n">
+      <c r="A65" s="1" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="n">
@@ -4352,7 +4364,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="n">
+      <c r="A66" s="1" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="n">
@@ -4410,7 +4422,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="n">
+      <c r="A67" s="1" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
@@ -4468,7 +4480,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="n">
+      <c r="A68" s="1" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
@@ -4532,7 +4544,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="n">
+      <c r="A69" s="1" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="n">
@@ -4592,7 +4604,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="n">
+      <c r="A70" s="1" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="n">
@@ -4652,7 +4664,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="n">
+      <c r="A71" s="1" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
@@ -4712,7 +4724,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="n">
+      <c r="A72" s="1" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="n">
@@ -4772,7 +4784,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="n">
+      <c r="A73" s="1" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
@@ -4832,7 +4844,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="n">
+      <c r="A74" s="1" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
@@ -4892,7 +4904,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="n">
+      <c r="A75" s="1" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="n">
@@ -4952,7 +4964,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="n">
+      <c r="A76" s="1" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="n">
@@ -5012,7 +5024,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="n">
+      <c r="A77" s="1" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="n">
@@ -5076,7 +5088,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="n">
+      <c r="A78" s="1" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="n">
@@ -5134,7 +5146,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="n">
+      <c r="A79" s="1" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
@@ -5192,7 +5204,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="n">
+      <c r="A80" s="1" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="n">
@@ -5252,7 +5264,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="n">
+      <c r="A81" s="1" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
@@ -5312,7 +5324,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="n">
+      <c r="A82" s="1" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="n">
@@ -5372,7 +5384,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="n">
+      <c r="A83" s="1" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
@@ -5432,7 +5444,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="n">
+      <c r="A84" s="1" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
@@ -5490,7 +5502,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="n">
+      <c r="A85" s="1" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
@@ -5550,7 +5562,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="n">
+      <c r="A86" s="1" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
@@ -5610,7 +5622,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="n">
+      <c r="A87" s="1" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="n">
@@ -5670,7 +5682,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="n">
+      <c r="A88" s="1" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="n">
@@ -5730,7 +5742,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="n">
+      <c r="A89" s="1" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
@@ -5788,7 +5800,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="n">
+      <c r="A90" s="1" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="n">
@@ -5852,7 +5864,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="n">
+      <c r="A91" s="1" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
@@ -5912,7 +5924,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="n">
+      <c r="A92" s="1" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="n">
@@ -5972,7 +5984,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="n">
+      <c r="A93" s="1" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="n">
@@ -6032,7 +6044,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="n">
+      <c r="A94" s="1" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="n">
@@ -6096,7 +6108,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="n">
+      <c r="A95" s="1" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
@@ -6156,7 +6168,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="n">
+      <c r="A96" s="1" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
@@ -6216,7 +6228,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="n">
+      <c r="A97" s="1" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
@@ -6274,7 +6286,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="n">
+      <c r="A98" s="1" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
@@ -6338,7 +6350,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="n">
+      <c r="A99" s="1" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
@@ -6402,7 +6414,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="n">
+      <c r="A100" s="1" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="n">
@@ -6462,7 +6474,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="n">
+      <c r="A101" s="1" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
@@ -6522,7 +6534,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="n">
+      <c r="A102" s="1" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="n">
@@ -6582,7 +6594,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="n">
+      <c r="A103" s="1" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="n">
@@ -6640,7 +6652,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="n">
+      <c r="A104" s="1" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="n">
@@ -6704,7 +6716,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="n">
+      <c r="A105" s="1" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="n">
@@ -6764,7 +6776,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="n">
+      <c r="A106" s="1" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="n">
@@ -6824,7 +6836,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="n">
+      <c r="A107" s="1" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="n">
@@ -6884,7 +6896,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="n">
+      <c r="A108" s="1" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="n">
@@ -6944,7 +6956,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="n">
+      <c r="A109" s="1" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="n">
@@ -7002,7 +7014,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="n">
+      <c r="A110" s="1" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="n">
+      <c r="A111" s="1" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="n">
+      <c r="A112" s="1" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="n">
@@ -7184,7 +7196,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
+      <c r="A113" s="1" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
@@ -7244,7 +7256,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="n">
+      <c r="A114" s="1" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="n">
@@ -7304,7 +7316,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="n">
+      <c r="A115" s="1" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
@@ -7364,7 +7376,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="n">
+      <c r="A116" s="1" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="n">
@@ -7424,7 +7436,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="1" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
@@ -7484,7 +7496,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="n">
+      <c r="A118" s="1" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
@@ -7544,7 +7556,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="n">
+      <c r="A119" s="1" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
@@ -7604,7 +7616,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="n">
+      <c r="A120" s="1" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
@@ -7668,7 +7680,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="n">
+      <c r="A121" s="1" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="n">
@@ -7728,7 +7740,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
+      <c r="A122" s="1" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
@@ -7788,7 +7800,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="n">
+      <c r="A123" s="1" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
@@ -7846,7 +7858,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="n">
+      <c r="A124" s="1" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="n">
@@ -7906,7 +7918,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="n">
+      <c r="A125" s="1" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
@@ -7970,7 +7982,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="n">
+      <c r="A126" s="1" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
@@ -8034,7 +8046,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="n">
+      <c r="A127" s="1" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="n">
@@ -8094,7 +8106,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="n">
+      <c r="A128" s="1" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="n">
@@ -8152,7 +8164,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="n">
+      <c r="A129" s="1" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="n">
@@ -8212,7 +8224,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="n">
+      <c r="A130" s="1" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="n">
@@ -8274,7 +8286,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="n">
+      <c r="A131" s="1" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="n">
@@ -8334,7 +8346,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="n">
+      <c r="A132" s="1" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="n">
@@ -8394,7 +8406,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="n">
+      <c r="A133" s="1" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
@@ -8454,7 +8466,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="n">
+      <c r="A134" s="1" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
@@ -8514,7 +8526,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="n">
+      <c r="A135" s="1" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
@@ -8574,7 +8586,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="n">
+      <c r="A136" s="1" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
@@ -8634,7 +8646,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="n">
+      <c r="A137" s="1" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
@@ -8694,7 +8706,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="n">
+      <c r="A138" s="1" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="n">
@@ -8758,7 +8770,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="n">
+      <c r="A139" s="1" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
@@ -8822,7 +8834,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="n">
+      <c r="A140" s="1" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="n">
@@ -8882,7 +8894,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="n">
+      <c r="A141" s="1" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
@@ -8946,7 +8958,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="n">
+      <c r="A142" s="1" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="n">
@@ -9004,7 +9016,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="n">
+      <c r="A143" s="1" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
@@ -9064,7 +9076,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="n">
+      <c r="A144" s="1" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="n">
@@ -9124,7 +9136,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="n">
+      <c r="A145" s="1" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
@@ -9184,7 +9196,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="n">
+      <c r="A146" s="1" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="n">
@@ -9244,7 +9256,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="n">
+      <c r="A147" s="1" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="n">
@@ -9304,7 +9316,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="n">
+      <c r="A148" s="1" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="n">
@@ -9364,7 +9376,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="n">
+      <c r="A149" s="1" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="n">
@@ -9424,7 +9436,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="n">
+      <c r="A150" s="1" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="n">
@@ -9488,7 +9500,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="n">
+      <c r="A151" s="1" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="n">
@@ -9548,7 +9560,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="n">
+      <c r="A152" s="1" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="n">
@@ -9608,7 +9620,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="n">
+      <c r="A153" s="1" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="n">
@@ -9672,7 +9684,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="n">
+      <c r="A154" s="1" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="n">
@@ -9732,7 +9744,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="n">
+      <c r="A155" s="1" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="n">
@@ -9792,7 +9804,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="n">
+      <c r="A156" s="1" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="n">
@@ -9850,7 +9862,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="n">
+      <c r="A157" s="1" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="n">
@@ -9910,7 +9922,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="n">
+      <c r="A158" s="1" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="n">
@@ -9970,7 +9982,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="n">
+      <c r="A159" s="1" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="n">
@@ -10030,7 +10042,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="n">
+      <c r="A160" s="1" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="n">
@@ -10088,7 +10100,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="n">
+      <c r="A161" s="1" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="n">
@@ -10146,7 +10158,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="n">
+      <c r="A162" s="1" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="n">
@@ -10206,7 +10218,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="n">
+      <c r="A163" s="1" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="n">
@@ -10266,7 +10278,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="n">
+      <c r="A164" s="1" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="n">
@@ -10326,7 +10338,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="n">
+      <c r="A165" s="1" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="n">
@@ -10386,7 +10398,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="n">
+      <c r="A166" s="1" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="n">
@@ -10446,7 +10458,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="n">
+      <c r="A167" s="1" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="n">
@@ -10506,7 +10518,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="n">
+      <c r="A168" s="1" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="n">
@@ -10568,7 +10580,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="n">
+      <c r="A169" s="1" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="n">
@@ -10628,7 +10640,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="n">
+      <c r="A170" s="1" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="n">
@@ -10686,7 +10698,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="n">
+      <c r="A171" s="1" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="n">
@@ -10746,7 +10758,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="n">
+      <c r="A172" s="1" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="n">
@@ -10810,7 +10822,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="n">
+      <c r="A173" s="1" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="n">
@@ -10870,7 +10882,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="n">
+      <c r="A174" s="1" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="n">
@@ -10930,7 +10942,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="n">
+      <c r="A175" s="1" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="n">
@@ -10990,7 +11002,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="n">
+      <c r="A176" s="1" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="n">
@@ -11054,7 +11066,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="n">
+      <c r="A177" s="1" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="n">
@@ -11114,7 +11126,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="n">
+      <c r="A178" s="1" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="n">
@@ -11172,7 +11184,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="n">
+      <c r="A179" s="1" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="n">
@@ -11236,7 +11248,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="n">
+      <c r="A180" s="1" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="n">
@@ -11296,7 +11308,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="n">
+      <c r="A181" s="1" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="n">
@@ -11356,7 +11368,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="n">
+      <c r="A182" s="1" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="n">
@@ -11414,7 +11426,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="n">
+      <c r="A183" s="1" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="n">
@@ -11472,7 +11484,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="n">
+      <c r="A184" s="1" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="n">
@@ -11532,7 +11544,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="n">
+      <c r="A185" s="1" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="n">
@@ -11596,7 +11608,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="n">
+      <c r="A186" s="1" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="n">
@@ -11656,7 +11668,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="n">
+      <c r="A187" s="1" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="n">
@@ -11718,7 +11730,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="n">
+      <c r="A188" s="1" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="n">
@@ -11776,7 +11788,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="n">
+      <c r="A189" s="1" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="n">
@@ -11836,7 +11848,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="n">
+      <c r="A190" s="1" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="n">
@@ -11896,7 +11908,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="n">
+      <c r="A191" s="1" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="n">
@@ -11956,7 +11968,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="n">
+      <c r="A192" s="1" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="n">
@@ -12016,7 +12028,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="n">
+      <c r="A193" s="1" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="n">
@@ -12076,7 +12088,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="n">
+      <c r="A194" s="1" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="n">
@@ -12136,7 +12148,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="n">
+      <c r="A195" s="1" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="n">
@@ -12200,7 +12212,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="n">
+      <c r="A196" s="1" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="n">
@@ -12264,7 +12276,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="n">
+      <c r="A197" s="1" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="n">
@@ -12328,7 +12340,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="n">
+      <c r="A198" s="1" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="n">
@@ -12386,7 +12398,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="n">
+      <c r="A199" s="1" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="n">
@@ -12446,7 +12458,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="n">
+      <c r="A200" s="1" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="n">
@@ -12504,7 +12516,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="n">
+      <c r="A201" s="1" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="n">
@@ -12564,7 +12576,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="n">
+      <c r="A202" s="1" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="n">
@@ -12624,7 +12636,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="n">
+      <c r="A203" s="1" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="n">
@@ -12682,7 +12694,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="n">
+      <c r="A204" s="1" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="n">
@@ -12742,7 +12754,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="n">
+      <c r="A205" s="1" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="n">
@@ -12802,7 +12814,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="n">
+      <c r="A206" s="1" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="n">
@@ -12862,7 +12874,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="n">
+      <c r="A207" s="1" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="n">
@@ -12926,7 +12938,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="n">
+      <c r="A208" s="1" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="n">
@@ -12986,7 +12998,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="n">
+      <c r="A209" s="1" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="n">
@@ -13046,7 +13058,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="n">
+      <c r="A210" s="1" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="n">
@@ -13106,7 +13118,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="n">
+      <c r="A211" s="1" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="n">
@@ -13170,7 +13182,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="n">
+      <c r="A212" s="1" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="n">
@@ -13230,7 +13242,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="n">
+      <c r="A213" s="1" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="n">
@@ -13290,7 +13302,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="n">
+      <c r="A214" s="1" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="n">
@@ -13350,7 +13362,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="n">
+      <c r="A215" s="1" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="n">
@@ -13410,7 +13422,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="n">
+      <c r="A216" s="1" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="n">
@@ -13468,7 +13480,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="n">
+      <c r="A217" s="1" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="n">
@@ -13532,7 +13544,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="n">
+      <c r="A218" s="1" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="n">
@@ -13592,7 +13604,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="n">
+      <c r="A219" s="1" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="n">
@@ -13652,7 +13664,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="n">
+      <c r="A220" s="1" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="n">
@@ -13716,7 +13728,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="n">
+      <c r="A221" s="1" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="n">
@@ -13776,7 +13788,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="n">
+      <c r="A222" s="1" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="n">
@@ -13836,7 +13848,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="n">
+      <c r="A223" s="1" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="n">
@@ -13896,7 +13908,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="n">
+      <c r="A224" s="1" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="n">
@@ -13956,7 +13968,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="n">
+      <c r="A225" s="1" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="n">
@@ -14014,7 +14026,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="n">
+      <c r="A226" s="1" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="n">
@@ -14078,7 +14090,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="n">
+      <c r="A227" s="1" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="n">
@@ -14138,7 +14150,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="n">
+      <c r="A228" s="1" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="n">
@@ -14198,7 +14210,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="n">
+      <c r="A229" s="1" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="n">
@@ -14258,7 +14270,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="n">
+      <c r="A230" s="1" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="n">
@@ -14318,7 +14330,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="n">
+      <c r="A231" s="1" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="n">
@@ -14376,7 +14388,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="n">
+      <c r="A232" s="1" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="n">
@@ -14440,7 +14452,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="n">
+      <c r="A233" s="1" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="n">
@@ -14500,7 +14512,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="n">
+      <c r="A234" s="1" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="n">
@@ -14560,7 +14572,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="n">
+      <c r="A235" s="1" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="n">
@@ -14620,7 +14632,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="n">
+      <c r="A236" s="1" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="n">
@@ -14680,7 +14692,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="n">
+      <c r="A237" s="1" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="n">
@@ -14738,7 +14750,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" t="n">
+      <c r="A238" s="1" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="n">
@@ -14798,7 +14810,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="n">
+      <c r="A239" s="1" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="n">
@@ -14858,7 +14870,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="n">
+      <c r="A240" s="1" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="n">
@@ -14918,7 +14930,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="n">
+      <c r="A241" s="1" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="n">
@@ -14978,7 +14990,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="n">
+      <c r="A242" s="1" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="n">
@@ -15036,7 +15048,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="n">
+      <c r="A243" s="1" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="n">
@@ -15094,7 +15106,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="n">
+      <c r="A244" s="1" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="n">
@@ -15154,7 +15166,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="n">
+      <c r="A245" s="1" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="n">
@@ -15214,7 +15226,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="n">
+      <c r="A246" s="1" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="n">
@@ -15274,7 +15286,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="n">
+      <c r="A247" s="1" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="n">
@@ -15338,7 +15350,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="n">
+      <c r="A248" s="1" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="n">
@@ -15398,7 +15410,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" t="n">
+      <c r="A249" s="1" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="n">
@@ -15458,7 +15470,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="n">
+      <c r="A250" s="1" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="n">
@@ -15522,7 +15534,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="n">
+      <c r="A251" s="1" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="n">
@@ -15582,7 +15594,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="n">
+      <c r="A252" s="1" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="n">
@@ -15640,7 +15652,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="n">
+      <c r="A253" s="1" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="n">
@@ -15704,7 +15716,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="n">
+      <c r="A254" s="1" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="n">
@@ -15768,7 +15780,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="n">
+      <c r="A255" s="1" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="n">
@@ -15828,7 +15840,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="n">
+      <c r="A256" s="1" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="n">
@@ -15888,7 +15900,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="n">
+      <c r="A257" s="1" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="n">
@@ -15948,7 +15960,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="n">
+      <c r="A258" s="1" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="n">
@@ -16006,7 +16018,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="n">
+      <c r="A259" s="1" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="n">
@@ -16070,7 +16082,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="n">
+      <c r="A260" s="1" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="n">
@@ -16130,7 +16142,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="n">
+      <c r="A261" s="1" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="n">
@@ -16190,7 +16202,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="n">
+      <c r="A262" s="1" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="n">
@@ -16248,7 +16260,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="n">
+      <c r="A263" s="1" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="n">
@@ -16308,7 +16320,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="n">
+      <c r="A264" s="1" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="n">
@@ -16372,7 +16384,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="n">
+      <c r="A265" s="1" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="n">
@@ -16436,7 +16448,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="n">
+      <c r="A266" s="1" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="n">
@@ -16494,7 +16506,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="n">
+      <c r="A267" s="1" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="n">
@@ -16554,7 +16566,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="n">
+      <c r="A268" s="1" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="n">
@@ -16614,7 +16626,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="n">
+      <c r="A269" s="1" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="n">
@@ -16674,7 +16686,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="n">
+      <c r="A270" s="1" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="n">
@@ -16738,7 +16750,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" t="n">
+      <c r="A271" s="1" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="n">
@@ -16802,7 +16814,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" t="n">
+      <c r="A272" s="1" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="n">
@@ -16860,7 +16872,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" t="n">
+      <c r="A273" s="1" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="n">
@@ -16920,7 +16932,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" t="n">
+      <c r="A274" s="1" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="n">
@@ -16980,7 +16992,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" t="n">
+      <c r="A275" s="1" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="n">
@@ -17044,7 +17056,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" t="n">
+      <c r="A276" s="1" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="n">
@@ -17102,7 +17114,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" t="n">
+      <c r="A277" s="1" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="n">
@@ -17166,7 +17178,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" t="n">
+      <c r="A278" s="1" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="n">
@@ -17226,7 +17238,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" t="n">
+      <c r="A279" s="1" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="n">
@@ -17284,7 +17296,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" t="n">
+      <c r="A280" s="1" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="n">
@@ -17344,7 +17356,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" t="n">
+      <c r="A281" s="1" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="n">
@@ -17404,7 +17416,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" t="n">
+      <c r="A282" s="1" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="n">
@@ -17464,7 +17476,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" t="n">
+      <c r="A283" s="1" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="n">
@@ -17524,7 +17536,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" t="n">
+      <c r="A284" s="1" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="n">
@@ -17584,7 +17596,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" t="n">
+      <c r="A285" s="1" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="n">
@@ -17644,7 +17656,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" t="n">
+      <c r="A286" s="1" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="n">
@@ -17706,7 +17718,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" t="n">
+      <c r="A287" s="1" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="n">
@@ -17766,7 +17778,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" t="n">
+      <c r="A288" s="1" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="n">
@@ -17826,7 +17838,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" t="n">
+      <c r="A289" s="1" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="n">
@@ -17886,7 +17898,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" t="n">
+      <c r="A290" s="1" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="n">
@@ -17946,7 +17958,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" t="n">
+      <c r="A291" s="1" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="n">
@@ -18006,7 +18018,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" t="n">
+      <c r="A292" s="1" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="n">
@@ -18066,7 +18078,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" t="n">
+      <c r="A293" s="1" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="n">
@@ -18130,7 +18142,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" t="n">
+      <c r="A294" s="1" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="n">
@@ -18194,7 +18206,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" t="n">
+      <c r="A295" s="1" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="n">
@@ -18254,7 +18266,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" t="n">
+      <c r="A296" s="1" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="n">
@@ -18314,7 +18326,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" t="n">
+      <c r="A297" s="1" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="n">
@@ -18372,7 +18384,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" t="n">
+      <c r="A298" s="1" t="n">
         <v>296</v>
       </c>
       <c r="B298" t="n">
@@ -18432,7 +18444,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" t="n">
+      <c r="A299" s="1" t="n">
         <v>297</v>
       </c>
       <c r="B299" t="n">
@@ -18496,7 +18508,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" t="n">
+      <c r="A300" s="1" t="n">
         <v>298</v>
       </c>
       <c r="B300" t="n">
@@ -18558,7 +18570,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" t="n">
+      <c r="A301" s="1" t="n">
         <v>299</v>
       </c>
       <c r="B301" t="n">
@@ -18622,7 +18634,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="n">
+      <c r="A302" s="1" t="n">
         <v>300</v>
       </c>
       <c r="B302" t="n">
@@ -18680,7 +18692,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="n">
+      <c r="A303" s="1" t="n">
         <v>301</v>
       </c>
       <c r="B303" t="n">
@@ -18738,7 +18750,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" t="n">
+      <c r="A304" s="1" t="n">
         <v>302</v>
       </c>
       <c r="B304" t="n">
@@ -18798,7 +18810,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" t="n">
+      <c r="A305" s="1" t="n">
         <v>303</v>
       </c>
       <c r="B305" t="n">
@@ -18860,7 +18872,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" t="n">
+      <c r="A306" s="1" t="n">
         <v>304</v>
       </c>
       <c r="B306" t="n">
@@ -18918,7 +18930,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" t="n">
+      <c r="A307" s="1" t="n">
         <v>305</v>
       </c>
       <c r="B307" t="n">
@@ -18982,7 +18994,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" t="n">
+      <c r="A308" s="1" t="n">
         <v>306</v>
       </c>
       <c r="B308" t="n">
@@ -19040,7 +19052,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" t="n">
+      <c r="A309" s="1" t="n">
         <v>307</v>
       </c>
       <c r="B309" t="n">
@@ -19104,7 +19116,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" t="n">
+      <c r="A310" s="1" t="n">
         <v>308</v>
       </c>
       <c r="B310" t="n">
@@ -19164,7 +19176,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" t="n">
+      <c r="A311" s="1" t="n">
         <v>309</v>
       </c>
       <c r="B311" t="n">
@@ -19228,7 +19240,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" t="n">
+      <c r="A312" s="1" t="n">
         <v>310</v>
       </c>
       <c r="B312" t="n">
@@ -19292,7 +19304,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" t="n">
+      <c r="A313" s="1" t="n">
         <v>311</v>
       </c>
       <c r="B313" t="n">
@@ -19356,7 +19368,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" t="n">
+      <c r="A314" s="1" t="n">
         <v>312</v>
       </c>
       <c r="B314" t="n">
@@ -19416,7 +19428,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" t="n">
+      <c r="A315" s="1" t="n">
         <v>313</v>
       </c>
       <c r="B315" t="n">
@@ -19476,7 +19488,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" t="n">
+      <c r="A316" s="1" t="n">
         <v>314</v>
       </c>
       <c r="B316" t="n">
@@ -19536,7 +19548,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" t="n">
+      <c r="A317" s="1" t="n">
         <v>315</v>
       </c>
       <c r="B317" t="n">
@@ -19596,7 +19608,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" t="n">
+      <c r="A318" s="1" t="n">
         <v>316</v>
       </c>
       <c r="B318" t="n">
@@ -19656,7 +19668,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" t="n">
+      <c r="A319" s="1" t="n">
         <v>317</v>
       </c>
       <c r="B319" t="n">
@@ -19716,7 +19728,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" t="n">
+      <c r="A320" s="1" t="n">
         <v>318</v>
       </c>
       <c r="B320" t="n">
@@ -19780,7 +19792,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" t="n">
+      <c r="A321" s="1" t="n">
         <v>319</v>
       </c>
       <c r="B321" t="n">
@@ -19844,7 +19856,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" t="n">
+      <c r="A322" s="1" t="n">
         <v>320</v>
       </c>
       <c r="B322" t="n">
@@ -19904,7 +19916,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" t="n">
+      <c r="A323" s="1" t="n">
         <v>321</v>
       </c>
       <c r="B323" t="n">
@@ -19964,7 +19976,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" t="n">
+      <c r="A324" s="1" t="n">
         <v>322</v>
       </c>
       <c r="B324" t="n">
@@ -20024,7 +20036,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" t="n">
+      <c r="A325" s="1" t="n">
         <v>323</v>
       </c>
       <c r="B325" t="n">
@@ -20084,7 +20096,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" t="n">
+      <c r="A326" s="1" t="n">
         <v>324</v>
       </c>
       <c r="B326" t="n">
@@ -20142,7 +20154,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" t="n">
+      <c r="A327" s="1" t="n">
         <v>325</v>
       </c>
       <c r="B327" t="n">
@@ -20206,7 +20218,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" t="n">
+      <c r="A328" s="1" t="n">
         <v>326</v>
       </c>
       <c r="B328" t="n">
@@ -20266,7 +20278,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" t="n">
+      <c r="A329" s="1" t="n">
         <v>327</v>
       </c>
       <c r="B329" t="n">
@@ -20330,7 +20342,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" t="n">
+      <c r="A330" s="1" t="n">
         <v>328</v>
       </c>
       <c r="B330" t="n">
@@ -20390,7 +20402,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" t="n">
+      <c r="A331" s="1" t="n">
         <v>329</v>
       </c>
       <c r="B331" t="n">
@@ -20454,7 +20466,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" t="n">
+      <c r="A332" s="1" t="n">
         <v>330</v>
       </c>
       <c r="B332" t="n">
@@ -20512,7 +20524,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" t="n">
+      <c r="A333" s="1" t="n">
         <v>331</v>
       </c>
       <c r="B333" t="n">
@@ -20576,7 +20588,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" t="n">
+      <c r="A334" s="1" t="n">
         <v>332</v>
       </c>
       <c r="B334" t="n">
@@ -20640,7 +20652,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" t="n">
+      <c r="A335" s="1" t="n">
         <v>333</v>
       </c>
       <c r="B335" t="n">
@@ -20700,7 +20712,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" t="n">
+      <c r="A336" s="1" t="n">
         <v>334</v>
       </c>
       <c r="B336" t="n">
@@ -20758,7 +20770,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="n">
+      <c r="A337" s="1" t="n">
         <v>335</v>
       </c>
       <c r="B337" t="n">
@@ -20816,7 +20828,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="n">
+      <c r="A338" s="1" t="n">
         <v>336</v>
       </c>
       <c r="B338" t="n">
@@ -20880,7 +20892,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="n">
+      <c r="A339" s="1" t="n">
         <v>337</v>
       </c>
       <c r="B339" t="n">
@@ -20944,7 +20956,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" t="n">
+      <c r="A340" s="1" t="n">
         <v>338</v>
       </c>
       <c r="B340" t="n">
@@ -21004,7 +21016,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" t="n">
+      <c r="A341" s="1" t="n">
         <v>339</v>
       </c>
       <c r="B341" t="n">
@@ -21064,7 +21076,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" t="n">
+      <c r="A342" s="1" t="n">
         <v>340</v>
       </c>
       <c r="B342" t="n">
@@ -21128,7 +21140,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" t="n">
+      <c r="A343" s="1" t="n">
         <v>341</v>
       </c>
       <c r="B343" t="n">
@@ -21192,7 +21204,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="n">
+      <c r="A344" s="1" t="n">
         <v>342</v>
       </c>
       <c r="B344" t="n">
@@ -21252,7 +21264,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" t="n">
+      <c r="A345" s="1" t="n">
         <v>343</v>
       </c>
       <c r="B345" t="n">
@@ -21312,7 +21324,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="n">
+      <c r="A346" s="1" t="n">
         <v>344</v>
       </c>
       <c r="B346" t="n">
@@ -21372,7 +21384,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" t="n">
+      <c r="A347" s="1" t="n">
         <v>345</v>
       </c>
       <c r="B347" t="n">
@@ -21436,7 +21448,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" t="n">
+      <c r="A348" s="1" t="n">
         <v>346</v>
       </c>
       <c r="B348" t="n">
@@ -21496,7 +21508,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="n">
+      <c r="A349" s="1" t="n">
         <v>347</v>
       </c>
       <c r="B349" t="n">
@@ -21554,7 +21566,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="n">
+      <c r="A350" s="1" t="n">
         <v>348</v>
       </c>
       <c r="B350" t="n">
@@ -21614,7 +21626,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="n">
+      <c r="A351" s="1" t="n">
         <v>349</v>
       </c>
       <c r="B351" t="n">
@@ -21674,7 +21686,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" t="n">
+      <c r="A352" s="1" t="n">
         <v>350</v>
       </c>
       <c r="B352" t="n">
@@ -21734,7 +21746,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="n">
+      <c r="A353" s="1" t="n">
         <v>351</v>
       </c>
       <c r="B353" t="n">
@@ -21796,7 +21808,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" t="n">
+      <c r="A354" s="1" t="n">
         <v>352</v>
       </c>
       <c r="B354" t="n">
@@ -21856,7 +21868,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" t="n">
+      <c r="A355" s="1" t="n">
         <v>353</v>
       </c>
       <c r="B355" t="n">
@@ -21916,7 +21928,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" t="n">
+      <c r="A356" s="1" t="n">
         <v>354</v>
       </c>
       <c r="B356" t="n">
@@ -21974,7 +21986,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" t="n">
+      <c r="A357" s="1" t="n">
         <v>355</v>
       </c>
       <c r="B357" t="n">
@@ -22034,7 +22046,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" t="n">
+      <c r="A358" s="1" t="n">
         <v>356</v>
       </c>
       <c r="B358" t="n">
@@ -22098,7 +22110,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" t="n">
+      <c r="A359" s="1" t="n">
         <v>357</v>
       </c>
       <c r="B359" t="n">
@@ -22158,7 +22170,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" t="n">
+      <c r="A360" s="1" t="n">
         <v>358</v>
       </c>
       <c r="B360" t="n">
@@ -22216,7 +22228,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="n">
+      <c r="A361" s="1" t="n">
         <v>359</v>
       </c>
       <c r="B361" t="n">
@@ -22274,7 +22286,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" t="n">
+      <c r="A362" s="1" t="n">
         <v>360</v>
       </c>
       <c r="B362" t="n">
@@ -22334,7 +22346,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="n">
+      <c r="A363" s="1" t="n">
         <v>361</v>
       </c>
       <c r="B363" t="n">
@@ -22394,7 +22406,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="n">
+      <c r="A364" s="1" t="n">
         <v>362</v>
       </c>
       <c r="B364" t="n">
@@ -22454,7 +22466,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" t="n">
+      <c r="A365" s="1" t="n">
         <v>363</v>
       </c>
       <c r="B365" t="n">
@@ -22514,7 +22526,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" t="n">
+      <c r="A366" s="1" t="n">
         <v>364</v>
       </c>
       <c r="B366" t="n">
@@ -22572,7 +22584,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" t="n">
+      <c r="A367" s="1" t="n">
         <v>365</v>
       </c>
       <c r="B367" t="n">
@@ -22632,7 +22644,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" t="n">
+      <c r="A368" s="1" t="n">
         <v>366</v>
       </c>
       <c r="B368" t="n">
@@ -22696,7 +22708,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="n">
+      <c r="A369" s="1" t="n">
         <v>367</v>
       </c>
       <c r="B369" t="n">
@@ -22754,7 +22766,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" t="n">
+      <c r="A370" s="1" t="n">
         <v>368</v>
       </c>
       <c r="B370" t="n">
@@ -22812,7 +22824,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" t="n">
+      <c r="A371" s="1" t="n">
         <v>369</v>
       </c>
       <c r="B371" t="n">
@@ -22876,7 +22888,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" t="n">
+      <c r="A372" s="1" t="n">
         <v>370</v>
       </c>
       <c r="B372" t="n">
@@ -22940,7 +22952,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" t="n">
+      <c r="A373" s="1" t="n">
         <v>371</v>
       </c>
       <c r="B373" t="n">
@@ -23000,7 +23012,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" t="n">
+      <c r="A374" s="1" t="n">
         <v>372</v>
       </c>
       <c r="B374" t="n">
@@ -23060,7 +23072,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" t="n">
+      <c r="A375" s="1" t="n">
         <v>373</v>
       </c>
       <c r="B375" t="n">
@@ -23120,7 +23132,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="n">
+      <c r="A376" s="1" t="n">
         <v>374</v>
       </c>
       <c r="B376" t="n">
@@ -23180,7 +23192,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="n">
+      <c r="A377" s="1" t="n">
         <v>375</v>
       </c>
       <c r="B377" t="n">
@@ -23238,7 +23250,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" t="n">
+      <c r="A378" s="1" t="n">
         <v>376</v>
       </c>
       <c r="B378" t="n">
@@ -23298,7 +23310,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" t="n">
+      <c r="A379" s="1" t="n">
         <v>377</v>
       </c>
       <c r="B379" t="n">
@@ -23362,7 +23374,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" t="n">
+      <c r="A380" s="1" t="n">
         <v>378</v>
       </c>
       <c r="B380" t="n">
@@ -23422,7 +23434,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" t="n">
+      <c r="A381" s="1" t="n">
         <v>379</v>
       </c>
       <c r="B381" t="n">
@@ -23482,7 +23494,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" t="n">
+      <c r="A382" s="1" t="n">
         <v>380</v>
       </c>
       <c r="B382" t="n">
@@ -23542,7 +23554,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" t="n">
+      <c r="A383" s="1" t="n">
         <v>381</v>
       </c>
       <c r="B383" t="n">
@@ -23602,7 +23614,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" t="n">
+      <c r="A384" s="1" t="n">
         <v>382</v>
       </c>
       <c r="B384" t="n">
@@ -23662,7 +23674,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" t="n">
+      <c r="A385" s="1" t="n">
         <v>383</v>
       </c>
       <c r="B385" t="n">
@@ -23722,7 +23734,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" t="n">
+      <c r="A386" s="1" t="n">
         <v>384</v>
       </c>
       <c r="B386" t="n">
@@ -23780,7 +23792,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" t="n">
+      <c r="A387" s="1" t="n">
         <v>385</v>
       </c>
       <c r="B387" t="n">
@@ -23840,7 +23852,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" t="n">
+      <c r="A388" s="1" t="n">
         <v>386</v>
       </c>
       <c r="B388" t="n">
@@ -23900,7 +23912,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="n">
+      <c r="A389" s="1" t="n">
         <v>387</v>
       </c>
       <c r="B389" t="n">
@@ -23960,7 +23972,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="n">
+      <c r="A390" s="1" t="n">
         <v>388</v>
       </c>
       <c r="B390" t="n">
@@ -24018,7 +24030,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" t="n">
+      <c r="A391" s="1" t="n">
         <v>389</v>
       </c>
       <c r="B391" t="n">
@@ -24078,7 +24090,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" t="n">
+      <c r="A392" s="1" t="n">
         <v>390</v>
       </c>
       <c r="B392" t="n">
@@ -24142,7 +24154,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" t="n">
+      <c r="A393" s="1" t="n">
         <v>391</v>
       </c>
       <c r="B393" t="n">
@@ -24202,7 +24214,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" t="n">
+      <c r="A394" s="1" t="n">
         <v>392</v>
       </c>
       <c r="B394" t="n">
@@ -24262,7 +24274,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" t="n">
+      <c r="A395" s="1" t="n">
         <v>393</v>
       </c>
       <c r="B395" t="n">
@@ -24326,7 +24338,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" t="n">
+      <c r="A396" s="1" t="n">
         <v>394</v>
       </c>
       <c r="B396" t="n">
@@ -24390,7 +24402,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" t="n">
+      <c r="A397" s="1" t="n">
         <v>395</v>
       </c>
       <c r="B397" t="n">
@@ -24450,7 +24462,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="n">
+      <c r="A398" s="1" t="n">
         <v>396</v>
       </c>
       <c r="B398" t="n">
@@ -24510,7 +24522,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="n">
+      <c r="A399" s="1" t="n">
         <v>397</v>
       </c>
       <c r="B399" t="n">
@@ -24570,7 +24582,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" t="n">
+      <c r="A400" s="1" t="n">
         <v>398</v>
       </c>
       <c r="B400" t="n">
@@ -24630,7 +24642,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" t="n">
+      <c r="A401" s="1" t="n">
         <v>399</v>
       </c>
       <c r="B401" t="n">
@@ -24690,7 +24702,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" t="n">
+      <c r="A402" s="1" t="n">
         <v>400</v>
       </c>
       <c r="B402" t="n">
@@ -24750,7 +24762,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="n">
+      <c r="A403" s="1" t="n">
         <v>401</v>
       </c>
       <c r="B403" t="n">
@@ -24810,7 +24822,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" t="n">
+      <c r="A404" s="1" t="n">
         <v>402</v>
       </c>
       <c r="B404" t="n">
@@ -24870,7 +24882,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" t="n">
+      <c r="A405" s="1" t="n">
         <v>403</v>
       </c>
       <c r="B405" t="n">
@@ -24930,7 +24942,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" t="n">
+      <c r="A406" s="1" t="n">
         <v>404</v>
       </c>
       <c r="B406" t="n">
@@ -24990,7 +25002,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" t="n">
+      <c r="A407" s="1" t="n">
         <v>405</v>
       </c>
       <c r="B407" t="n">
@@ -25050,7 +25062,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" t="n">
+      <c r="A408" s="1" t="n">
         <v>406</v>
       </c>
       <c r="B408" t="n">
@@ -25110,7 +25122,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" t="n">
+      <c r="A409" s="1" t="n">
         <v>407</v>
       </c>
       <c r="B409" t="n">
@@ -25170,7 +25182,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" t="n">
+      <c r="A410" s="1" t="n">
         <v>408</v>
       </c>
       <c r="B410" t="n">
@@ -25230,7 +25242,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" t="n">
+      <c r="A411" s="1" t="n">
         <v>409</v>
       </c>
       <c r="B411" t="n">
@@ -25288,7 +25300,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" t="n">
+      <c r="A412" s="1" t="n">
         <v>410</v>
       </c>
       <c r="B412" t="n">
@@ -25346,7 +25358,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" t="n">
+      <c r="A413" s="1" t="n">
         <v>411</v>
       </c>
       <c r="B413" t="n">
@@ -25404,7 +25416,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" t="n">
+      <c r="A414" s="1" t="n">
         <v>412</v>
       </c>
       <c r="B414" t="n">
@@ -25468,7 +25480,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="n">
+      <c r="A415" s="1" t="n">
         <v>413</v>
       </c>
       <c r="B415" t="n">
@@ -25526,7 +25538,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" t="n">
+      <c r="A416" s="1" t="n">
         <v>414</v>
       </c>
       <c r="B416" t="n">
@@ -25586,7 +25598,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" t="n">
+      <c r="A417" s="1" t="n">
         <v>415</v>
       </c>
       <c r="B417" t="n">
@@ -25644,7 +25656,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" t="n">
+      <c r="A418" s="1" t="n">
         <v>416</v>
       </c>
       <c r="B418" t="n">
@@ -25704,7 +25716,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" t="n">
+      <c r="A419" s="1" t="n">
         <v>417</v>
       </c>
       <c r="B419" t="n">
@@ -25764,7 +25776,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" t="n">
+      <c r="A420" s="1" t="n">
         <v>418</v>
       </c>
       <c r="B420" t="n">
@@ -25824,7 +25836,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" t="n">
+      <c r="A421" s="1" t="n">
         <v>419</v>
       </c>
       <c r="B421" t="n">
@@ -25884,7 +25896,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" t="n">
+      <c r="A422" s="1" t="n">
         <v>420</v>
       </c>
       <c r="B422" t="n">
@@ -25942,7 +25954,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" t="n">
+      <c r="A423" s="1" t="n">
         <v>421</v>
       </c>
       <c r="B423" t="n">
@@ -26002,7 +26014,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" t="n">
+      <c r="A424" s="1" t="n">
         <v>422</v>
       </c>
       <c r="B424" t="n">
@@ -26062,7 +26074,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" t="n">
+      <c r="A425" s="1" t="n">
         <v>423</v>
       </c>
       <c r="B425" t="n">
@@ -26122,7 +26134,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" t="n">
+      <c r="A426" s="1" t="n">
         <v>424</v>
       </c>
       <c r="B426" t="n">
@@ -26182,7 +26194,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="n">
+      <c r="A427" s="1" t="n">
         <v>425</v>
       </c>
       <c r="B427" t="n">
@@ -26240,7 +26252,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" t="n">
+      <c r="A428" s="1" t="n">
         <v>426</v>
       </c>
       <c r="B428" t="n">
@@ -26300,7 +26312,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" t="n">
+      <c r="A429" s="1" t="n">
         <v>427</v>
       </c>
       <c r="B429" t="n">
@@ -26360,7 +26372,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" t="n">
+      <c r="A430" s="1" t="n">
         <v>428</v>
       </c>
       <c r="B430" t="n">
@@ -26418,7 +26430,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" t="n">
+      <c r="A431" s="1" t="n">
         <v>429</v>
       </c>
       <c r="B431" t="n">
@@ -26482,7 +26494,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="n">
+      <c r="A432" s="1" t="n">
         <v>430</v>
       </c>
       <c r="B432" t="n">
@@ -26546,7 +26558,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" t="n">
+      <c r="A433" s="1" t="n">
         <v>431</v>
       </c>
       <c r="B433" t="n">
@@ -26604,7 +26616,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" t="n">
+      <c r="A434" s="1" t="n">
         <v>432</v>
       </c>
       <c r="B434" t="n">
@@ -26664,7 +26676,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" t="n">
+      <c r="A435" s="1" t="n">
         <v>433</v>
       </c>
       <c r="B435" t="n">
@@ -26724,7 +26736,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" t="n">
+      <c r="A436" s="1" t="n">
         <v>434</v>
       </c>
       <c r="B436" t="n">
@@ -26788,7 +26800,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" t="n">
+      <c r="A437" s="1" t="n">
         <v>435</v>
       </c>
       <c r="B437" t="n">
@@ -26852,7 +26864,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" t="n">
+      <c r="A438" s="1" t="n">
         <v>436</v>
       </c>
       <c r="B438" t="n">
@@ -26912,7 +26924,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" t="n">
+      <c r="A439" s="1" t="n">
         <v>437</v>
       </c>
       <c r="B439" t="n">
@@ -26972,7 +26984,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" t="n">
+      <c r="A440" s="1" t="n">
         <v>438</v>
       </c>
       <c r="B440" t="n">
@@ -27036,7 +27048,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" t="n">
+      <c r="A441" s="1" t="n">
         <v>439</v>
       </c>
       <c r="B441" t="n">
@@ -27096,7 +27108,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" t="n">
+      <c r="A442" s="1" t="n">
         <v>440</v>
       </c>
       <c r="B442" t="n">
@@ -27156,7 +27168,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" t="n">
+      <c r="A443" s="1" t="n">
         <v>441</v>
       </c>
       <c r="B443" t="n">
@@ -27216,7 +27228,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" t="n">
+      <c r="A444" s="1" t="n">
         <v>442</v>
       </c>
       <c r="B444" t="n">
@@ -27276,7 +27288,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" t="n">
+      <c r="A445" s="1" t="n">
         <v>443</v>
       </c>
       <c r="B445" t="n">
@@ -27336,7 +27348,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" t="n">
+      <c r="A446" s="1" t="n">
         <v>444</v>
       </c>
       <c r="B446" t="n">
@@ -27394,7 +27406,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" t="n">
+      <c r="A447" s="1" t="n">
         <v>445</v>
       </c>
       <c r="B447" t="n">
@@ -27458,7 +27470,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" t="n">
+      <c r="A448" s="1" t="n">
         <v>446</v>
       </c>
       <c r="B448" t="n">
@@ -27518,7 +27530,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" t="n">
+      <c r="A449" s="1" t="n">
         <v>447</v>
       </c>
       <c r="B449" t="n">
@@ -27578,7 +27590,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" t="n">
+      <c r="A450" s="1" t="n">
         <v>448</v>
       </c>
       <c r="B450" t="n">
@@ -27638,7 +27650,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" t="n">
+      <c r="A451" s="1" t="n">
         <v>449</v>
       </c>
       <c r="B451" t="n">
@@ -27702,7 +27714,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" t="n">
+      <c r="A452" s="1" t="n">
         <v>450</v>
       </c>
       <c r="B452" t="n">
@@ -27762,7 +27774,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" t="n">
+      <c r="A453" s="1" t="n">
         <v>451</v>
       </c>
       <c r="B453" t="n">
@@ -27820,7 +27832,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" t="n">
+      <c r="A454" s="1" t="n">
         <v>452</v>
       </c>
       <c r="B454" t="n">
@@ -27884,7 +27896,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="n">
+      <c r="A455" s="1" t="n">
         <v>453</v>
       </c>
       <c r="B455" t="n">
@@ -27948,7 +27960,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" t="n">
+      <c r="A456" s="1" t="n">
         <v>454</v>
       </c>
       <c r="B456" t="n">
@@ -28006,7 +28018,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" t="n">
+      <c r="A457" s="1" t="n">
         <v>455</v>
       </c>
       <c r="B457" t="n">
@@ -28066,7 +28078,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" t="n">
+      <c r="A458" s="1" t="n">
         <v>456</v>
       </c>
       <c r="B458" t="n">
@@ -28130,7 +28142,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" t="n">
+      <c r="A459" s="1" t="n">
         <v>457</v>
       </c>
       <c r="B459" t="n">
@@ -28192,7 +28204,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" t="n">
+      <c r="A460" s="1" t="n">
         <v>458</v>
       </c>
       <c r="B460" t="n">
@@ -28252,7 +28264,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" t="n">
+      <c r="A461" s="1" t="n">
         <v>459</v>
       </c>
       <c r="B461" t="n">
@@ -28310,7 +28322,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" t="n">
+      <c r="A462" s="1" t="n">
         <v>460</v>
       </c>
       <c r="B462" t="n">
@@ -28374,7 +28386,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" t="n">
+      <c r="A463" s="1" t="n">
         <v>461</v>
       </c>
       <c r="B463" t="n">
@@ -28434,7 +28446,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" t="n">
+      <c r="A464" s="1" t="n">
         <v>462</v>
       </c>
       <c r="B464" t="n">
@@ -28498,7 +28510,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" t="n">
+      <c r="A465" s="1" t="n">
         <v>463</v>
       </c>
       <c r="B465" t="n">
@@ -28558,7 +28570,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" t="n">
+      <c r="A466" s="1" t="n">
         <v>464</v>
       </c>
       <c r="B466" t="n">
@@ -28616,7 +28628,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" t="n">
+      <c r="A467" s="1" t="n">
         <v>465</v>
       </c>
       <c r="B467" t="n">
@@ -28676,7 +28688,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" t="n">
+      <c r="A468" s="1" t="n">
         <v>466</v>
       </c>
       <c r="B468" t="n">
@@ -28734,7 +28746,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" t="n">
+      <c r="A469" s="1" t="n">
         <v>467</v>
       </c>
       <c r="B469" t="n">
@@ -28794,7 +28806,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" t="n">
+      <c r="A470" s="1" t="n">
         <v>468</v>
       </c>
       <c r="B470" t="n">
@@ -28852,7 +28864,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" t="n">
+      <c r="A471" s="1" t="n">
         <v>469</v>
       </c>
       <c r="B471" t="n">
@@ -28912,7 +28924,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" t="n">
+      <c r="A472" s="1" t="n">
         <v>470</v>
       </c>
       <c r="B472" t="n">
@@ -28970,7 +28982,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" t="n">
+      <c r="A473" s="1" t="n">
         <v>471</v>
       </c>
       <c r="B473" t="n">
@@ -29030,7 +29042,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" t="n">
+      <c r="A474" s="1" t="n">
         <v>472</v>
       </c>
       <c r="B474" t="n">
@@ -29090,7 +29102,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" t="n">
+      <c r="A475" s="1" t="n">
         <v>473</v>
       </c>
       <c r="B475" t="n">
@@ -29154,7 +29166,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" t="n">
+      <c r="A476" s="1" t="n">
         <v>474</v>
       </c>
       <c r="B476" t="n">
@@ -29214,7 +29226,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" t="n">
+      <c r="A477" s="1" t="n">
         <v>475</v>
       </c>
       <c r="B477" t="n">
@@ -29276,7 +29288,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" t="n">
+      <c r="A478" s="1" t="n">
         <v>476</v>
       </c>
       <c r="B478" t="n">
@@ -29336,7 +29348,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" t="n">
+      <c r="A479" s="1" t="n">
         <v>477</v>
       </c>
       <c r="B479" t="n">
@@ -29396,7 +29408,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" t="n">
+      <c r="A480" s="1" t="n">
         <v>478</v>
       </c>
       <c r="B480" t="n">
@@ -29456,7 +29468,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" t="n">
+      <c r="A481" s="1" t="n">
         <v>479</v>
       </c>
       <c r="B481" t="n">
@@ -29516,7 +29528,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" t="n">
+      <c r="A482" s="1" t="n">
         <v>480</v>
       </c>
       <c r="B482" t="n">
@@ -29576,7 +29588,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" t="n">
+      <c r="A483" s="1" t="n">
         <v>481</v>
       </c>
       <c r="B483" t="n">
@@ -29634,7 +29646,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" t="n">
+      <c r="A484" s="1" t="n">
         <v>482</v>
       </c>
       <c r="B484" t="n">
@@ -29694,7 +29706,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" t="n">
+      <c r="A485" s="1" t="n">
         <v>483</v>
       </c>
       <c r="B485" t="n">
@@ -29754,7 +29766,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" t="n">
+      <c r="A486" s="1" t="n">
         <v>484</v>
       </c>
       <c r="B486" t="n">
@@ -29818,7 +29830,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" t="n">
+      <c r="A487" s="1" t="n">
         <v>485</v>
       </c>
       <c r="B487" t="n">
@@ -29876,7 +29888,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" t="n">
+      <c r="A488" s="1" t="n">
         <v>486</v>
       </c>
       <c r="B488" t="n">
@@ -29940,7 +29952,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" t="n">
+      <c r="A489" s="1" t="n">
         <v>487</v>
       </c>
       <c r="B489" t="n">
@@ -30004,7 +30016,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" t="n">
+      <c r="A490" s="1" t="n">
         <v>488</v>
       </c>
       <c r="B490" t="n">
@@ -30064,7 +30076,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" t="n">
+      <c r="A491" s="1" t="n">
         <v>489</v>
       </c>
       <c r="B491" t="n">
@@ -30124,7 +30136,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" t="n">
+      <c r="A492" s="1" t="n">
         <v>490</v>
       </c>
       <c r="B492" t="n">
@@ -30182,7 +30194,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" t="n">
+      <c r="A493" s="1" t="n">
         <v>491</v>
       </c>
       <c r="B493" t="n">
@@ -30242,7 +30254,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" t="n">
+      <c r="A494" s="1" t="n">
         <v>492</v>
       </c>
       <c r="B494" t="n">
@@ -30306,7 +30318,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" t="n">
+      <c r="A495" s="1" t="n">
         <v>493</v>
       </c>
       <c r="B495" t="n">
@@ -30366,7 +30378,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" t="n">
+      <c r="A496" s="1" t="n">
         <v>494</v>
       </c>
       <c r="B496" t="n">
@@ -30426,7 +30438,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" t="n">
+      <c r="A497" s="1" t="n">
         <v>495</v>
       </c>
       <c r="B497" t="n">
@@ -30484,7 +30496,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" t="n">
+      <c r="A498" s="1" t="n">
         <v>496</v>
       </c>
       <c r="B498" t="n">
@@ -30548,7 +30560,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" t="n">
+      <c r="A499" s="1" t="n">
         <v>497</v>
       </c>
       <c r="B499" t="n">
@@ -30606,7 +30618,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" t="n">
+      <c r="A500" s="1" t="n">
         <v>498</v>
       </c>
       <c r="B500" t="n">
@@ -30670,7 +30682,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" t="n">
+      <c r="A501" s="1" t="n">
         <v>499</v>
       </c>
       <c r="B501" t="n">
@@ -30730,7 +30742,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" t="n">
+      <c r="A502" s="1" t="n">
         <v>500</v>
       </c>
       <c r="B502" t="n">
@@ -30790,7 +30802,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" t="n">
+      <c r="A503" s="1" t="n">
         <v>501</v>
       </c>
       <c r="B503" t="n">
@@ -30850,7 +30862,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" t="n">
+      <c r="A504" s="1" t="n">
         <v>502</v>
       </c>
       <c r="B504" t="n">
@@ -30908,7 +30920,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" t="n">
+      <c r="A505" s="1" t="n">
         <v>503</v>
       </c>
       <c r="B505" t="n">
@@ -30968,7 +30980,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" t="n">
+      <c r="A506" s="1" t="n">
         <v>504</v>
       </c>
       <c r="B506" t="n">
@@ -31032,7 +31044,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" t="n">
+      <c r="A507" s="1" t="n">
         <v>505</v>
       </c>
       <c r="B507" t="n">
@@ -31096,7 +31108,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" t="n">
+      <c r="A508" s="1" t="n">
         <v>506</v>
       </c>
       <c r="B508" t="n">
@@ -31156,7 +31168,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" t="n">
+      <c r="A509" s="1" t="n">
         <v>507</v>
       </c>
       <c r="B509" t="n">
@@ -31214,7 +31226,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" t="n">
+      <c r="A510" s="1" t="n">
         <v>508</v>
       </c>
       <c r="B510" t="n">
@@ -31274,7 +31286,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" t="n">
+      <c r="A511" s="1" t="n">
         <v>509</v>
       </c>
       <c r="B511" t="n">
@@ -31334,7 +31346,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" t="n">
+      <c r="A512" s="1" t="n">
         <v>510</v>
       </c>
       <c r="B512" t="n">
@@ -31394,7 +31406,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" t="n">
+      <c r="A513" s="1" t="n">
         <v>511</v>
       </c>
       <c r="B513" t="n">
@@ -31452,7 +31464,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" t="n">
+      <c r="A514" s="1" t="n">
         <v>512</v>
       </c>
       <c r="B514" t="n">
@@ -31516,7 +31528,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" t="n">
+      <c r="A515" s="1" t="n">
         <v>513</v>
       </c>
       <c r="B515" t="n">
@@ -31576,7 +31588,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" t="n">
+      <c r="A516" s="1" t="n">
         <v>514</v>
       </c>
       <c r="B516" t="n">
@@ -31636,7 +31648,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" t="n">
+      <c r="A517" s="1" t="n">
         <v>515</v>
       </c>
       <c r="B517" t="n">
@@ -31700,7 +31712,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" t="n">
+      <c r="A518" s="1" t="n">
         <v>516</v>
       </c>
       <c r="B518" t="n">
@@ -31764,7 +31776,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" t="n">
+      <c r="A519" s="1" t="n">
         <v>517</v>
       </c>
       <c r="B519" t="n">
@@ -31822,7 +31834,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" t="n">
+      <c r="A520" s="1" t="n">
         <v>518</v>
       </c>
       <c r="B520" t="n">
@@ -31882,7 +31894,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" t="n">
+      <c r="A521" s="1" t="n">
         <v>519</v>
       </c>
       <c r="B521" t="n">
@@ -31942,7 +31954,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" t="n">
+      <c r="A522" s="1" t="n">
         <v>520</v>
       </c>
       <c r="B522" t="n">
@@ -32006,7 +32018,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" t="n">
+      <c r="A523" s="1" t="n">
         <v>521</v>
       </c>
       <c r="B523" t="n">
@@ -32066,7 +32078,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" t="n">
+      <c r="A524" s="1" t="n">
         <v>522</v>
       </c>
       <c r="B524" t="n">
@@ -32124,7 +32136,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" t="n">
+      <c r="A525" s="1" t="n">
         <v>523</v>
       </c>
       <c r="B525" t="n">
@@ -32188,7 +32200,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" t="n">
+      <c r="A526" s="1" t="n">
         <v>524</v>
       </c>
       <c r="B526" t="n">
@@ -32246,7 +32258,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" t="n">
+      <c r="A527" s="1" t="n">
         <v>525</v>
       </c>
       <c r="B527" t="n">
@@ -32306,7 +32318,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" t="n">
+      <c r="A528" s="1" t="n">
         <v>526</v>
       </c>
       <c r="B528" t="n">
@@ -32366,7 +32378,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" t="n">
+      <c r="A529" s="1" t="n">
         <v>527</v>
       </c>
       <c r="B529" t="n">
@@ -32428,7 +32440,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" t="n">
+      <c r="A530" s="1" t="n">
         <v>528</v>
       </c>
       <c r="B530" t="n">
@@ -32488,7 +32500,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" t="n">
+      <c r="A531" s="1" t="n">
         <v>529</v>
       </c>
       <c r="B531" t="n">
@@ -32548,7 +32560,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" t="n">
+      <c r="A532" s="1" t="n">
         <v>530</v>
       </c>
       <c r="B532" t="n">
@@ -32608,7 +32620,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" t="n">
+      <c r="A533" s="1" t="n">
         <v>531</v>
       </c>
       <c r="B533" t="n">
@@ -32666,7 +32678,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" t="n">
+      <c r="A534" s="1" t="n">
         <v>532</v>
       </c>
       <c r="B534" t="n">
@@ -32726,7 +32738,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" t="n">
+      <c r="A535" s="1" t="n">
         <v>533</v>
       </c>
       <c r="B535" t="n">
@@ -32784,7 +32796,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" t="n">
+      <c r="A536" s="1" t="n">
         <v>534</v>
       </c>
       <c r="B536" t="n">
@@ -32844,7 +32856,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" t="n">
+      <c r="A537" s="1" t="n">
         <v>535</v>
       </c>
       <c r="B537" t="n">
@@ -32904,7 +32916,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" t="n">
+      <c r="A538" s="1" t="n">
         <v>536</v>
       </c>
       <c r="B538" t="n">
@@ -32968,7 +32980,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" t="n">
+      <c r="A539" s="1" t="n">
         <v>537</v>
       </c>
       <c r="B539" t="n">
@@ -33028,7 +33040,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" t="n">
+      <c r="A540" s="1" t="n">
         <v>538</v>
       </c>
       <c r="B540" t="n">
@@ -33086,7 +33098,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" t="n">
+      <c r="A541" s="1" t="n">
         <v>539</v>
       </c>
       <c r="B541" t="n">
@@ -33150,7 +33162,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" t="n">
+      <c r="A542" s="1" t="n">
         <v>540</v>
       </c>
       <c r="B542" t="n">
@@ -33214,7 +33226,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" t="n">
+      <c r="A543" s="1" t="n">
         <v>541</v>
       </c>
       <c r="B543" t="n">
@@ -33274,7 +33286,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" t="n">
+      <c r="A544" s="1" t="n">
         <v>542</v>
       </c>
       <c r="B544" t="n">
@@ -33334,7 +33346,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" t="n">
+      <c r="A545" s="1" t="n">
         <v>543</v>
       </c>
       <c r="B545" t="n">
@@ -33394,7 +33406,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" t="n">
+      <c r="A546" s="1" t="n">
         <v>544</v>
       </c>
       <c r="B546" t="n">
@@ -33458,7 +33470,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" t="n">
+      <c r="A547" s="1" t="n">
         <v>545</v>
       </c>
       <c r="B547" t="n">
@@ -33518,7 +33530,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" t="n">
+      <c r="A548" s="1" t="n">
         <v>546</v>
       </c>
       <c r="B548" t="n">
@@ -33578,7 +33590,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" t="n">
+      <c r="A549" s="1" t="n">
         <v>547</v>
       </c>
       <c r="B549" t="n">
@@ -33636,7 +33648,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" t="n">
+      <c r="A550" s="1" t="n">
         <v>548</v>
       </c>
       <c r="B550" t="n">
@@ -33696,7 +33708,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" t="n">
+      <c r="A551" s="1" t="n">
         <v>549</v>
       </c>
       <c r="B551" t="n">
@@ -33756,7 +33768,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" t="n">
+      <c r="A552" s="1" t="n">
         <v>550</v>
       </c>
       <c r="B552" t="n">
@@ -33820,7 +33832,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" t="n">
+      <c r="A553" s="1" t="n">
         <v>551</v>
       </c>
       <c r="B553" t="n">
@@ -33880,7 +33892,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" t="n">
+      <c r="A554" s="1" t="n">
         <v>552</v>
       </c>
       <c r="B554" t="n">
@@ -33938,7 +33950,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" t="n">
+      <c r="A555" s="1" t="n">
         <v>553</v>
       </c>
       <c r="B555" t="n">
@@ -33998,7 +34010,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" t="n">
+      <c r="A556" s="1" t="n">
         <v>554</v>
       </c>
       <c r="B556" t="n">
@@ -34058,7 +34070,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" t="n">
+      <c r="A557" s="1" t="n">
         <v>555</v>
       </c>
       <c r="B557" t="n">
@@ -34118,7 +34130,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" t="n">
+      <c r="A558" s="1" t="n">
         <v>556</v>
       </c>
       <c r="B558" t="n">
@@ -34182,7 +34194,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" t="n">
+      <c r="A559" s="1" t="n">
         <v>557</v>
       </c>
       <c r="B559" t="n">
@@ -34240,7 +34252,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" t="n">
+      <c r="A560" s="1" t="n">
         <v>558</v>
       </c>
       <c r="B560" t="n">
@@ -34304,7 +34316,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" t="n">
+      <c r="A561" s="1" t="n">
         <v>559</v>
       </c>
       <c r="B561" t="n">
@@ -34364,7 +34376,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" t="n">
+      <c r="A562" s="1" t="n">
         <v>560</v>
       </c>
       <c r="B562" t="n">
@@ -34422,7 +34434,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" t="n">
+      <c r="A563" s="1" t="n">
         <v>561</v>
       </c>
       <c r="B563" t="n">
@@ -34482,7 +34494,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" t="n">
+      <c r="A564" s="1" t="n">
         <v>562</v>
       </c>
       <c r="B564" t="n">
@@ -34542,7 +34554,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" t="n">
+      <c r="A565" s="1" t="n">
         <v>563</v>
       </c>
       <c r="B565" t="n">
@@ -34600,7 +34612,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" t="n">
+      <c r="A566" s="1" t="n">
         <v>564</v>
       </c>
       <c r="B566" t="n">
@@ -34658,7 +34670,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" t="n">
+      <c r="A567" s="1" t="n">
         <v>565</v>
       </c>
       <c r="B567" t="n">
@@ -34718,7 +34730,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" t="n">
+      <c r="A568" s="1" t="n">
         <v>566</v>
       </c>
       <c r="B568" t="n">
@@ -34778,7 +34790,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" t="n">
+      <c r="A569" s="1" t="n">
         <v>567</v>
       </c>
       <c r="B569" t="n">
@@ -34838,7 +34850,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" t="n">
+      <c r="A570" s="1" t="n">
         <v>568</v>
       </c>
       <c r="B570" t="n">
@@ -34896,7 +34908,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" t="n">
+      <c r="A571" s="1" t="n">
         <v>569</v>
       </c>
       <c r="B571" t="n">
@@ -34956,7 +34968,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" t="n">
+      <c r="A572" s="1" t="n">
         <v>570</v>
       </c>
       <c r="B572" t="n">
@@ -35016,7 +35028,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="n">
+      <c r="A573" s="1" t="n">
         <v>571</v>
       </c>
       <c r="B573" t="n">
@@ -35080,7 +35092,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="n">
+      <c r="A574" s="1" t="n">
         <v>572</v>
       </c>
       <c r="B574" t="n">
@@ -35144,7 +35156,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="n">
+      <c r="A575" s="1" t="n">
         <v>573</v>
       </c>
       <c r="B575" t="n">
@@ -35202,7 +35214,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="n">
+      <c r="A576" s="1" t="n">
         <v>574</v>
       </c>
       <c r="B576" t="n">
@@ -35262,7 +35274,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="n">
+      <c r="A577" s="1" t="n">
         <v>575</v>
       </c>
       <c r="B577" t="n">
@@ -35322,7 +35334,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="n">
+      <c r="A578" s="1" t="n">
         <v>576</v>
       </c>
       <c r="B578" t="n">
@@ -35382,7 +35394,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="n">
+      <c r="A579" s="1" t="n">
         <v>577</v>
       </c>
       <c r="B579" t="n">
@@ -35446,7 +35458,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="n">
+      <c r="A580" s="1" t="n">
         <v>578</v>
       </c>
       <c r="B580" t="n">
@@ -35504,7 +35516,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="n">
+      <c r="A581" s="1" t="n">
         <v>579</v>
       </c>
       <c r="B581" t="n">
@@ -35564,7 +35576,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="n">
+      <c r="A582" s="1" t="n">
         <v>580</v>
       </c>
       <c r="B582" t="n">
@@ -35624,7 +35636,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="n">
+      <c r="A583" s="1" t="n">
         <v>581</v>
       </c>
       <c r="B583" t="n">
@@ -35688,7 +35700,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="n">
+      <c r="A584" s="1" t="n">
         <v>582</v>
       </c>
       <c r="B584" t="n">
@@ -35748,7 +35760,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="n">
+      <c r="A585" s="1" t="n">
         <v>583</v>
       </c>
       <c r="B585" t="n">
@@ -35812,7 +35824,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="n">
+      <c r="A586" s="1" t="n">
         <v>584</v>
       </c>
       <c r="B586" t="n">
@@ -35870,7 +35882,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="n">
+      <c r="A587" s="1" t="n">
         <v>585</v>
       </c>
       <c r="B587" t="n">
@@ -35934,7 +35946,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="n">
+      <c r="A588" s="1" t="n">
         <v>586</v>
       </c>
       <c r="B588" t="n">
@@ -35994,7 +36006,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="n">
+      <c r="A589" s="1" t="n">
         <v>587</v>
       </c>
       <c r="B589" t="n">
@@ -36058,7 +36070,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="n">
+      <c r="A590" s="1" t="n">
         <v>588</v>
       </c>
       <c r="B590" t="n">
@@ -36118,7 +36130,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="n">
+      <c r="A591" s="1" t="n">
         <v>589</v>
       </c>
       <c r="B591" t="n">
@@ -36176,7 +36188,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="n">
+      <c r="A592" s="1" t="n">
         <v>590</v>
       </c>
       <c r="B592" t="n">
@@ -36236,7 +36248,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="n">
+      <c r="A593" s="1" t="n">
         <v>591</v>
       </c>
       <c r="B593" t="n">
@@ -36300,7 +36312,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="n">
+      <c r="A594" s="1" t="n">
         <v>592</v>
       </c>
       <c r="B594" t="n">
@@ -36360,7 +36372,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="n">
+      <c r="A595" s="1" t="n">
         <v>593</v>
       </c>
       <c r="B595" t="n">
@@ -36418,7 +36430,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="n">
+      <c r="A596" s="1" t="n">
         <v>594</v>
       </c>
       <c r="B596" t="n">
@@ -36478,7 +36490,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="n">
+      <c r="A597" s="1" t="n">
         <v>595</v>
       </c>
       <c r="B597" t="n">
@@ -36538,7 +36550,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="n">
+      <c r="A598" s="1" t="n">
         <v>596</v>
       </c>
       <c r="B598" t="n">
@@ -36596,7 +36608,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="n">
+      <c r="A599" s="1" t="n">
         <v>597</v>
       </c>
       <c r="B599" t="n">
@@ -36656,7 +36668,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="n">
+      <c r="A600" s="1" t="n">
         <v>598</v>
       </c>
       <c r="B600" t="n">
@@ -36714,7 +36726,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="n">
+      <c r="A601" s="1" t="n">
         <v>599</v>
       </c>
       <c r="B601" t="n">
@@ -36778,7 +36790,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="n">
+      <c r="A602" s="1" t="n">
         <v>600</v>
       </c>
       <c r="B602" t="n">
@@ -36838,7 +36850,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="n">
+      <c r="A603" s="1" t="n">
         <v>601</v>
       </c>
       <c r="B603" t="n">
@@ -36896,7 +36908,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="n">
+      <c r="A604" s="1" t="n">
         <v>602</v>
       </c>
       <c r="B604" t="n">
@@ -36954,7 +36966,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="n">
+      <c r="A605" s="1" t="n">
         <v>603</v>
       </c>
       <c r="B605" t="n">
@@ -37014,7 +37026,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="n">
+      <c r="A606" s="1" t="n">
         <v>604</v>
       </c>
       <c r="B606" t="n">
@@ -37074,7 +37086,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="n">
+      <c r="A607" s="1" t="n">
         <v>605</v>
       </c>
       <c r="B607" t="n">
@@ -37134,7 +37146,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="n">
+      <c r="A608" s="1" t="n">
         <v>606</v>
       </c>
       <c r="B608" t="n">
@@ -37194,7 +37206,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="n">
+      <c r="A609" s="1" t="n">
         <v>607</v>
       </c>
       <c r="B609" t="n">
@@ -37254,7 +37266,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="n">
+      <c r="A610" s="1" t="n">
         <v>608</v>
       </c>
       <c r="B610" t="n">
@@ -37314,7 +37326,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="n">
+      <c r="A611" s="1" t="n">
         <v>609</v>
       </c>
       <c r="B611" t="n">
@@ -37378,7 +37390,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="n">
+      <c r="A612" s="1" t="n">
         <v>610</v>
       </c>
       <c r="B612" t="n">
@@ -37438,7 +37450,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="n">
+      <c r="A613" s="1" t="n">
         <v>611</v>
       </c>
       <c r="B613" t="n">
@@ -37496,7 +37508,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="n">
+      <c r="A614" s="1" t="n">
         <v>612</v>
       </c>
       <c r="B614" t="n">
@@ -37554,7 +37566,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="n">
+      <c r="A615" s="1" t="n">
         <v>613</v>
       </c>
       <c r="B615" t="n">
@@ -37612,7 +37624,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="n">
+      <c r="A616" s="1" t="n">
         <v>614</v>
       </c>
       <c r="B616" t="n">
@@ -37672,7 +37684,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="n">
+      <c r="A617" s="1" t="n">
         <v>615</v>
       </c>
       <c r="B617" t="n">
@@ -37732,7 +37744,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="n">
+      <c r="A618" s="1" t="n">
         <v>616</v>
       </c>
       <c r="B618" t="n">
@@ -37792,7 +37804,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="n">
+      <c r="A619" s="1" t="n">
         <v>617</v>
       </c>
       <c r="B619" t="n">
@@ -37852,7 +37864,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="n">
+      <c r="A620" s="1" t="n">
         <v>618</v>
       </c>
       <c r="B620" t="n">
@@ -37916,7 +37928,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="n">
+      <c r="A621" s="1" t="n">
         <v>619</v>
       </c>
       <c r="B621" t="n">
@@ -37976,7 +37988,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="n">
+      <c r="A622" s="1" t="n">
         <v>620</v>
       </c>
       <c r="B622" t="n">
@@ -38036,7 +38048,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="n">
+      <c r="A623" s="1" t="n">
         <v>621</v>
       </c>
       <c r="B623" t="n">
@@ -38100,7 +38112,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="n">
+      <c r="A624" s="1" t="n">
         <v>622</v>
       </c>
       <c r="B624" t="n">
@@ -38160,7 +38172,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="n">
+      <c r="A625" s="1" t="n">
         <v>623</v>
       </c>
       <c r="B625" t="n">
@@ -38220,7 +38232,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="n">
+      <c r="A626" s="1" t="n">
         <v>624</v>
       </c>
       <c r="B626" t="n">
@@ -38280,7 +38292,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="n">
+      <c r="A627" s="1" t="n">
         <v>625</v>
       </c>
       <c r="B627" t="n">
@@ -38344,7 +38356,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="n">
+      <c r="A628" s="1" t="n">
         <v>626</v>
       </c>
       <c r="B628" t="n">
@@ -38404,7 +38416,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="n">
+      <c r="A629" s="1" t="n">
         <v>627</v>
       </c>
       <c r="B629" t="n">
@@ -38468,7 +38480,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="n">
+      <c r="A630" s="1" t="n">
         <v>628</v>
       </c>
       <c r="B630" t="n">
@@ -38528,7 +38540,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="n">
+      <c r="A631" s="1" t="n">
         <v>629</v>
       </c>
       <c r="B631" t="n">
@@ -38586,7 +38598,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="n">
+      <c r="A632" s="1" t="n">
         <v>630</v>
       </c>
       <c r="B632" t="n">
@@ -38650,7 +38662,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="n">
+      <c r="A633" s="1" t="n">
         <v>631</v>
       </c>
       <c r="B633" t="n">
@@ -38710,7 +38722,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="n">
+      <c r="A634" s="1" t="n">
         <v>632</v>
       </c>
       <c r="B634" t="n">
@@ -38774,7 +38786,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="n">
+      <c r="A635" s="1" t="n">
         <v>633</v>
       </c>
       <c r="B635" t="n">
@@ -38832,7 +38844,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="n">
+      <c r="A636" s="1" t="n">
         <v>634</v>
       </c>
       <c r="B636" t="n">
@@ -38892,7 +38904,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="n">
+      <c r="A637" s="1" t="n">
         <v>635</v>
       </c>
       <c r="B637" t="n">
@@ -38952,7 +38964,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="n">
+      <c r="A638" s="1" t="n">
         <v>636</v>
       </c>
       <c r="B638" t="n">
@@ -39012,7 +39024,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="n">
+      <c r="A639" s="1" t="n">
         <v>637</v>
       </c>
       <c r="B639" t="n">
@@ -39072,7 +39084,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="n">
+      <c r="A640" s="1" t="n">
         <v>638</v>
       </c>
       <c r="B640" t="n">
@@ -39132,7 +39144,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="n">
+      <c r="A641" s="1" t="n">
         <v>639</v>
       </c>
       <c r="B641" t="n">
@@ -39190,7 +39202,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="n">
+      <c r="A642" s="1" t="n">
         <v>640</v>
       </c>
       <c r="B642" t="n">
@@ -39250,7 +39262,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="n">
+      <c r="A643" s="1" t="n">
         <v>641</v>
       </c>
       <c r="B643" t="n">
@@ -39314,7 +39326,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="n">
+      <c r="A644" s="1" t="n">
         <v>642</v>
       </c>
       <c r="B644" t="n">
@@ -39374,7 +39386,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="n">
+      <c r="A645" s="1" t="n">
         <v>643</v>
       </c>
       <c r="B645" t="n">
@@ -39432,7 +39444,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="n">
+      <c r="A646" s="1" t="n">
         <v>644</v>
       </c>
       <c r="B646" t="n">
@@ -39492,7 +39504,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="n">
+      <c r="A647" s="1" t="n">
         <v>645</v>
       </c>
       <c r="B647" t="n">
@@ -39556,7 +39568,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="n">
+      <c r="A648" s="1" t="n">
         <v>646</v>
       </c>
       <c r="B648" t="n">
@@ -39616,7 +39628,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="n">
+      <c r="A649" s="1" t="n">
         <v>647</v>
       </c>
       <c r="B649" t="n">
@@ -39680,7 +39692,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="n">
+      <c r="A650" s="1" t="n">
         <v>648</v>
       </c>
       <c r="B650" t="n">
@@ -39738,7 +39750,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="n">
+      <c r="A651" s="1" t="n">
         <v>649</v>
       </c>
       <c r="B651" t="n">
@@ -39798,7 +39810,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="n">
+      <c r="A652" s="1" t="n">
         <v>650</v>
       </c>
       <c r="B652" t="n">
@@ -39856,7 +39868,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="n">
+      <c r="A653" s="1" t="n">
         <v>651</v>
       </c>
       <c r="B653" t="n">
@@ -39916,7 +39928,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" t="n">
+      <c r="A654" s="1" t="n">
         <v>652</v>
       </c>
       <c r="B654" t="n">
@@ -39976,7 +39988,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" t="n">
+      <c r="A655" s="1" t="n">
         <v>653</v>
       </c>
       <c r="B655" t="n">
@@ -40034,7 +40046,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" t="n">
+      <c r="A656" s="1" t="n">
         <v>654</v>
       </c>
       <c r="B656" t="n">
@@ -40094,7 +40106,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" t="n">
+      <c r="A657" s="1" t="n">
         <v>655</v>
       </c>
       <c r="B657" t="n">
@@ -40154,7 +40166,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" t="n">
+      <c r="A658" s="1" t="n">
         <v>656</v>
       </c>
       <c r="B658" t="n">
@@ -40212,7 +40224,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" t="n">
+      <c r="A659" s="1" t="n">
         <v>657</v>
       </c>
       <c r="B659" t="n">
@@ -40272,7 +40284,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" t="n">
+      <c r="A660" s="1" t="n">
         <v>658</v>
       </c>
       <c r="B660" t="n">
@@ -40332,7 +40344,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" t="n">
+      <c r="A661" s="1" t="n">
         <v>659</v>
       </c>
       <c r="B661" t="n">
@@ -40396,7 +40408,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" t="n">
+      <c r="A662" s="1" t="n">
         <v>660</v>
       </c>
       <c r="B662" t="n">
@@ -40456,7 +40468,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" t="n">
+      <c r="A663" s="1" t="n">
         <v>661</v>
       </c>
       <c r="B663" t="n">
@@ -40516,7 +40528,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" t="n">
+      <c r="A664" s="1" t="n">
         <v>662</v>
       </c>
       <c r="B664" t="n">
@@ -40580,7 +40592,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" t="n">
+      <c r="A665" s="1" t="n">
         <v>663</v>
       </c>
       <c r="B665" t="n">
@@ -40640,7 +40652,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" t="n">
+      <c r="A666" s="1" t="n">
         <v>664</v>
       </c>
       <c r="B666" t="n">
@@ -40700,7 +40712,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" t="n">
+      <c r="A667" s="1" t="n">
         <v>665</v>
       </c>
       <c r="B667" t="n">
@@ -40760,7 +40772,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" t="n">
+      <c r="A668" s="1" t="n">
         <v>666</v>
       </c>
       <c r="B668" t="n">
@@ -40820,7 +40832,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" t="n">
+      <c r="A669" s="1" t="n">
         <v>667</v>
       </c>
       <c r="B669" t="n">
@@ -40878,7 +40890,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="n">
+      <c r="A670" s="1" t="n">
         <v>668</v>
       </c>
       <c r="B670" t="n">
@@ -40938,7 +40950,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="n">
+      <c r="A671" s="1" t="n">
         <v>669</v>
       </c>
       <c r="B671" t="n">
@@ -41000,7 +41012,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="n">
+      <c r="A672" s="1" t="n">
         <v>670</v>
       </c>
       <c r="B672" t="n">
@@ -41060,7 +41072,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="n">
+      <c r="A673" s="1" t="n">
         <v>671</v>
       </c>
       <c r="B673" t="n">
@@ -41124,7 +41136,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="n">
+      <c r="A674" s="1" t="n">
         <v>672</v>
       </c>
       <c r="B674" t="n">
@@ -41184,7 +41196,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="n">
+      <c r="A675" s="1" t="n">
         <v>673</v>
       </c>
       <c r="B675" t="n">
@@ -41244,7 +41256,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="n">
+      <c r="A676" s="1" t="n">
         <v>674</v>
       </c>
       <c r="B676" t="n">
@@ -41302,7 +41314,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="n">
+      <c r="A677" s="1" t="n">
         <v>675</v>
       </c>
       <c r="B677" t="n">
@@ -41362,7 +41374,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="n">
+      <c r="A678" s="1" t="n">
         <v>676</v>
       </c>
       <c r="B678" t="n">
@@ -41422,7 +41434,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="n">
+      <c r="A679" s="1" t="n">
         <v>677</v>
       </c>
       <c r="B679" t="n">
@@ -41482,7 +41494,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="n">
+      <c r="A680" s="1" t="n">
         <v>678</v>
       </c>
       <c r="B680" t="n">
@@ -41542,7 +41554,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="n">
+      <c r="A681" s="1" t="n">
         <v>679</v>
       </c>
       <c r="B681" t="n">
@@ -41606,7 +41618,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="n">
+      <c r="A682" s="1" t="n">
         <v>680</v>
       </c>
       <c r="B682" t="n">
@@ -41664,7 +41676,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="n">
+      <c r="A683" s="1" t="n">
         <v>681</v>
       </c>
       <c r="B683" t="n">
@@ -41728,7 +41740,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="n">
+      <c r="A684" s="1" t="n">
         <v>682</v>
       </c>
       <c r="B684" t="n">
@@ -41788,7 +41800,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="n">
+      <c r="A685" s="1" t="n">
         <v>683</v>
       </c>
       <c r="B685" t="n">
@@ -41848,7 +41860,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="n">
+      <c r="A686" s="1" t="n">
         <v>684</v>
       </c>
       <c r="B686" t="n">
@@ -41908,7 +41920,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="n">
+      <c r="A687" s="1" t="n">
         <v>685</v>
       </c>
       <c r="B687" t="n">
@@ -41968,7 +41980,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="n">
+      <c r="A688" s="1" t="n">
         <v>686</v>
       </c>
       <c r="B688" t="n">
@@ -42028,7 +42040,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="n">
+      <c r="A689" s="1" t="n">
         <v>687</v>
       </c>
       <c r="B689" t="n">
@@ -42088,7 +42100,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" t="n">
+      <c r="A690" s="1" t="n">
         <v>688</v>
       </c>
       <c r="B690" t="n">
@@ -42148,7 +42160,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" t="n">
+      <c r="A691" s="1" t="n">
         <v>689</v>
       </c>
       <c r="B691" t="n">
@@ -42212,7 +42224,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" t="n">
+      <c r="A692" s="1" t="n">
         <v>690</v>
       </c>
       <c r="B692" t="n">
@@ -42276,7 +42288,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" t="n">
+      <c r="A693" s="1" t="n">
         <v>691</v>
       </c>
       <c r="B693" t="n">
@@ -42336,7 +42348,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" t="n">
+      <c r="A694" s="1" t="n">
         <v>692</v>
       </c>
       <c r="B694" t="n">
@@ -42394,7 +42406,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" t="n">
+      <c r="A695" s="1" t="n">
         <v>693</v>
       </c>
       <c r="B695" t="n">
@@ -42454,7 +42466,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" t="n">
+      <c r="A696" s="1" t="n">
         <v>694</v>
       </c>
       <c r="B696" t="n">
@@ -42514,7 +42526,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" t="n">
+      <c r="A697" s="1" t="n">
         <v>695</v>
       </c>
       <c r="B697" t="n">
@@ -42574,7 +42586,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" t="n">
+      <c r="A698" s="1" t="n">
         <v>696</v>
       </c>
       <c r="B698" t="n">
@@ -42634,7 +42646,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" t="n">
+      <c r="A699" s="1" t="n">
         <v>697</v>
       </c>
       <c r="B699" t="n">
@@ -42692,7 +42704,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" t="n">
+      <c r="A700" s="1" t="n">
         <v>698</v>
       </c>
       <c r="B700" t="n">
@@ -42756,7 +42768,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" t="n">
+      <c r="A701" s="1" t="n">
         <v>699</v>
       </c>
       <c r="B701" t="n">
@@ -42820,7 +42832,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" t="n">
+      <c r="A702" s="1" t="n">
         <v>700</v>
       </c>
       <c r="B702" t="n">
@@ -42884,7 +42896,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" t="n">
+      <c r="A703" s="1" t="n">
         <v>701</v>
       </c>
       <c r="B703" t="n">
@@ -42948,7 +42960,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" t="n">
+      <c r="A704" s="1" t="n">
         <v>702</v>
       </c>
       <c r="B704" t="n">
@@ -43008,7 +43020,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" t="n">
+      <c r="A705" s="1" t="n">
         <v>703</v>
       </c>
       <c r="B705" t="n">
@@ -43068,7 +43080,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" t="n">
+      <c r="A706" s="1" t="n">
         <v>704</v>
       </c>
       <c r="B706" t="n">
@@ -43128,7 +43140,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" t="n">
+      <c r="A707" s="1" t="n">
         <v>705</v>
       </c>
       <c r="B707" t="n">
@@ -43188,7 +43200,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" t="n">
+      <c r="A708" s="1" t="n">
         <v>706</v>
       </c>
       <c r="B708" t="n">
@@ -43248,7 +43260,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" t="n">
+      <c r="A709" s="1" t="n">
         <v>707</v>
       </c>
       <c r="B709" t="n">
@@ -43312,7 +43324,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" t="n">
+      <c r="A710" s="1" t="n">
         <v>708</v>
       </c>
       <c r="B710" t="n">
@@ -43372,7 +43384,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" t="n">
+      <c r="A711" s="1" t="n">
         <v>709</v>
       </c>
       <c r="B711" t="n">
@@ -43430,7 +43442,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" t="n">
+      <c r="A712" s="1" t="n">
         <v>710</v>
       </c>
       <c r="B712" t="n">
@@ -43494,7 +43506,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" t="n">
+      <c r="A713" s="1" t="n">
         <v>711</v>
       </c>
       <c r="B713" t="n">
@@ -43556,7 +43568,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" t="n">
+      <c r="A714" s="1" t="n">
         <v>712</v>
       </c>
       <c r="B714" t="n">
@@ -43620,7 +43632,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" t="n">
+      <c r="A715" s="1" t="n">
         <v>713</v>
       </c>
       <c r="B715" t="n">
@@ -43680,7 +43692,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" t="n">
+      <c r="A716" s="1" t="n">
         <v>714</v>
       </c>
       <c r="B716" t="n">
@@ -43740,7 +43752,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" t="n">
+      <c r="A717" s="1" t="n">
         <v>715</v>
       </c>
       <c r="B717" t="n">
@@ -43804,7 +43816,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" t="n">
+      <c r="A718" s="1" t="n">
         <v>716</v>
       </c>
       <c r="B718" t="n">
@@ -43868,7 +43880,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" t="n">
+      <c r="A719" s="1" t="n">
         <v>717</v>
       </c>
       <c r="B719" t="n">
@@ -43932,7 +43944,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" t="n">
+      <c r="A720" s="1" t="n">
         <v>718</v>
       </c>
       <c r="B720" t="n">
@@ -43990,7 +44002,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" t="n">
+      <c r="A721" s="1" t="n">
         <v>719</v>
       </c>
       <c r="B721" t="n">
@@ -44050,7 +44062,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" t="n">
+      <c r="A722" s="1" t="n">
         <v>720</v>
       </c>
       <c r="B722" t="n">
@@ -44110,7 +44122,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" t="n">
+      <c r="A723" s="1" t="n">
         <v>721</v>
       </c>
       <c r="B723" t="n">
@@ -44170,7 +44182,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" t="n">
+      <c r="A724" s="1" t="n">
         <v>722</v>
       </c>
       <c r="B724" t="n">
@@ -44230,7 +44242,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" t="n">
+      <c r="A725" s="1" t="n">
         <v>723</v>
       </c>
       <c r="B725" t="n">
@@ -44290,7 +44302,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" t="n">
+      <c r="A726" s="1" t="n">
         <v>724</v>
       </c>
       <c r="B726" t="n">
@@ -44354,7 +44366,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" t="n">
+      <c r="A727" s="1" t="n">
         <v>725</v>
       </c>
       <c r="B727" t="n">
@@ -44414,7 +44426,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" t="n">
+      <c r="A728" s="1" t="n">
         <v>726</v>
       </c>
       <c r="B728" t="n">
@@ -44474,7 +44486,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" t="n">
+      <c r="A729" s="1" t="n">
         <v>727</v>
       </c>
       <c r="B729" t="n">
@@ -44532,7 +44544,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" t="n">
+      <c r="A730" s="1" t="n">
         <v>728</v>
       </c>
       <c r="B730" t="n">
@@ -44592,7 +44604,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" t="n">
+      <c r="A731" s="1" t="n">
         <v>729</v>
       </c>
       <c r="B731" t="n">
@@ -44652,7 +44664,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" t="n">
+      <c r="A732" s="1" t="n">
         <v>730</v>
       </c>
       <c r="B732" t="n">
@@ -44716,7 +44728,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" t="n">
+      <c r="A733" s="1" t="n">
         <v>731</v>
       </c>
       <c r="B733" t="n">
@@ -44776,7 +44788,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" t="n">
+      <c r="A734" s="1" t="n">
         <v>732</v>
       </c>
       <c r="B734" t="n">
@@ -44834,7 +44846,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" t="n">
+      <c r="A735" s="1" t="n">
         <v>733</v>
       </c>
       <c r="B735" t="n">
@@ -44894,7 +44906,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" t="n">
+      <c r="A736" s="1" t="n">
         <v>734</v>
       </c>
       <c r="B736" t="n">
@@ -44954,7 +44966,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" t="n">
+      <c r="A737" s="1" t="n">
         <v>735</v>
       </c>
       <c r="B737" t="n">
@@ -45014,7 +45026,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" t="n">
+      <c r="A738" s="1" t="n">
         <v>736</v>
       </c>
       <c r="B738" t="n">
@@ -45074,7 +45086,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" t="n">
+      <c r="A739" s="1" t="n">
         <v>737</v>
       </c>
       <c r="B739" t="n">
@@ -45138,7 +45150,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" t="n">
+      <c r="A740" s="1" t="n">
         <v>738</v>
       </c>
       <c r="B740" t="n">
@@ -45196,7 +45208,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" t="n">
+      <c r="A741" s="1" t="n">
         <v>739</v>
       </c>
       <c r="B741" t="n">
@@ -45254,7 +45266,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" t="n">
+      <c r="A742" s="1" t="n">
         <v>740</v>
       </c>
       <c r="B742" t="n">
@@ -45316,7 +45328,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" t="n">
+      <c r="A743" s="1" t="n">
         <v>741</v>
       </c>
       <c r="B743" t="n">
@@ -45380,7 +45392,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" t="n">
+      <c r="A744" s="1" t="n">
         <v>742</v>
       </c>
       <c r="B744" t="n">
@@ -45444,7 +45456,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" t="n">
+      <c r="A745" s="1" t="n">
         <v>743</v>
       </c>
       <c r="B745" t="n">
@@ -45504,7 +45516,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" t="n">
+      <c r="A746" s="1" t="n">
         <v>744</v>
       </c>
       <c r="B746" t="n">
@@ -45564,7 +45576,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" t="n">
+      <c r="A747" s="1" t="n">
         <v>745</v>
       </c>
       <c r="B747" t="n">
@@ -45628,7 +45640,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" t="n">
+      <c r="A748" s="1" t="n">
         <v>746</v>
       </c>
       <c r="B748" t="n">
@@ -45688,7 +45700,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" t="n">
+      <c r="A749" s="1" t="n">
         <v>747</v>
       </c>
       <c r="B749" t="n">
@@ -45748,7 +45760,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" t="n">
+      <c r="A750" s="1" t="n">
         <v>748</v>
       </c>
       <c r="B750" t="n">
@@ -45812,7 +45824,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" t="n">
+      <c r="A751" s="1" t="n">
         <v>749</v>
       </c>
       <c r="B751" t="n">
@@ -45872,7 +45884,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" t="n">
+      <c r="A752" s="1" t="n">
         <v>750</v>
       </c>
       <c r="B752" t="n">
@@ -45932,7 +45944,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" t="n">
+      <c r="A753" s="1" t="n">
         <v>751</v>
       </c>
       <c r="B753" t="n">
@@ -45996,7 +46008,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" t="n">
+      <c r="A754" s="1" t="n">
         <v>752</v>
       </c>
       <c r="B754" t="n">
@@ -46056,7 +46068,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" t="n">
+      <c r="A755" s="1" t="n">
         <v>753</v>
       </c>
       <c r="B755" t="n">
@@ -46116,7 +46128,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" t="n">
+      <c r="A756" s="1" t="n">
         <v>754</v>
       </c>
       <c r="B756" t="n">
@@ -46176,7 +46188,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" t="n">
+      <c r="A757" s="1" t="n">
         <v>755</v>
       </c>
       <c r="B757" t="n">
@@ -46236,7 +46248,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" t="n">
+      <c r="A758" s="1" t="n">
         <v>756</v>
       </c>
       <c r="B758" t="n">
@@ -46296,7 +46308,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" t="n">
+      <c r="A759" s="1" t="n">
         <v>757</v>
       </c>
       <c r="B759" t="n">
@@ -46356,7 +46368,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" t="n">
+      <c r="A760" s="1" t="n">
         <v>758</v>
       </c>
       <c r="B760" t="n">
@@ -46416,7 +46428,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" t="n">
+      <c r="A761" s="1" t="n">
         <v>759</v>
       </c>
       <c r="B761" t="n">
@@ -46480,7 +46492,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" t="n">
+      <c r="A762" s="1" t="n">
         <v>760</v>
       </c>
       <c r="B762" t="n">
@@ -46538,7 +46550,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" t="n">
+      <c r="A763" s="1" t="n">
         <v>761</v>
       </c>
       <c r="B763" t="n">
@@ -46598,7 +46610,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" t="n">
+      <c r="A764" s="1" t="n">
         <v>762</v>
       </c>
       <c r="B764" t="n">
@@ -46658,7 +46670,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" t="n">
+      <c r="A765" s="1" t="n">
         <v>763</v>
       </c>
       <c r="B765" t="n">
@@ -46722,7 +46734,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" t="n">
+      <c r="A766" s="1" t="n">
         <v>764</v>
       </c>
       <c r="B766" t="n">
@@ -46782,7 +46794,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" t="n">
+      <c r="A767" s="1" t="n">
         <v>765</v>
       </c>
       <c r="B767" t="n">
@@ -46846,7 +46858,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" t="n">
+      <c r="A768" s="1" t="n">
         <v>766</v>
       </c>
       <c r="B768" t="n">
@@ -46904,7 +46916,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" t="n">
+      <c r="A769" s="1" t="n">
         <v>767</v>
       </c>
       <c r="B769" t="n">
@@ -46964,7 +46976,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" t="n">
+      <c r="A770" s="1" t="n">
         <v>768</v>
       </c>
       <c r="B770" t="n">
@@ -47022,7 +47034,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" t="n">
+      <c r="A771" s="1" t="n">
         <v>769</v>
       </c>
       <c r="B771" t="n">
@@ -47082,7 +47094,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" t="n">
+      <c r="A772" s="1" t="n">
         <v>770</v>
       </c>
       <c r="B772" t="n">
@@ -47142,7 +47154,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" t="n">
+      <c r="A773" s="1" t="n">
         <v>771</v>
       </c>
       <c r="B773" t="n">
@@ -47202,7 +47214,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" t="n">
+      <c r="A774" s="1" t="n">
         <v>772</v>
       </c>
       <c r="B774" t="n">
@@ -47266,7 +47278,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" t="n">
+      <c r="A775" s="1" t="n">
         <v>773</v>
       </c>
       <c r="B775" t="n">
@@ -47324,7 +47336,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" t="n">
+      <c r="A776" s="1" t="n">
         <v>774</v>
       </c>
       <c r="B776" t="n">
@@ -47384,7 +47396,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" t="n">
+      <c r="A777" s="1" t="n">
         <v>775</v>
       </c>
       <c r="B777" t="n">
@@ -47444,7 +47456,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" t="n">
+      <c r="A778" s="1" t="n">
         <v>776</v>
       </c>
       <c r="B778" t="n">
@@ -47506,7 +47518,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" t="n">
+      <c r="A779" s="1" t="n">
         <v>777</v>
       </c>
       <c r="B779" t="n">
@@ -47566,7 +47578,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" t="n">
+      <c r="A780" s="1" t="n">
         <v>778</v>
       </c>
       <c r="B780" t="n">
@@ -47624,7 +47636,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" t="n">
+      <c r="A781" s="1" t="n">
         <v>779</v>
       </c>
       <c r="B781" t="n">
@@ -47688,7 +47700,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" t="n">
+      <c r="A782" s="1" t="n">
         <v>780</v>
       </c>
       <c r="B782" t="n">
@@ -47748,7 +47760,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" t="n">
+      <c r="A783" s="1" t="n">
         <v>781</v>
       </c>
       <c r="B783" t="n">
@@ -47812,7 +47824,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" t="n">
+      <c r="A784" s="1" t="n">
         <v>782</v>
       </c>
       <c r="B784" t="n">
@@ -47876,7 +47888,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" t="n">
+      <c r="A785" s="1" t="n">
         <v>783</v>
       </c>
       <c r="B785" t="n">
@@ -47934,7 +47946,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" t="n">
+      <c r="A786" s="1" t="n">
         <v>784</v>
       </c>
       <c r="B786" t="n">
@@ -47994,7 +48006,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" t="n">
+      <c r="A787" s="1" t="n">
         <v>785</v>
       </c>
       <c r="B787" t="n">
@@ -48054,7 +48066,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" t="n">
+      <c r="A788" s="1" t="n">
         <v>786</v>
       </c>
       <c r="B788" t="n">
@@ -48114,7 +48126,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" t="n">
+      <c r="A789" s="1" t="n">
         <v>787</v>
       </c>
       <c r="B789" t="n">
@@ -48174,7 +48186,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" t="n">
+      <c r="A790" s="1" t="n">
         <v>788</v>
       </c>
       <c r="B790" t="n">
@@ -48234,7 +48246,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" t="n">
+      <c r="A791" s="1" t="n">
         <v>789</v>
       </c>
       <c r="B791" t="n">
@@ -48298,7 +48310,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" t="n">
+      <c r="A792" s="1" t="n">
         <v>790</v>
       </c>
       <c r="B792" t="n">
@@ -48356,7 +48368,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" t="n">
+      <c r="A793" s="1" t="n">
         <v>791</v>
       </c>
       <c r="B793" t="n">
@@ -48416,7 +48428,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" t="n">
+      <c r="A794" s="1" t="n">
         <v>792</v>
       </c>
       <c r="B794" t="n">
@@ -48474,7 +48486,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" t="n">
+      <c r="A795" s="1" t="n">
         <v>793</v>
       </c>
       <c r="B795" t="n">
@@ -48532,7 +48544,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" t="n">
+      <c r="A796" s="1" t="n">
         <v>794</v>
       </c>
       <c r="B796" t="n">
@@ -48592,7 +48604,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" t="n">
+      <c r="A797" s="1" t="n">
         <v>795</v>
       </c>
       <c r="B797" t="n">
@@ -48652,7 +48664,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" t="n">
+      <c r="A798" s="1" t="n">
         <v>796</v>
       </c>
       <c r="B798" t="n">
@@ -48716,7 +48728,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" t="n">
+      <c r="A799" s="1" t="n">
         <v>797</v>
       </c>
       <c r="B799" t="n">
@@ -48776,7 +48788,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" t="n">
+      <c r="A800" s="1" t="n">
         <v>798</v>
       </c>
       <c r="B800" t="n">
@@ -48836,7 +48848,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" t="n">
+      <c r="A801" s="1" t="n">
         <v>799</v>
       </c>
       <c r="B801" t="n">
@@ -48896,7 +48908,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" t="n">
+      <c r="A802" s="1" t="n">
         <v>800</v>
       </c>
       <c r="B802" t="n">
@@ -48956,7 +48968,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" t="n">
+      <c r="A803" s="1" t="n">
         <v>801</v>
       </c>
       <c r="B803" t="n">
@@ -49016,7 +49028,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" t="n">
+      <c r="A804" s="1" t="n">
         <v>802</v>
       </c>
       <c r="B804" t="n">
@@ -49080,7 +49092,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" t="n">
+      <c r="A805" s="1" t="n">
         <v>803</v>
       </c>
       <c r="B805" t="n">
@@ -49140,7 +49152,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" t="n">
+      <c r="A806" s="1" t="n">
         <v>804</v>
       </c>
       <c r="B806" t="n">
@@ -49200,7 +49212,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" t="n">
+      <c r="A807" s="1" t="n">
         <v>805</v>
       </c>
       <c r="B807" t="n">
@@ -49260,7 +49272,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" t="n">
+      <c r="A808" s="1" t="n">
         <v>806</v>
       </c>
       <c r="B808" t="n">
@@ -49324,7 +49336,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" t="n">
+      <c r="A809" s="1" t="n">
         <v>807</v>
       </c>
       <c r="B809" t="n">
@@ -49384,7 +49396,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" t="n">
+      <c r="A810" s="1" t="n">
         <v>808</v>
       </c>
       <c r="B810" t="n">
@@ -49444,7 +49456,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" t="n">
+      <c r="A811" s="1" t="n">
         <v>809</v>
       </c>
       <c r="B811" t="n">
@@ -49508,7 +49520,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" t="n">
+      <c r="A812" s="1" t="n">
         <v>810</v>
       </c>
       <c r="B812" t="n">
@@ -49568,7 +49580,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" t="n">
+      <c r="A813" s="1" t="n">
         <v>811</v>
       </c>
       <c r="B813" t="n">
@@ -49628,7 +49640,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" t="n">
+      <c r="A814" s="1" t="n">
         <v>812</v>
       </c>
       <c r="B814" t="n">
@@ -49688,7 +49700,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" t="n">
+      <c r="A815" s="1" t="n">
         <v>813</v>
       </c>
       <c r="B815" t="n">
@@ -49748,7 +49760,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" t="n">
+      <c r="A816" s="1" t="n">
         <v>814</v>
       </c>
       <c r="B816" t="n">
@@ -49808,7 +49820,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" t="n">
+      <c r="A817" s="1" t="n">
         <v>815</v>
       </c>
       <c r="B817" t="n">
@@ -49870,7 +49882,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" t="n">
+      <c r="A818" s="1" t="n">
         <v>816</v>
       </c>
       <c r="B818" t="n">
@@ -49930,7 +49942,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" t="n">
+      <c r="A819" s="1" t="n">
         <v>817</v>
       </c>
       <c r="B819" t="n">
@@ -49990,7 +50002,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" t="n">
+      <c r="A820" s="1" t="n">
         <v>818</v>
       </c>
       <c r="B820" t="n">
@@ -50050,7 +50062,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" t="n">
+      <c r="A821" s="1" t="n">
         <v>819</v>
       </c>
       <c r="B821" t="n">
@@ -50110,7 +50122,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" t="n">
+      <c r="A822" s="1" t="n">
         <v>820</v>
       </c>
       <c r="B822" t="n">
@@ -50174,7 +50186,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" t="n">
+      <c r="A823" s="1" t="n">
         <v>821</v>
       </c>
       <c r="B823" t="n">
@@ -50234,7 +50246,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" t="n">
+      <c r="A824" s="1" t="n">
         <v>822</v>
       </c>
       <c r="B824" t="n">
@@ -50294,7 +50306,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" t="n">
+      <c r="A825" s="1" t="n">
         <v>823</v>
       </c>
       <c r="B825" t="n">
@@ -50358,7 +50370,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" t="n">
+      <c r="A826" s="1" t="n">
         <v>824</v>
       </c>
       <c r="B826" t="n">
@@ -50418,7 +50430,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" t="n">
+      <c r="A827" s="1" t="n">
         <v>825</v>
       </c>
       <c r="B827" t="n">
@@ -50476,7 +50488,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" t="n">
+      <c r="A828" s="1" t="n">
         <v>826</v>
       </c>
       <c r="B828" t="n">
@@ -50534,7 +50546,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" t="n">
+      <c r="A829" s="1" t="n">
         <v>827</v>
       </c>
       <c r="B829" t="n">
@@ -50594,7 +50606,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" t="n">
+      <c r="A830" s="1" t="n">
         <v>828</v>
       </c>
       <c r="B830" t="n">
@@ -50652,7 +50664,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" t="n">
+      <c r="A831" s="1" t="n">
         <v>829</v>
       </c>
       <c r="B831" t="n">
@@ -50708,7 +50720,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" t="n">
+      <c r="A832" s="1" t="n">
         <v>830</v>
       </c>
       <c r="B832" t="n">
@@ -50768,7 +50780,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" t="n">
+      <c r="A833" s="1" t="n">
         <v>831</v>
       </c>
       <c r="B833" t="n">
@@ -50828,7 +50840,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" t="n">
+      <c r="A834" s="1" t="n">
         <v>832</v>
       </c>
       <c r="B834" t="n">
@@ -50886,7 +50898,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" t="n">
+      <c r="A835" s="1" t="n">
         <v>833</v>
       </c>
       <c r="B835" t="n">
@@ -50946,7 +50958,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" t="n">
+      <c r="A836" s="1" t="n">
         <v>834</v>
       </c>
       <c r="B836" t="n">
@@ -51006,7 +51018,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" t="n">
+      <c r="A837" s="1" t="n">
         <v>835</v>
       </c>
       <c r="B837" t="n">
@@ -51070,7 +51082,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" t="n">
+      <c r="A838" s="1" t="n">
         <v>836</v>
       </c>
       <c r="B838" t="n">
@@ -51130,7 +51142,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" t="n">
+      <c r="A839" s="1" t="n">
         <v>837</v>
       </c>
       <c r="B839" t="n">
@@ -51188,7 +51200,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" t="n">
+      <c r="A840" s="1" t="n">
         <v>838</v>
       </c>
       <c r="B840" t="n">
@@ -51248,7 +51260,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" t="n">
+      <c r="A841" s="1" t="n">
         <v>839</v>
       </c>
       <c r="B841" t="n">
@@ -51310,7 +51322,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" t="n">
+      <c r="A842" s="1" t="n">
         <v>840</v>
       </c>
       <c r="B842" t="n">
@@ -51370,7 +51382,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" t="n">
+      <c r="A843" s="1" t="n">
         <v>841</v>
       </c>
       <c r="B843" t="n">
@@ -51430,7 +51442,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" t="n">
+      <c r="A844" s="1" t="n">
         <v>842</v>
       </c>
       <c r="B844" t="n">
@@ -51490,7 +51502,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" t="n">
+      <c r="A845" s="1" t="n">
         <v>843</v>
       </c>
       <c r="B845" t="n">
@@ -51550,7 +51562,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" t="n">
+      <c r="A846" s="1" t="n">
         <v>844</v>
       </c>
       <c r="B846" t="n">
@@ -51610,7 +51622,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" t="n">
+      <c r="A847" s="1" t="n">
         <v>845</v>
       </c>
       <c r="B847" t="n">
@@ -51670,7 +51682,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" t="n">
+      <c r="A848" s="1" t="n">
         <v>846</v>
       </c>
       <c r="B848" t="n">
@@ -51728,7 +51740,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" t="n">
+      <c r="A849" s="1" t="n">
         <v>847</v>
       </c>
       <c r="B849" t="n">
@@ -51788,7 +51800,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" t="n">
+      <c r="A850" s="1" t="n">
         <v>848</v>
       </c>
       <c r="B850" t="n">
@@ -51848,7 +51860,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" t="n">
+      <c r="A851" s="1" t="n">
         <v>849</v>
       </c>
       <c r="B851" t="n">
@@ -51910,7 +51922,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" t="n">
+      <c r="A852" s="1" t="n">
         <v>850</v>
       </c>
       <c r="B852" t="n">
@@ -51970,7 +51982,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" t="n">
+      <c r="A853" s="1" t="n">
         <v>851</v>
       </c>
       <c r="B853" t="n">
@@ -52030,7 +52042,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" t="n">
+      <c r="A854" s="1" t="n">
         <v>852</v>
       </c>
       <c r="B854" t="n">
@@ -52090,7 +52102,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" t="n">
+      <c r="A855" s="1" t="n">
         <v>853</v>
       </c>
       <c r="B855" t="n">
@@ -52154,7 +52166,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" t="n">
+      <c r="A856" s="1" t="n">
         <v>854</v>
       </c>
       <c r="B856" t="n">
@@ -52214,7 +52226,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" t="n">
+      <c r="A857" s="1" t="n">
         <v>855</v>
       </c>
       <c r="B857" t="n">
@@ -52274,7 +52286,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" t="n">
+      <c r="A858" s="1" t="n">
         <v>856</v>
       </c>
       <c r="B858" t="n">
@@ -52334,7 +52346,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" t="n">
+      <c r="A859" s="1" t="n">
         <v>857</v>
       </c>
       <c r="B859" t="n">
@@ -52398,7 +52410,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" t="n">
+      <c r="A860" s="1" t="n">
         <v>858</v>
       </c>
       <c r="B860" t="n">
@@ -52458,7 +52470,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" t="n">
+      <c r="A861" s="1" t="n">
         <v>859</v>
       </c>
       <c r="B861" t="n">
@@ -52516,7 +52528,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" t="n">
+      <c r="A862" s="1" t="n">
         <v>860</v>
       </c>
       <c r="B862" t="n">
@@ -52576,7 +52588,7 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" t="n">
+      <c r="A863" s="1" t="n">
         <v>861</v>
       </c>
       <c r="B863" t="n">
@@ -52636,7 +52648,7 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" t="n">
+      <c r="A864" s="1" t="n">
         <v>862</v>
       </c>
       <c r="B864" t="n">
@@ -52700,7 +52712,7 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" t="n">
+      <c r="A865" s="1" t="n">
         <v>863</v>
       </c>
       <c r="B865" t="n">
@@ -52758,7 +52770,7 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" t="n">
+      <c r="A866" s="1" t="n">
         <v>864</v>
       </c>
       <c r="B866" t="n">
@@ -52818,7 +52830,7 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" t="n">
+      <c r="A867" s="1" t="n">
         <v>865</v>
       </c>
       <c r="B867" t="n">
@@ -52878,7 +52890,7 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" t="n">
+      <c r="A868" s="1" t="n">
         <v>866</v>
       </c>
       <c r="B868" t="n">
@@ -52938,7 +52950,7 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" t="n">
+      <c r="A869" s="1" t="n">
         <v>867</v>
       </c>
       <c r="B869" t="n">
@@ -53002,7 +53014,7 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" t="n">
+      <c r="A870" s="1" t="n">
         <v>868</v>
       </c>
       <c r="B870" t="n">
@@ -53060,7 +53072,7 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" t="n">
+      <c r="A871" s="1" t="n">
         <v>869</v>
       </c>
       <c r="B871" t="n">
@@ -53120,7 +53132,7 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" t="n">
+      <c r="A872" s="1" t="n">
         <v>870</v>
       </c>
       <c r="B872" t="n">
@@ -53180,7 +53192,7 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" t="n">
+      <c r="A873" s="1" t="n">
         <v>871</v>
       </c>
       <c r="B873" t="n">
@@ -53244,7 +53256,7 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" t="n">
+      <c r="A874" s="1" t="n">
         <v>872</v>
       </c>
       <c r="B874" t="n">
@@ -53308,7 +53320,7 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" t="n">
+      <c r="A875" s="1" t="n">
         <v>873</v>
       </c>
       <c r="B875" t="n">
@@ -53368,7 +53380,7 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" t="n">
+      <c r="A876" s="1" t="n">
         <v>874</v>
       </c>
       <c r="B876" t="n">
@@ -53428,7 +53440,7 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" t="n">
+      <c r="A877" s="1" t="n">
         <v>875</v>
       </c>
       <c r="B877" t="n">
@@ -53488,7 +53500,7 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" t="n">
+      <c r="A878" s="1" t="n">
         <v>876</v>
       </c>
       <c r="B878" t="n">
@@ -53548,7 +53560,7 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" t="n">
+      <c r="A879" s="1" t="n">
         <v>877</v>
       </c>
       <c r="B879" t="n">
@@ -53608,7 +53620,7 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" t="n">
+      <c r="A880" s="1" t="n">
         <v>878</v>
       </c>
       <c r="B880" t="n">
@@ -53666,7 +53678,7 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" t="n">
+      <c r="A881" s="1" t="n">
         <v>879</v>
       </c>
       <c r="B881" t="n">
@@ -53730,7 +53742,7 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" t="n">
+      <c r="A882" s="1" t="n">
         <v>880</v>
       </c>
       <c r="B882" t="n">
@@ -53790,7 +53802,7 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" t="n">
+      <c r="A883" s="1" t="n">
         <v>881</v>
       </c>
       <c r="B883" t="n">
@@ -53850,7 +53862,7 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" t="n">
+      <c r="A884" s="1" t="n">
         <v>882</v>
       </c>
       <c r="B884" t="n">
@@ -53910,7 +53922,7 @@
       </c>
     </row>
     <row r="885">
-      <c r="A885" t="n">
+      <c r="A885" s="1" t="n">
         <v>883</v>
       </c>
       <c r="B885" t="n">
@@ -53970,7 +53982,7 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" t="n">
+      <c r="A886" s="1" t="n">
         <v>884</v>
       </c>
       <c r="B886" t="n">
@@ -54030,7 +54042,7 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" t="n">
+      <c r="A887" s="1" t="n">
         <v>885</v>
       </c>
       <c r="B887" t="n">
@@ -54090,7 +54102,7 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" t="n">
+      <c r="A888" s="1" t="n">
         <v>886</v>
       </c>
       <c r="B888" t="n">
@@ -54150,7 +54162,7 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" t="n">
+      <c r="A889" s="1" t="n">
         <v>887</v>
       </c>
       <c r="B889" t="n">
@@ -54214,7 +54226,7 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" t="n">
+      <c r="A890" s="1" t="n">
         <v>888</v>
       </c>
       <c r="B890" t="n">
@@ -54272,7 +54284,7 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" t="n">
+      <c r="A891" s="1" t="n">
         <v>889</v>
       </c>
       <c r="B891" t="n">
@@ -54336,7 +54348,7 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" t="n">
+      <c r="A892" s="1" t="n">
         <v>890</v>
       </c>
       <c r="B892" t="n">

--- a/DataSets/tit.xlsx
+++ b/DataSets/tit.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,84 +417,84 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>survived</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>pclass</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>sex</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>age</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sibsp</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>parch</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>fare</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>embarked</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>class</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>who</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>adult_male</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>deck</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>embark_town</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>alive</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>alone</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="n">
@@ -566,7 +554,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="n">
@@ -630,7 +618,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="n">
@@ -690,7 +678,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="n">
@@ -754,7 +742,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="n">
@@ -814,7 +802,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="n">
@@ -872,7 +860,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="n">
@@ -936,7 +924,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="n">
@@ -996,7 +984,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="n">
@@ -1056,7 +1044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="n">
@@ -1116,7 +1104,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="n">
@@ -1180,7 +1168,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="n">
@@ -1244,7 +1232,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="n">
@@ -1304,7 +1292,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="n">
@@ -1364,7 +1352,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="n">
@@ -1424,7 +1412,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="n">
@@ -1484,7 +1472,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="n">
@@ -1544,7 +1532,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="n">
@@ -1602,7 +1590,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="n">
@@ -1662,7 +1650,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="n">
@@ -1720,7 +1708,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="n">
@@ -1780,7 +1768,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="n">
@@ -1844,7 +1832,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="n">
@@ -1904,7 +1892,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="n">
@@ -1968,7 +1956,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="n">
@@ -2028,7 +2016,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="n">
@@ -2088,7 +2076,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="n">
@@ -2146,7 +2134,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="n">
@@ -2210,7 +2198,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="n">
@@ -2268,7 +2256,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="n">
@@ -2326,7 +2314,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="n">
@@ -2386,7 +2374,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="n">
@@ -2448,7 +2436,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="n">
@@ -2506,7 +2494,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="n">
@@ -2566,7 +2554,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="n">
@@ -2626,7 +2614,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="n">
@@ -2686,7 +2674,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="n">
@@ -2744,7 +2732,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="n">
@@ -2804,7 +2792,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="n">
@@ -2864,7 +2852,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="n">
@@ -2924,7 +2912,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="n">
@@ -2984,7 +2972,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="n">
@@ -3044,7 +3032,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="n">
@@ -3102,7 +3090,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="n">
@@ -3162,7 +3150,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="n">
@@ -3222,7 +3210,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="n">
@@ -3280,7 +3268,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="n">
@@ -3338,7 +3326,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="n">
@@ -3396,7 +3384,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="n">
@@ -3454,7 +3442,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="n">
@@ -3514,7 +3502,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="n">
@@ -3574,7 +3562,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="n">
@@ -3634,7 +3622,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="n">
@@ -3698,7 +3686,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="n">
@@ -3758,7 +3746,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="n">
@@ -3822,7 +3810,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="n">
@@ -3884,7 +3872,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="n">
@@ -3944,7 +3932,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="n">
@@ -4004,7 +3992,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="n">
@@ -4064,7 +4052,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="n">
@@ -4124,7 +4112,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="n">
@@ -4184,7 +4172,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="n">
@@ -4240,7 +4228,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="n">
@@ -4304,7 +4292,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="n">
@@ -4364,7 +4352,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="n">
@@ -4422,7 +4410,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="n">
@@ -4480,7 +4468,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="n">
@@ -4544,7 +4532,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="n">
@@ -4604,7 +4592,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="n">
@@ -4664,7 +4652,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="n">
@@ -4724,7 +4712,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="n">
@@ -4784,7 +4772,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="n">
@@ -4844,7 +4832,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="n">
@@ -4904,7 +4892,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="n">
@@ -4964,7 +4952,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="n">
@@ -5024,7 +5012,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="n">
@@ -5088,7 +5076,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="n">
@@ -5146,7 +5134,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="n">
@@ -5204,7 +5192,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="n">
@@ -5264,7 +5252,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="n">
@@ -5324,7 +5312,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="n">
@@ -5384,7 +5372,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="n">
@@ -5444,7 +5432,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="n">
@@ -5502,7 +5490,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="n">
@@ -5562,7 +5550,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="n">
@@ -5622,7 +5610,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="n">
@@ -5682,7 +5670,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="n">
@@ -5742,7 +5730,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="n">
@@ -5800,7 +5788,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="n">
@@ -5864,7 +5852,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="n">
@@ -5924,7 +5912,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="n">
@@ -5984,7 +5972,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="n">
@@ -6044,7 +6032,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="n">
@@ -6108,7 +6096,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="n">
@@ -6168,7 +6156,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="n">
@@ -6228,7 +6216,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="n">
@@ -6286,7 +6274,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="n">
@@ -6350,7 +6338,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="n">
@@ -6414,7 +6402,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="n">
@@ -6474,7 +6462,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="n">
@@ -6534,7 +6522,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="n">
@@ -6594,7 +6582,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="n">
@@ -6652,7 +6640,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="n">
@@ -6716,7 +6704,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="n">
@@ -6776,7 +6764,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="n">
@@ -6836,7 +6824,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="n">
@@ -6896,7 +6884,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="n">
@@ -6956,7 +6944,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="n">
@@ -7014,7 +7002,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="n">
@@ -7074,7 +7062,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="n">
@@ -7132,7 +7120,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="n">
@@ -7196,7 +7184,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="n">
@@ -7256,7 +7244,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="n">
@@ -7316,7 +7304,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="n">
@@ -7376,7 +7364,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="n">
@@ -7436,7 +7424,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="n">
@@ -7496,7 +7484,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="n">
@@ -7556,7 +7544,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="n">
@@ -7616,7 +7604,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="n">
@@ -7680,7 +7668,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="n">
@@ -7740,7 +7728,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="n">
@@ -7800,7 +7788,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="n">
@@ -7858,7 +7846,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="n">
@@ -7918,7 +7906,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="n">
@@ -7982,7 +7970,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="n">
@@ -8046,7 +8034,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="n">
@@ -8106,7 +8094,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="n">
@@ -8164,7 +8152,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="n">
@@ -8224,7 +8212,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="n">
@@ -8286,7 +8274,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="n">
@@ -8346,7 +8334,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="n">
@@ -8406,7 +8394,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="n">
@@ -8466,7 +8454,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="n">
@@ -8526,7 +8514,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="n">
@@ -8586,7 +8574,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="n">
@@ -8646,7 +8634,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="n">
@@ -8706,7 +8694,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="n">
@@ -8770,7 +8758,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="n">
@@ -8834,7 +8822,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="n">
@@ -8894,7 +8882,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="n">
@@ -8958,7 +8946,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="n">
@@ -9016,7 +9004,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="n">
@@ -9076,7 +9064,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="n">
@@ -9136,7 +9124,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="n">
@@ -9196,7 +9184,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="n">
@@ -9256,7 +9244,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="n">
@@ -9316,7 +9304,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="n">
@@ -9376,7 +9364,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="n">
@@ -9436,7 +9424,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="n">
@@ -9500,7 +9488,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="n">
@@ -9560,7 +9548,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="n">
@@ -9620,7 +9608,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="n">
@@ -9684,7 +9672,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="n">
@@ -9744,7 +9732,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="n">
@@ -9804,7 +9792,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="n">
@@ -9862,7 +9850,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="n">
@@ -9922,7 +9910,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="n">
@@ -9982,7 +9970,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="n">
@@ -10042,7 +10030,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="n">
@@ -10100,7 +10088,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="n">
@@ -10158,7 +10146,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="n">
@@ -10218,7 +10206,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="n">
@@ -10278,7 +10266,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="n">
@@ -10338,7 +10326,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="n">
@@ -10398,7 +10386,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="n">
@@ -10458,7 +10446,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="n">
@@ -10518,7 +10506,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="n">
@@ -10580,7 +10568,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="n">
@@ -10640,7 +10628,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="n">
@@ -10698,7 +10686,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="n">
@@ -10758,7 +10746,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="n">
@@ -10822,7 +10810,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="n">
@@ -10882,7 +10870,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="n">
@@ -10942,7 +10930,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="n">
@@ -11002,7 +10990,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="n">
@@ -11066,7 +11054,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="n">
@@ -11126,7 +11114,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="n">
@@ -11184,7 +11172,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="n">
@@ -11248,7 +11236,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="n">
@@ -11308,7 +11296,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="n">
@@ -11368,7 +11356,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="n">
@@ -11426,7 +11414,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="n">
@@ -11484,7 +11472,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="n">
@@ -11544,7 +11532,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="n">
@@ -11608,7 +11596,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="n">
@@ -11668,7 +11656,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="n">
@@ -11730,7 +11718,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="n">
@@ -11788,7 +11776,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="n">
@@ -11848,7 +11836,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="n">
@@ -11908,7 +11896,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="n">
@@ -11968,7 +11956,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="n">
@@ -12028,7 +12016,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="n">
@@ -12088,7 +12076,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="n">
@@ -12148,7 +12136,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="n">
@@ -12212,7 +12200,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="n">
@@ -12276,7 +12264,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="n">
@@ -12340,7 +12328,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="n">
@@ -12398,7 +12386,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="n">
@@ -12458,7 +12446,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="n">
@@ -12516,7 +12504,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="n">
@@ -12576,7 +12564,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="n">
@@ -12636,7 +12624,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="n">
@@ -12694,7 +12682,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="n">
@@ -12754,7 +12742,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="n">
@@ -12814,7 +12802,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="n">
@@ -12874,7 +12862,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="n">
@@ -12938,7 +12926,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="n">
@@ -12998,7 +12986,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="n">
@@ -13058,7 +13046,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="n">
@@ -13118,7 +13106,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="n">
@@ -13182,7 +13170,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="n">
@@ -13242,7 +13230,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="n">
@@ -13302,7 +13290,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="n">
@@ -13362,7 +13350,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="n">
@@ -13422,7 +13410,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="n">
@@ -13480,7 +13468,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="n">
@@ -13544,7 +13532,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="n">
@@ -13604,7 +13592,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="n">
@@ -13664,7 +13652,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="n">
@@ -13728,7 +13716,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="n">
@@ -13788,7 +13776,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="n">
@@ -13848,7 +13836,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="n">
@@ -13908,7 +13896,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="n">
@@ -13968,7 +13956,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="n">
@@ -14026,7 +14014,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="n">
@@ -14090,7 +14078,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="n">
@@ -14150,7 +14138,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="n">
@@ -14210,7 +14198,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="n">
@@ -14270,7 +14258,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="n">
@@ -14330,7 +14318,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="n">
@@ -14388,7 +14376,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="n">
@@ -14452,7 +14440,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="n">
@@ -14512,7 +14500,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="n">
@@ -14572,7 +14560,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="n">
@@ -14632,7 +14620,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="n">
@@ -14692,7 +14680,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="n">
@@ -14750,7 +14738,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="n">
@@ -14810,7 +14798,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="n">
@@ -14870,7 +14858,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="n">
@@ -14930,7 +14918,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="n">
@@ -14990,7 +14978,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="n">
@@ -15048,7 +15036,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="n">
@@ -15106,7 +15094,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="n">
@@ -15166,7 +15154,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="n">
@@ -15226,7 +15214,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="n">
@@ -15286,7 +15274,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="n">
@@ -15350,7 +15338,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="n">
@@ -15410,7 +15398,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="n">
@@ -15470,7 +15458,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="n">
@@ -15534,7 +15522,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="n">
@@ -15594,7 +15582,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="n">
@@ -15652,7 +15640,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="n">
@@ -15716,7 +15704,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="n">
@@ -15780,7 +15768,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="n">
@@ -15840,7 +15828,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="n">
@@ -15900,7 +15888,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="n">
@@ -15960,7 +15948,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="n">
@@ -16018,7 +16006,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="n">
@@ -16082,7 +16070,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="n">
@@ -16142,7 +16130,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="n">
@@ -16202,7 +16190,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="n">
@@ -16260,7 +16248,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="n">
@@ -16320,7 +16308,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="n">
@@ -16384,7 +16372,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="n">
@@ -16448,7 +16436,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="n">
@@ -16506,7 +16494,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="n">
@@ -16566,7 +16554,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="n">
@@ -16626,7 +16614,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="n">
@@ -16686,7 +16674,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="n">
@@ -16750,7 +16738,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="n">
@@ -16814,7 +16802,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="n">
@@ -16872,7 +16860,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="n">
@@ -16932,7 +16920,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="n">
@@ -16992,7 +16980,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="n">
@@ -17056,7 +17044,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="n">
@@ -17114,7 +17102,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="n">
@@ -17178,7 +17166,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="n">
@@ -17238,7 +17226,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="n">
@@ -17296,7 +17284,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="n">
@@ -17356,7 +17344,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="n">
@@ -17416,7 +17404,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="n">
@@ -17476,7 +17464,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="n">
@@ -17536,7 +17524,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="n">
@@ -17596,7 +17584,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="n">
@@ -17656,7 +17644,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="n">
@@ -17718,7 +17706,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="n">
@@ -17778,7 +17766,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="n">
@@ -17838,7 +17826,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="n">
@@ -17898,7 +17886,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="n">
@@ -17958,7 +17946,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="n">
@@ -18018,7 +18006,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="n">
@@ -18078,7 +18066,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="n">
@@ -18142,7 +18130,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="n">
@@ -18206,7 +18194,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="n">
@@ -18266,7 +18254,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="n">
@@ -18326,7 +18314,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="n">
@@ -18384,7 +18372,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" t="n">
         <v>296</v>
       </c>
       <c r="B298" t="n">
@@ -18444,7 +18432,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" t="n">
         <v>297</v>
       </c>
       <c r="B299" t="n">
@@ -18508,7 +18496,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" t="n">
         <v>298</v>
       </c>
       <c r="B300" t="n">
@@ -18570,7 +18558,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" t="n">
         <v>299</v>
       </c>
       <c r="B301" t="n">
@@ -18634,7 +18622,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" t="n">
         <v>300</v>
       </c>
       <c r="B302" t="n">
@@ -18692,7 +18680,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" t="n">
         <v>301</v>
       </c>
       <c r="B303" t="n">
@@ -18750,7 +18738,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" t="n">
         <v>302</v>
       </c>
       <c r="B304" t="n">
@@ -18810,7 +18798,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" t="n">
         <v>303</v>
       </c>
       <c r="B305" t="n">
@@ -18872,7 +18860,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" t="n">
         <v>304</v>
       </c>
       <c r="B306" t="n">
@@ -18930,7 +18918,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" t="n">
         <v>305</v>
       </c>
       <c r="B307" t="n">
@@ -18994,7 +18982,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" t="n">
         <v>306</v>
       </c>
       <c r="B308" t="n">
@@ -19052,7 +19040,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" t="n">
         <v>307</v>
       </c>
       <c r="B309" t="n">
@@ -19116,7 +19104,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" t="n">
         <v>308</v>
       </c>
       <c r="B310" t="n">
@@ -19176,7 +19164,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" t="n">
         <v>309</v>
       </c>
       <c r="B311" t="n">
@@ -19240,7 +19228,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" t="n">
         <v>310</v>
       </c>
       <c r="B312" t="n">
@@ -19304,7 +19292,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" t="n">
         <v>311</v>
       </c>
       <c r="B313" t="n">
@@ -19368,7 +19356,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" t="n">
         <v>312</v>
       </c>
       <c r="B314" t="n">
@@ -19428,7 +19416,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" t="n">
         <v>313</v>
       </c>
       <c r="B315" t="n">
@@ -19488,7 +19476,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" t="n">
         <v>314</v>
       </c>
       <c r="B316" t="n">
@@ -19548,7 +19536,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" t="n">
         <v>315</v>
       </c>
       <c r="B317" t="n">
@@ -19608,7 +19596,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" t="n">
         <v>316</v>
       </c>
       <c r="B318" t="n">
@@ -19668,7 +19656,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" t="n">
         <v>317</v>
       </c>
       <c r="B319" t="n">
@@ -19728,7 +19716,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" t="n">
         <v>318</v>
       </c>
       <c r="B320" t="n">
@@ -19792,7 +19780,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" t="n">
         <v>319</v>
       </c>
       <c r="B321" t="n">
@@ -19856,7 +19844,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" t="n">
         <v>320</v>
       </c>
       <c r="B322" t="n">
@@ -19916,7 +19904,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" t="n">
         <v>321</v>
       </c>
       <c r="B323" t="n">
@@ -19976,7 +19964,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" t="n">
         <v>322</v>
       </c>
       <c r="B324" t="n">
@@ -20036,7 +20024,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" t="n">
         <v>323</v>
       </c>
       <c r="B325" t="n">
@@ -20096,7 +20084,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" t="n">
         <v>324</v>
       </c>
       <c r="B326" t="n">
@@ -20154,7 +20142,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" t="n">
         <v>325</v>
       </c>
       <c r="B327" t="n">
@@ -20218,7 +20206,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" t="n">
         <v>326</v>
       </c>
       <c r="B328" t="n">
@@ -20278,7 +20266,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" t="n">
         <v>327</v>
       </c>
       <c r="B329" t="n">
@@ -20342,7 +20330,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" t="n">
         <v>328</v>
       </c>
       <c r="B330" t="n">
@@ -20402,7 +20390,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" t="n">
         <v>329</v>
       </c>
       <c r="B331" t="n">
@@ -20466,7 +20454,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" t="n">
         <v>330</v>
       </c>
       <c r="B332" t="n">
@@ -20524,7 +20512,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" t="n">
         <v>331</v>
       </c>
       <c r="B333" t="n">
@@ -20588,7 +20576,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" t="n">
         <v>332</v>
       </c>
       <c r="B334" t="n">
@@ -20652,7 +20640,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" t="n">
         <v>333</v>
       </c>
       <c r="B335" t="n">
@@ -20712,7 +20700,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" t="n">
         <v>334</v>
       </c>
       <c r="B336" t="n">
@@ -20770,7 +20758,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" t="n">
         <v>335</v>
       </c>
       <c r="B337" t="n">
@@ -20828,7 +20816,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" t="n">
         <v>336</v>
       </c>
       <c r="B338" t="n">
@@ -20892,7 +20880,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" t="n">
         <v>337</v>
       </c>
       <c r="B339" t="n">
@@ -20956,7 +20944,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" t="n">
         <v>338</v>
       </c>
       <c r="B340" t="n">
@@ -21016,7 +21004,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" t="n">
         <v>339</v>
       </c>
       <c r="B341" t="n">
@@ -21076,7 +21064,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" t="n">
         <v>340</v>
       </c>
       <c r="B342" t="n">
@@ -21140,7 +21128,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" t="n">
         <v>341</v>
       </c>
       <c r="B343" t="n">
@@ -21204,7 +21192,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" t="n">
         <v>342</v>
       </c>
       <c r="B344" t="n">
@@ -21264,7 +21252,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" t="n">
         <v>343</v>
       </c>
       <c r="B345" t="n">
@@ -21324,7 +21312,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" t="n">
         <v>344</v>
       </c>
       <c r="B346" t="n">
@@ -21384,7 +21372,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" t="n">
         <v>345</v>
       </c>
       <c r="B347" t="n">
@@ -21448,7 +21436,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" t="n">
         <v>346</v>
       </c>
       <c r="B348" t="n">
@@ -21508,7 +21496,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" t="n">
         <v>347</v>
       </c>
       <c r="B349" t="n">
@@ -21566,7 +21554,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" t="n">
         <v>348</v>
       </c>
       <c r="B350" t="n">
@@ -21626,7 +21614,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" t="n">
         <v>349</v>
       </c>
       <c r="B351" t="n">
@@ -21686,7 +21674,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" t="n">
         <v>350</v>
       </c>
       <c r="B352" t="n">
@@ -21746,7 +21734,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" t="n">
         <v>351</v>
       </c>
       <c r="B353" t="n">
@@ -21808,7 +21796,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" t="n">
         <v>352</v>
       </c>
       <c r="B354" t="n">
@@ -21868,7 +21856,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" t="n">
         <v>353</v>
       </c>
       <c r="B355" t="n">
@@ -21928,7 +21916,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" t="n">
         <v>354</v>
       </c>
       <c r="B356" t="n">
@@ -21986,7 +21974,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" t="n">
         <v>355</v>
       </c>
       <c r="B357" t="n">
@@ -22046,7 +22034,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" t="n">
         <v>356</v>
       </c>
       <c r="B358" t="n">
@@ -22110,7 +22098,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" t="n">
         <v>357</v>
       </c>
       <c r="B359" t="n">
@@ -22170,7 +22158,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" t="n">
         <v>358</v>
       </c>
       <c r="B360" t="n">
@@ -22228,7 +22216,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" t="n">
         <v>359</v>
       </c>
       <c r="B361" t="n">
@@ -22286,7 +22274,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" t="n">
         <v>360</v>
       </c>
       <c r="B362" t="n">
@@ -22346,7 +22334,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" t="n">
         <v>361</v>
       </c>
       <c r="B363" t="n">
@@ -22406,7 +22394,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" t="n">
         <v>362</v>
       </c>
       <c r="B364" t="n">
@@ -22466,7 +22454,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" t="n">
         <v>363</v>
       </c>
       <c r="B365" t="n">
@@ -22526,7 +22514,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" t="n">
         <v>364</v>
       </c>
       <c r="B366" t="n">
@@ -22584,7 +22572,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" t="n">
         <v>365</v>
       </c>
       <c r="B367" t="n">
@@ -22644,7 +22632,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" t="n">
         <v>366</v>
       </c>
       <c r="B368" t="n">
@@ -22708,7 +22696,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" t="n">
         <v>367</v>
       </c>
       <c r="B369" t="n">
@@ -22766,7 +22754,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" t="n">
         <v>368</v>
       </c>
       <c r="B370" t="n">
@@ -22824,7 +22812,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" t="n">
         <v>369</v>
       </c>
       <c r="B371" t="n">
@@ -22888,7 +22876,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" t="n">
         <v>370</v>
       </c>
       <c r="B372" t="n">
@@ -22952,7 +22940,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" t="n">
         <v>371</v>
       </c>
       <c r="B373" t="n">
@@ -23012,7 +23000,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" t="n">
         <v>372</v>
       </c>
       <c r="B374" t="n">
@@ -23072,7 +23060,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" t="n">
         <v>373</v>
       </c>
       <c r="B375" t="n">
@@ -23132,7 +23120,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" t="n">
         <v>374</v>
       </c>
       <c r="B376" t="n">
@@ -23192,7 +23180,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" t="n">
         <v>375</v>
       </c>
       <c r="B377" t="n">
@@ -23250,7 +23238,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" t="n">
         <v>376</v>
       </c>
       <c r="B378" t="n">
@@ -23310,7 +23298,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" t="n">
         <v>377</v>
       </c>
       <c r="B379" t="n">
@@ -23374,7 +23362,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" t="n">
         <v>378</v>
       </c>
       <c r="B380" t="n">
@@ -23434,7 +23422,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" t="n">
         <v>379</v>
       </c>
       <c r="B381" t="n">
@@ -23494,7 +23482,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" t="n">
         <v>380</v>
       </c>
       <c r="B382" t="n">
@@ -23554,7 +23542,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" t="n">
         <v>381</v>
       </c>
       <c r="B383" t="n">
@@ -23614,7 +23602,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" t="n">
         <v>382</v>
       </c>
       <c r="B384" t="n">
@@ -23674,7 +23662,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" t="n">
         <v>383</v>
       </c>
       <c r="B385" t="n">
@@ -23734,7 +23722,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" t="n">
         <v>384</v>
       </c>
       <c r="B386" t="n">
@@ -23792,7 +23780,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" t="n">
         <v>385</v>
       </c>
       <c r="B387" t="n">
@@ -23852,7 +23840,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" t="n">
         <v>386</v>
       </c>
       <c r="B388" t="n">
@@ -23912,7 +23900,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" t="n">
         <v>387</v>
       </c>
       <c r="B389" t="n">
@@ -23972,7 +23960,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" t="n">
         <v>388</v>
       </c>
       <c r="B390" t="n">
@@ -24030,7 +24018,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" t="n">
         <v>389</v>
       </c>
       <c r="B391" t="n">
@@ -24090,7 +24078,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" t="n">
         <v>390</v>
       </c>
       <c r="B392" t="n">
@@ -24154,7 +24142,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" t="n">
         <v>391</v>
       </c>
       <c r="B393" t="n">
@@ -24214,7 +24202,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" t="n">
         <v>392</v>
       </c>
       <c r="B394" t="n">
@@ -24274,7 +24262,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" t="n">
         <v>393</v>
       </c>
       <c r="B395" t="n">
@@ -24338,7 +24326,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" t="n">
         <v>394</v>
       </c>
       <c r="B396" t="n">
@@ -24402,7 +24390,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" t="n">
         <v>395</v>
       </c>
       <c r="B397" t="n">
@@ -24462,7 +24450,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" t="n">
         <v>396</v>
       </c>
       <c r="B398" t="n">
@@ -24522,7 +24510,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" t="n">
         <v>397</v>
       </c>
       <c r="B399" t="n">
@@ -24582,7 +24570,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" t="n">
         <v>398</v>
       </c>
       <c r="B400" t="n">
@@ -24642,7 +24630,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" t="n">
         <v>399</v>
       </c>
       <c r="B401" t="n">
@@ -24702,7 +24690,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" t="n">
         <v>400</v>
       </c>
       <c r="B402" t="n">
@@ -24762,7 +24750,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" t="n">
         <v>401</v>
       </c>
       <c r="B403" t="n">
@@ -24822,7 +24810,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" t="n">
         <v>402</v>
       </c>
       <c r="B404" t="n">
@@ -24882,7 +24870,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" t="n">
         <v>403</v>
       </c>
       <c r="B405" t="n">
@@ -24942,7 +24930,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" t="n">
         <v>404</v>
       </c>
       <c r="B406" t="n">
@@ -25002,7 +24990,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" t="n">
         <v>405</v>
       </c>
       <c r="B407" t="n">
@@ -25062,7 +25050,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" t="n">
         <v>406</v>
       </c>
       <c r="B408" t="n">
@@ -25122,7 +25110,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" t="n">
         <v>407</v>
       </c>
       <c r="B409" t="n">
@@ -25182,7 +25170,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" t="n">
         <v>408</v>
       </c>
       <c r="B410" t="n">
@@ -25242,7 +25230,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" t="n">
         <v>409</v>
       </c>
       <c r="B411" t="n">
@@ -25300,7 +25288,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" t="n">
         <v>410</v>
       </c>
       <c r="B412" t="n">
@@ -25358,7 +25346,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" t="n">
         <v>411</v>
       </c>
       <c r="B413" t="n">
@@ -25416,7 +25404,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" t="n">
         <v>412</v>
       </c>
       <c r="B414" t="n">
@@ -25480,7 +25468,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" t="n">
         <v>413</v>
       </c>
       <c r="B415" t="n">
@@ -25538,7 +25526,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" t="n">
         <v>414</v>
       </c>
       <c r="B416" t="n">
@@ -25598,7 +25586,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" t="n">
         <v>415</v>
       </c>
       <c r="B417" t="n">
@@ -25656,7 +25644,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" t="n">
         <v>416</v>
       </c>
       <c r="B418" t="n">
@@ -25716,7 +25704,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" t="n">
         <v>417</v>
       </c>
       <c r="B419" t="n">
@@ -25776,7 +25764,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" t="n">
         <v>418</v>
       </c>
       <c r="B420" t="n">
@@ -25836,7 +25824,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" t="n">
         <v>419</v>
       </c>
       <c r="B421" t="n">
@@ -25896,7 +25884,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" t="n">
         <v>420</v>
       </c>
       <c r="B422" t="n">
@@ -25954,7 +25942,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" t="n">
         <v>421</v>
       </c>
       <c r="B423" t="n">
@@ -26014,7 +26002,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" t="n">
         <v>422</v>
       </c>
       <c r="B424" t="n">
@@ -26074,7 +26062,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" t="n">
         <v>423</v>
       </c>
       <c r="B425" t="n">
@@ -26134,7 +26122,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" t="n">
         <v>424</v>
       </c>
       <c r="B426" t="n">
@@ -26194,7 +26182,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" t="n">
         <v>425</v>
       </c>
       <c r="B427" t="n">
@@ -26252,7 +26240,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" t="n">
         <v>426</v>
       </c>
       <c r="B428" t="n">
@@ -26312,7 +26300,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" t="n">
         <v>427</v>
       </c>
       <c r="B429" t="n">
@@ -26372,7 +26360,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" t="n">
         <v>428</v>
       </c>
       <c r="B430" t="n">
@@ -26430,7 +26418,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" t="n">
         <v>429</v>
       </c>
       <c r="B431" t="n">
@@ -26494,7 +26482,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" t="n">
         <v>430</v>
       </c>
       <c r="B432" t="n">
@@ -26558,7 +26546,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" t="n">
         <v>431</v>
       </c>
       <c r="B433" t="n">
@@ -26616,7 +26604,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" t="n">
         <v>432</v>
       </c>
       <c r="B434" t="n">
@@ -26676,7 +26664,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" t="n">
         <v>433</v>
       </c>
       <c r="B435" t="n">
@@ -26736,7 +26724,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" t="n">
         <v>434</v>
       </c>
       <c r="B436" t="n">
@@ -26800,7 +26788,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" t="n">
         <v>435</v>
       </c>
       <c r="B437" t="n">
@@ -26864,7 +26852,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" t="n">
         <v>436</v>
       </c>
       <c r="B438" t="n">
@@ -26924,7 +26912,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" t="n">
         <v>437</v>
       </c>
       <c r="B439" t="n">
@@ -26984,7 +26972,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" t="n">
         <v>438</v>
       </c>
       <c r="B440" t="n">
@@ -27048,7 +27036,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" t="n">
         <v>439</v>
       </c>
       <c r="B441" t="n">
@@ -27108,7 +27096,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" t="n">
         <v>440</v>
       </c>
       <c r="B442" t="n">
@@ -27168,7 +27156,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" t="n">
         <v>441</v>
       </c>
       <c r="B443" t="n">
@@ -27228,7 +27216,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" t="n">
         <v>442</v>
       </c>
       <c r="B444" t="n">
@@ -27288,7 +27276,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" t="n">
         <v>443</v>
       </c>
       <c r="B445" t="n">
@@ -27348,7 +27336,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" t="n">
         <v>444</v>
       </c>
       <c r="B446" t="n">
@@ -27406,7 +27394,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" t="n">
         <v>445</v>
       </c>
       <c r="B447" t="n">
@@ -27470,7 +27458,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" t="n">
         <v>446</v>
       </c>
       <c r="B448" t="n">
@@ -27530,7 +27518,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" t="n">
         <v>447</v>
       </c>
       <c r="B449" t="n">
@@ -27590,7 +27578,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" t="n">
         <v>448</v>
       </c>
       <c r="B450" t="n">
@@ -27650,7 +27638,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" t="n">
         <v>449</v>
       </c>
       <c r="B451" t="n">
@@ -27714,7 +27702,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" t="n">
         <v>450</v>
       </c>
       <c r="B452" t="n">
@@ -27774,7 +27762,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" t="n">
         <v>451</v>
       </c>
       <c r="B453" t="n">
@@ -27832,7 +27820,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" t="n">
         <v>452</v>
       </c>
       <c r="B454" t="n">
@@ -27896,7 +27884,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" t="n">
         <v>453</v>
       </c>
       <c r="B455" t="n">
@@ -27960,7 +27948,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" t="n">
         <v>454</v>
       </c>
       <c r="B456" t="n">
@@ -28018,7 +28006,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" t="n">
         <v>455</v>
       </c>
       <c r="B457" t="n">
@@ -28078,7 +28066,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" t="n">
         <v>456</v>
       </c>
       <c r="B458" t="n">
@@ -28142,7 +28130,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" t="n">
         <v>457</v>
       </c>
       <c r="B459" t="n">
@@ -28204,7 +28192,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" t="n">
         <v>458</v>
       </c>
       <c r="B460" t="n">
@@ -28264,7 +28252,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" t="n">
         <v>459</v>
       </c>
       <c r="B461" t="n">
@@ -28322,7 +28310,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" t="n">
         <v>460</v>
       </c>
       <c r="B462" t="n">
@@ -28386,7 +28374,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" t="n">
         <v>461</v>
       </c>
       <c r="B463" t="n">
@@ -28446,7 +28434,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" t="n">
         <v>462</v>
       </c>
       <c r="B464" t="n">
@@ -28510,7 +28498,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" t="n">
         <v>463</v>
       </c>
       <c r="B465" t="n">
@@ -28570,7 +28558,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" t="n">
         <v>464</v>
       </c>
       <c r="B466" t="n">
@@ -28628,7 +28616,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" t="n">
         <v>465</v>
       </c>
       <c r="B467" t="n">
@@ -28688,7 +28676,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" t="n">
         <v>466</v>
       </c>
       <c r="B468" t="n">
@@ -28746,7 +28734,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" t="n">
         <v>467</v>
       </c>
       <c r="B469" t="n">
@@ -28806,7 +28794,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" t="n">
         <v>468</v>
       </c>
       <c r="B470" t="n">
@@ -28864,7 +28852,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" t="n">
         <v>469</v>
       </c>
       <c r="B471" t="n">
@@ -28924,7 +28912,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" t="n">
         <v>470</v>
       </c>
       <c r="B472" t="n">
@@ -28982,7 +28970,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" t="n">
         <v>471</v>
       </c>
       <c r="B473" t="n">
@@ -29042,7 +29030,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" t="n">
         <v>472</v>
       </c>
       <c r="B474" t="n">
@@ -29102,7 +29090,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" t="n">
         <v>473</v>
       </c>
       <c r="B475" t="n">
@@ -29166,7 +29154,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" t="n">
         <v>474</v>
       </c>
       <c r="B476" t="n">
@@ -29226,7 +29214,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" t="n">
         <v>475</v>
       </c>
       <c r="B477" t="n">
@@ -29288,7 +29276,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" t="n">
         <v>476</v>
       </c>
       <c r="B478" t="n">
@@ -29348,7 +29336,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" t="n">
         <v>477</v>
       </c>
       <c r="B479" t="n">
@@ -29408,7 +29396,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" t="n">
         <v>478</v>
       </c>
       <c r="B480" t="n">
@@ -29468,7 +29456,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" t="n">
         <v>479</v>
       </c>
       <c r="B481" t="n">
@@ -29528,7 +29516,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" t="n">
         <v>480</v>
       </c>
       <c r="B482" t="n">
@@ -29588,7 +29576,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" t="n">
         <v>481</v>
       </c>
       <c r="B483" t="n">
@@ -29646,7 +29634,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" t="n">
         <v>482</v>
       </c>
       <c r="B484" t="n">
@@ -29706,7 +29694,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" t="n">
         <v>483</v>
       </c>
       <c r="B485" t="n">
@@ -29766,7 +29754,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" t="n">
         <v>484</v>
       </c>
       <c r="B486" t="n">
@@ -29830,7 +29818,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" t="n">
         <v>485</v>
       </c>
       <c r="B487" t="n">
@@ -29888,7 +29876,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" t="n">
         <v>486</v>
       </c>
       <c r="B488" t="n">
@@ -29952,7 +29940,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" t="n">
         <v>487</v>
       </c>
       <c r="B489" t="n">
@@ -30016,7 +30004,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" t="n">
         <v>488</v>
       </c>
       <c r="B490" t="n">
@@ -30076,7 +30064,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" t="n">
         <v>489</v>
       </c>
       <c r="B491" t="n">
@@ -30136,7 +30124,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" t="n">
         <v>490</v>
       </c>
       <c r="B492" t="n">
@@ -30194,7 +30182,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" t="n">
         <v>491</v>
       </c>
       <c r="B493" t="n">
@@ -30254,7 +30242,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" t="n">
         <v>492</v>
       </c>
       <c r="B494" t="n">
@@ -30318,7 +30306,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" t="n">
         <v>493</v>
       </c>
       <c r="B495" t="n">
@@ -30378,7 +30366,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" t="n">
         <v>494</v>
       </c>
       <c r="B496" t="n">
@@ -30438,7 +30426,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" t="n">
         <v>495</v>
       </c>
       <c r="B497" t="n">
@@ -30496,7 +30484,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" t="n">
         <v>496</v>
       </c>
       <c r="B498" t="n">
@@ -30560,7 +30548,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" t="n">
         <v>497</v>
       </c>
       <c r="B499" t="n">
@@ -30618,7 +30606,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" t="n">
         <v>498</v>
       </c>
       <c r="B500" t="n">
@@ -30682,7 +30670,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" t="n">
         <v>499</v>
       </c>
       <c r="B501" t="n">
@@ -30742,7 +30730,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" t="n">
         <v>500</v>
       </c>
       <c r="B502" t="n">
@@ -30802,7 +30790,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" t="n">
         <v>501</v>
       </c>
       <c r="B503" t="n">
@@ -30862,7 +30850,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" t="n">
         <v>502</v>
       </c>
       <c r="B504" t="n">
@@ -30920,7 +30908,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" t="n">
         <v>503</v>
       </c>
       <c r="B505" t="n">
@@ -30980,7 +30968,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" t="n">
         <v>504</v>
       </c>
       <c r="B506" t="n">
@@ -31044,7 +31032,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" t="n">
         <v>505</v>
       </c>
       <c r="B507" t="n">
@@ -31108,7 +31096,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" t="n">
         <v>506</v>
       </c>
       <c r="B508" t="n">
@@ -31168,7 +31156,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" t="n">
         <v>507</v>
       </c>
       <c r="B509" t="n">
@@ -31226,7 +31214,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" t="n">
         <v>508</v>
       </c>
       <c r="B510" t="n">
@@ -31286,7 +31274,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" t="n">
         <v>509</v>
       </c>
       <c r="B511" t="n">
@@ -31346,7 +31334,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" t="n">
         <v>510</v>
       </c>
       <c r="B512" t="n">
@@ -31406,7 +31394,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" t="n">
         <v>511</v>
       </c>
       <c r="B513" t="n">
@@ -31464,7 +31452,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" t="n">
         <v>512</v>
       </c>
       <c r="B514" t="n">
@@ -31528,7 +31516,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" t="n">
         <v>513</v>
       </c>
       <c r="B515" t="n">
@@ -31588,7 +31576,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" t="n">
         <v>514</v>
       </c>
       <c r="B516" t="n">
@@ -31648,7 +31636,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" t="n">
         <v>515</v>
       </c>
       <c r="B517" t="n">
@@ -31712,7 +31700,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" t="n">
         <v>516</v>
       </c>
       <c r="B518" t="n">
@@ -31776,7 +31764,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" t="n">
         <v>517</v>
       </c>
       <c r="B519" t="n">
@@ -31834,7 +31822,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" t="n">
         <v>518</v>
       </c>
       <c r="B520" t="n">
@@ -31894,7 +31882,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" t="n">
         <v>519</v>
       </c>
       <c r="B521" t="n">
@@ -31954,7 +31942,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" t="n">
         <v>520</v>
       </c>
       <c r="B522" t="n">
@@ -32018,7 +32006,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" t="n">
         <v>521</v>
       </c>
       <c r="B523" t="n">
@@ -32078,7 +32066,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" t="n">
         <v>522</v>
       </c>
       <c r="B524" t="n">
@@ -32136,7 +32124,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" t="n">
         <v>523</v>
       </c>
       <c r="B525" t="n">
@@ -32200,7 +32188,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" t="n">
         <v>524</v>
       </c>
       <c r="B526" t="n">
@@ -32258,7 +32246,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" t="n">
         <v>525</v>
       </c>
       <c r="B527" t="n">
@@ -32318,7 +32306,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" t="n">
         <v>526</v>
       </c>
       <c r="B528" t="n">
@@ -32378,7 +32366,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" t="n">
         <v>527</v>
       </c>
       <c r="B529" t="n">
@@ -32440,7 +32428,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="1" t="n">
+      <c r="A530" t="n">
         <v>528</v>
       </c>
       <c r="B530" t="n">
@@ -32500,7 +32488,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="1" t="n">
+      <c r="A531" t="n">
         <v>529</v>
       </c>
       <c r="B531" t="n">
@@ -32560,7 +32548,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="1" t="n">
+      <c r="A532" t="n">
         <v>530</v>
       </c>
       <c r="B532" t="n">
@@ -32620,7 +32608,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="1" t="n">
+      <c r="A533" t="n">
         <v>531</v>
       </c>
       <c r="B533" t="n">
@@ -32678,7 +32666,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="1" t="n">
+      <c r="A534" t="n">
         <v>532</v>
       </c>
       <c r="B534" t="n">
@@ -32738,7 +32726,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="1" t="n">
+      <c r="A535" t="n">
         <v>533</v>
       </c>
       <c r="B535" t="n">
@@ -32796,7 +32784,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="1" t="n">
+      <c r="A536" t="n">
         <v>534</v>
       </c>
       <c r="B536" t="n">
@@ -32856,7 +32844,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="1" t="n">
+      <c r="A537" t="n">
         <v>535</v>
       </c>
       <c r="B537" t="n">
@@ -32916,7 +32904,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="1" t="n">
+      <c r="A538" t="n">
         <v>536</v>
       </c>
       <c r="B538" t="n">
@@ -32980,7 +32968,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="1" t="n">
+      <c r="A539" t="n">
         <v>537</v>
       </c>
       <c r="B539" t="n">
@@ -33040,7 +33028,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="1" t="n">
+      <c r="A540" t="n">
         <v>538</v>
       </c>
       <c r="B540" t="n">
@@ -33098,7 +33086,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="1" t="n">
+      <c r="A541" t="n">
         <v>539</v>
       </c>
       <c r="B541" t="n">
@@ -33162,7 +33150,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="1" t="n">
+      <c r="A542" t="n">
         <v>540</v>
       </c>
       <c r="B542" t="n">
@@ -33226,7 +33214,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="1" t="n">
+      <c r="A543" t="n">
         <v>541</v>
       </c>
       <c r="B543" t="n">
@@ -33286,7 +33274,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="1" t="n">
+      <c r="A544" t="n">
         <v>542</v>
       </c>
       <c r="B544" t="n">
@@ -33346,7 +33334,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="1" t="n">
+      <c r="A545" t="n">
         <v>543</v>
       </c>
       <c r="B545" t="n">
@@ -33406,7 +33394,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="1" t="n">
+      <c r="A546" t="n">
         <v>544</v>
       </c>
       <c r="B546" t="n">
@@ -33470,7 +33458,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="1" t="n">
+      <c r="A547" t="n">
         <v>545</v>
       </c>
       <c r="B547" t="n">
@@ -33530,7 +33518,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="1" t="n">
+      <c r="A548" t="n">
         <v>546</v>
       </c>
       <c r="B548" t="n">
@@ -33590,7 +33578,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="1" t="n">
+      <c r="A549" t="n">
         <v>547</v>
       </c>
       <c r="B549" t="n">
@@ -33648,7 +33636,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="1" t="n">
+      <c r="A550" t="n">
         <v>548</v>
       </c>
       <c r="B550" t="n">
@@ -33708,7 +33696,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="1" t="n">
+      <c r="A551" t="n">
         <v>549</v>
       </c>
       <c r="B551" t="n">
@@ -33768,7 +33756,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="1" t="n">
+      <c r="A552" t="n">
         <v>550</v>
       </c>
       <c r="B552" t="n">
@@ -33832,7 +33820,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="1" t="n">
+      <c r="A553" t="n">
         <v>551</v>
       </c>
       <c r="B553" t="n">
@@ -33892,7 +33880,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="1" t="n">
+      <c r="A554" t="n">
         <v>552</v>
       </c>
       <c r="B554" t="n">
@@ -33950,7 +33938,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="1" t="n">
+      <c r="A555" t="n">
         <v>553</v>
       </c>
       <c r="B555" t="n">
@@ -34010,7 +33998,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="1" t="n">
+      <c r="A556" t="n">
         <v>554</v>
       </c>
       <c r="B556" t="n">
@@ -34070,7 +34058,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="1" t="n">
+      <c r="A557" t="n">
         <v>555</v>
       </c>
       <c r="B557" t="n">
@@ -34130,7 +34118,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="1" t="n">
+      <c r="A558" t="n">
         <v>556</v>
       </c>
       <c r="B558" t="n">
@@ -34194,7 +34182,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="1" t="n">
+      <c r="A559" t="n">
         <v>557</v>
       </c>
       <c r="B559" t="n">
@@ -34252,7 +34240,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="1" t="n">
+      <c r="A560" t="n">
         <v>558</v>
       </c>
       <c r="B560" t="n">
@@ -34316,7 +34304,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="1" t="n">
+      <c r="A561" t="n">
         <v>559</v>
       </c>
       <c r="B561" t="n">
@@ -34376,7 +34364,7 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="1" t="n">
+      <c r="A562" t="n">
         <v>560</v>
       </c>
       <c r="B562" t="n">
@@ -34434,7 +34422,7 @@
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="1" t="n">
+      <c r="A563" t="n">
         <v>561</v>
       </c>
       <c r="B563" t="n">
@@ -34494,7 +34482,7 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="1" t="n">
+      <c r="A564" t="n">
         <v>562</v>
       </c>
       <c r="B564" t="n">
@@ -34554,7 +34542,7 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="1" t="n">
+      <c r="A565" t="n">
         <v>563</v>
       </c>
       <c r="B565" t="n">
@@ -34612,7 +34600,7 @@
       </c>
     </row>
     <row r="566">
-      <c r="A566" s="1" t="n">
+      <c r="A566" t="n">
         <v>564</v>
       </c>
       <c r="B566" t="n">
@@ -34670,7 +34658,7 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="1" t="n">
+      <c r="A567" t="n">
         <v>565</v>
       </c>
       <c r="B567" t="n">
@@ -34730,7 +34718,7 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="1" t="n">
+      <c r="A568" t="n">
         <v>566</v>
       </c>
       <c r="B568" t="n">
@@ -34790,7 +34778,7 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="1" t="n">
+      <c r="A569" t="n">
         <v>567</v>
       </c>
       <c r="B569" t="n">
@@ -34850,7 +34838,7 @@
       </c>
     </row>
     <row r="570">
-      <c r="A570" s="1" t="n">
+      <c r="A570" t="n">
         <v>568</v>
       </c>
       <c r="B570" t="n">
@@ -34908,7 +34896,7 @@
       </c>
     </row>
     <row r="571">
-      <c r="A571" s="1" t="n">
+      <c r="A571" t="n">
         <v>569</v>
       </c>
       <c r="B571" t="n">
@@ -34968,7 +34956,7 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="1" t="n">
+      <c r="A572" t="n">
         <v>570</v>
       </c>
       <c r="B572" t="n">
@@ -35028,7 +35016,7 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="1" t="n">
+      <c r="A573" t="n">
         <v>571</v>
       </c>
       <c r="B573" t="n">
@@ -35092,7 +35080,7 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" s="1" t="n">
+      <c r="A574" t="n">
         <v>572</v>
       </c>
       <c r="B574" t="n">
@@ -35156,7 +35144,7 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="1" t="n">
+      <c r="A575" t="n">
         <v>573</v>
       </c>
       <c r="B575" t="n">
@@ -35214,7 +35202,7 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="1" t="n">
+      <c r="A576" t="n">
         <v>574</v>
       </c>
       <c r="B576" t="n">
@@ -35274,7 +35262,7 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" s="1" t="n">
+      <c r="A577" t="n">
         <v>575</v>
       </c>
       <c r="B577" t="n">
@@ -35334,7 +35322,7 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="1" t="n">
+      <c r="A578" t="n">
         <v>576</v>
       </c>
       <c r="B578" t="n">
@@ -35394,7 +35382,7 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="1" t="n">
+      <c r="A579" t="n">
         <v>577</v>
       </c>
       <c r="B579" t="n">
@@ -35458,7 +35446,7 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" s="1" t="n">
+      <c r="A580" t="n">
         <v>578</v>
       </c>
       <c r="B580" t="n">
@@ -35516,7 +35504,7 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" s="1" t="n">
+      <c r="A581" t="n">
         <v>579</v>
       </c>
       <c r="B581" t="n">
@@ -35576,7 +35564,7 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="1" t="n">
+      <c r="A582" t="n">
         <v>580</v>
       </c>
       <c r="B582" t="n">
@@ -35636,7 +35624,7 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="1" t="n">
+      <c r="A583" t="n">
         <v>581</v>
       </c>
       <c r="B583" t="n">
@@ -35700,7 +35688,7 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="1" t="n">
+      <c r="A584" t="n">
         <v>582</v>
       </c>
       <c r="B584" t="n">
@@ -35760,7 +35748,7 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" s="1" t="n">
+      <c r="A585" t="n">
         <v>583</v>
       </c>
       <c r="B585" t="n">
@@ -35824,7 +35812,7 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" s="1" t="n">
+      <c r="A586" t="n">
         <v>584</v>
       </c>
       <c r="B586" t="n">
@@ -35882,7 +35870,7 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" s="1" t="n">
+      <c r="A587" t="n">
         <v>585</v>
       </c>
       <c r="B587" t="n">
@@ -35946,7 +35934,7 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" s="1" t="n">
+      <c r="A588" t="n">
         <v>586</v>
       </c>
       <c r="B588" t="n">
@@ -36006,7 +35994,7 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" s="1" t="n">
+      <c r="A589" t="n">
         <v>587</v>
       </c>
       <c r="B589" t="n">
@@ -36070,7 +36058,7 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="1" t="n">
+      <c r="A590" t="n">
         <v>588</v>
       </c>
       <c r="B590" t="n">
@@ -36130,7 +36118,7 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" s="1" t="n">
+      <c r="A591" t="n">
         <v>589</v>
       </c>
       <c r="B591" t="n">
@@ -36188,7 +36176,7 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="1" t="n">
+      <c r="A592" t="n">
         <v>590</v>
       </c>
       <c r="B592" t="n">
@@ -36248,7 +36236,7 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" s="1" t="n">
+      <c r="A593" t="n">
         <v>591</v>
       </c>
       <c r="B593" t="n">
@@ -36312,7 +36300,7 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="1" t="n">
+      <c r="A594" t="n">
         <v>592</v>
       </c>
       <c r="B594" t="n">
@@ -36372,7 +36360,7 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" s="1" t="n">
+      <c r="A595" t="n">
         <v>593</v>
       </c>
       <c r="B595" t="n">
@@ -36430,7 +36418,7 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="1" t="n">
+      <c r="A596" t="n">
         <v>594</v>
       </c>
       <c r="B596" t="n">
@@ -36490,7 +36478,7 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" s="1" t="n">
+      <c r="A597" t="n">
         <v>595</v>
       </c>
       <c r="B597" t="n">
@@ -36550,7 +36538,7 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="1" t="n">
+      <c r="A598" t="n">
         <v>596</v>
       </c>
       <c r="B598" t="n">
@@ -36608,7 +36596,7 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="1" t="n">
+      <c r="A599" t="n">
         <v>597</v>
       </c>
       <c r="B599" t="n">
@@ -36668,7 +36656,7 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" s="1" t="n">
+      <c r="A600" t="n">
         <v>598</v>
       </c>
       <c r="B600" t="n">
@@ -36726,7 +36714,7 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="1" t="n">
+      <c r="A601" t="n">
         <v>599</v>
       </c>
       <c r="B601" t="n">
@@ -36790,7 +36778,7 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="1" t="n">
+      <c r="A602" t="n">
         <v>600</v>
       </c>
       <c r="B602" t="n">
@@ -36850,7 +36838,7 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="1" t="n">
+      <c r="A603" t="n">
         <v>601</v>
       </c>
       <c r="B603" t="n">
@@ -36908,7 +36896,7 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="1" t="n">
+      <c r="A604" t="n">
         <v>602</v>
       </c>
       <c r="B604" t="n">
@@ -36966,7 +36954,7 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" s="1" t="n">
+      <c r="A605" t="n">
         <v>603</v>
       </c>
       <c r="B605" t="n">
@@ -37026,7 +37014,7 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="1" t="n">
+      <c r="A606" t="n">
         <v>604</v>
       </c>
       <c r="B606" t="n">
@@ -37086,7 +37074,7 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="1" t="n">
+      <c r="A607" t="n">
         <v>605</v>
       </c>
       <c r="B607" t="n">
@@ -37146,7 +37134,7 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" s="1" t="n">
+      <c r="A608" t="n">
         <v>606</v>
       </c>
       <c r="B608" t="n">
@@ -37206,7 +37194,7 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="1" t="n">
+      <c r="A609" t="n">
         <v>607</v>
       </c>
       <c r="B609" t="n">
@@ -37266,7 +37254,7 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" s="1" t="n">
+      <c r="A610" t="n">
         <v>608</v>
       </c>
       <c r="B610" t="n">
@@ -37326,7 +37314,7 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="1" t="n">
+      <c r="A611" t="n">
         <v>609</v>
       </c>
       <c r="B611" t="n">
@@ -37390,7 +37378,7 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" s="1" t="n">
+      <c r="A612" t="n">
         <v>610</v>
       </c>
       <c r="B612" t="n">
@@ -37450,7 +37438,7 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" s="1" t="n">
+      <c r="A613" t="n">
         <v>611</v>
       </c>
       <c r="B613" t="n">
@@ -37508,7 +37496,7 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="1" t="n">
+      <c r="A614" t="n">
         <v>612</v>
       </c>
       <c r="B614" t="n">
@@ -37566,7 +37554,7 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="1" t="n">
+      <c r="A615" t="n">
         <v>613</v>
       </c>
       <c r="B615" t="n">
@@ -37624,7 +37612,7 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="1" t="n">
+      <c r="A616" t="n">
         <v>614</v>
       </c>
       <c r="B616" t="n">
@@ -37684,7 +37672,7 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" s="1" t="n">
+      <c r="A617" t="n">
         <v>615</v>
       </c>
       <c r="B617" t="n">
@@ -37744,7 +37732,7 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" s="1" t="n">
+      <c r="A618" t="n">
         <v>616</v>
       </c>
       <c r="B618" t="n">
@@ -37804,7 +37792,7 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" s="1" t="n">
+      <c r="A619" t="n">
         <v>617</v>
       </c>
       <c r="B619" t="n">
@@ -37864,7 +37852,7 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" s="1" t="n">
+      <c r="A620" t="n">
         <v>618</v>
       </c>
       <c r="B620" t="n">
@@ -37928,7 +37916,7 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="1" t="n">
+      <c r="A621" t="n">
         <v>619</v>
       </c>
       <c r="B621" t="n">
@@ -37988,7 +37976,7 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="1" t="n">
+      <c r="A622" t="n">
         <v>620</v>
       </c>
       <c r="B622" t="n">
@@ -38048,7 +38036,7 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="1" t="n">
+      <c r="A623" t="n">
         <v>621</v>
       </c>
       <c r="B623" t="n">
@@ -38112,7 +38100,7 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="1" t="n">
+      <c r="A624" t="n">
         <v>622</v>
       </c>
       <c r="B624" t="n">
@@ -38172,7 +38160,7 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" s="1" t="n">
+      <c r="A625" t="n">
         <v>623</v>
       </c>
       <c r="B625" t="n">
@@ -38232,7 +38220,7 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="1" t="n">
+      <c r="A626" t="n">
         <v>624</v>
       </c>
       <c r="B626" t="n">
@@ -38292,7 +38280,7 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" s="1" t="n">
+      <c r="A627" t="n">
         <v>625</v>
       </c>
       <c r="B627" t="n">
@@ -38356,7 +38344,7 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" s="1" t="n">
+      <c r="A628" t="n">
         <v>626</v>
       </c>
       <c r="B628" t="n">
@@ -38416,7 +38404,7 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="1" t="n">
+      <c r="A629" t="n">
         <v>627</v>
       </c>
       <c r="B629" t="n">
@@ -38480,7 +38468,7 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="1" t="n">
+      <c r="A630" t="n">
         <v>628</v>
       </c>
       <c r="B630" t="n">
@@ -38540,7 +38528,7 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" s="1" t="n">
+      <c r="A631" t="n">
         <v>629</v>
       </c>
       <c r="B631" t="n">
@@ -38598,7 +38586,7 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="1" t="n">
+      <c r="A632" t="n">
         <v>630</v>
       </c>
       <c r="B632" t="n">
@@ -38662,7 +38650,7 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="1" t="n">
+      <c r="A633" t="n">
         <v>631</v>
       </c>
       <c r="B633" t="n">
@@ -38722,7 +38710,7 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" s="1" t="n">
+      <c r="A634" t="n">
         <v>632</v>
       </c>
       <c r="B634" t="n">
@@ -38786,7 +38774,7 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" s="1" t="n">
+      <c r="A635" t="n">
         <v>633</v>
       </c>
       <c r="B635" t="n">
@@ -38844,7 +38832,7 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" s="1" t="n">
+      <c r="A636" t="n">
         <v>634</v>
       </c>
       <c r="B636" t="n">
@@ -38904,7 +38892,7 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" s="1" t="n">
+      <c r="A637" t="n">
         <v>635</v>
       </c>
       <c r="B637" t="n">
@@ -38964,7 +38952,7 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" s="1" t="n">
+      <c r="A638" t="n">
         <v>636</v>
       </c>
       <c r="B638" t="n">
@@ -39024,7 +39012,7 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" s="1" t="n">
+      <c r="A639" t="n">
         <v>637</v>
       </c>
       <c r="B639" t="n">
@@ -39084,7 +39072,7 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="1" t="n">
+      <c r="A640" t="n">
         <v>638</v>
       </c>
       <c r="B640" t="n">
@@ -39144,7 +39132,7 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" s="1" t="n">
+      <c r="A641" t="n">
         <v>639</v>
       </c>
       <c r="B641" t="n">
@@ -39202,7 +39190,7 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" s="1" t="n">
+      <c r="A642" t="n">
         <v>640</v>
       </c>
       <c r="B642" t="n">
@@ -39262,7 +39250,7 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="1" t="n">
+      <c r="A643" t="n">
         <v>641</v>
       </c>
       <c r="B643" t="n">
@@ -39326,7 +39314,7 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" s="1" t="n">
+      <c r="A644" t="n">
         <v>642</v>
       </c>
       <c r="B644" t="n">
@@ -39386,7 +39374,7 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" s="1" t="n">
+      <c r="A645" t="n">
         <v>643</v>
       </c>
       <c r="B645" t="n">
@@ -39444,7 +39432,7 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="1" t="n">
+      <c r="A646" t="n">
         <v>644</v>
       </c>
       <c r="B646" t="n">
@@ -39504,7 +39492,7 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" s="1" t="n">
+      <c r="A647" t="n">
         <v>645</v>
       </c>
       <c r="B647" t="n">
@@ -39568,7 +39556,7 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="1" t="n">
+      <c r="A648" t="n">
         <v>646</v>
       </c>
       <c r="B648" t="n">
@@ -39628,7 +39616,7 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" s="1" t="n">
+      <c r="A649" t="n">
         <v>647</v>
       </c>
       <c r="B649" t="n">
@@ -39692,7 +39680,7 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" s="1" t="n">
+      <c r="A650" t="n">
         <v>648</v>
       </c>
       <c r="B650" t="n">
@@ -39750,7 +39738,7 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" s="1" t="n">
+      <c r="A651" t="n">
         <v>649</v>
       </c>
       <c r="B651" t="n">
@@ -39810,7 +39798,7 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" s="1" t="n">
+      <c r="A652" t="n">
         <v>650</v>
       </c>
       <c r="B652" t="n">
@@ -39868,7 +39856,7 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" s="1" t="n">
+      <c r="A653" t="n">
         <v>651</v>
       </c>
       <c r="B653" t="n">
@@ -39928,7 +39916,7 @@
       </c>
     </row>
     <row r="654">
-      <c r="A654" s="1" t="n">
+      <c r="A654" t="n">
         <v>652</v>
       </c>
       <c r="B654" t="n">
@@ -39988,7 +39976,7 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="1" t="n">
+      <c r="A655" t="n">
         <v>653</v>
       </c>
       <c r="B655" t="n">
@@ -40046,7 +40034,7 @@
       </c>
     </row>
     <row r="656">
-      <c r="A656" s="1" t="n">
+      <c r="A656" t="n">
         <v>654</v>
       </c>
       <c r="B656" t="n">
@@ -40106,7 +40094,7 @@
       </c>
     </row>
     <row r="657">
-      <c r="A657" s="1" t="n">
+      <c r="A657" t="n">
         <v>655</v>
       </c>
       <c r="B657" t="n">
@@ -40166,7 +40154,7 @@
       </c>
     </row>
     <row r="658">
-      <c r="A658" s="1" t="n">
+      <c r="A658" t="n">
         <v>656</v>
       </c>
       <c r="B658" t="n">
@@ -40224,7 +40212,7 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="1" t="n">
+      <c r="A659" t="n">
         <v>657</v>
       </c>
       <c r="B659" t="n">
@@ -40284,7 +40272,7 @@
       </c>
     </row>
     <row r="660">
-      <c r="A660" s="1" t="n">
+      <c r="A660" t="n">
         <v>658</v>
       </c>
       <c r="B660" t="n">
@@ -40344,7 +40332,7 @@
       </c>
     </row>
     <row r="661">
-      <c r="A661" s="1" t="n">
+      <c r="A661" t="n">
         <v>659</v>
       </c>
       <c r="B661" t="n">
@@ -40408,7 +40396,7 @@
       </c>
     </row>
     <row r="662">
-      <c r="A662" s="1" t="n">
+      <c r="A662" t="n">
         <v>660</v>
       </c>
       <c r="B662" t="n">
@@ -40468,7 +40456,7 @@
       </c>
     </row>
     <row r="663">
-      <c r="A663" s="1" t="n">
+      <c r="A663" t="n">
         <v>661</v>
       </c>
       <c r="B663" t="n">
@@ -40528,7 +40516,7 @@
       </c>
     </row>
     <row r="664">
-      <c r="A664" s="1" t="n">
+      <c r="A664" t="n">
         <v>662</v>
       </c>
       <c r="B664" t="n">
@@ -40592,7 +40580,7 @@
       </c>
     </row>
     <row r="665">
-      <c r="A665" s="1" t="n">
+      <c r="A665" t="n">
         <v>663</v>
       </c>
       <c r="B665" t="n">
@@ -40652,7 +40640,7 @@
       </c>
     </row>
     <row r="666">
-      <c r="A666" s="1" t="n">
+      <c r="A666" t="n">
         <v>664</v>
       </c>
       <c r="B666" t="n">
@@ -40712,7 +40700,7 @@
       </c>
     </row>
     <row r="667">
-      <c r="A667" s="1" t="n">
+      <c r="A667" t="n">
         <v>665</v>
       </c>
       <c r="B667" t="n">
@@ -40772,7 +40760,7 @@
       </c>
     </row>
     <row r="668">
-      <c r="A668" s="1" t="n">
+      <c r="A668" t="n">
         <v>666</v>
       </c>
       <c r="B668" t="n">
@@ -40832,7 +40820,7 @@
       </c>
     </row>
     <row r="669">
-      <c r="A669" s="1" t="n">
+      <c r="A669" t="n">
         <v>667</v>
       </c>
       <c r="B669" t="n">
@@ -40890,7 +40878,7 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" s="1" t="n">
+      <c r="A670" t="n">
         <v>668</v>
       </c>
       <c r="B670" t="n">
@@ -40950,7 +40938,7 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" s="1" t="n">
+      <c r="A671" t="n">
         <v>669</v>
       </c>
       <c r="B671" t="n">
@@ -41012,7 +41000,7 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" s="1" t="n">
+      <c r="A672" t="n">
         <v>670</v>
       </c>
       <c r="B672" t="n">
@@ -41072,7 +41060,7 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" s="1" t="n">
+      <c r="A673" t="n">
         <v>671</v>
       </c>
       <c r="B673" t="n">
@@ -41136,7 +41124,7 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" s="1" t="n">
+      <c r="A674" t="n">
         <v>672</v>
       </c>
       <c r="B674" t="n">
@@ -41196,7 +41184,7 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" s="1" t="n">
+      <c r="A675" t="n">
         <v>673</v>
       </c>
       <c r="B675" t="n">
@@ -41256,7 +41244,7 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" s="1" t="n">
+      <c r="A676" t="n">
         <v>674</v>
       </c>
       <c r="B676" t="n">
@@ -41314,7 +41302,7 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" s="1" t="n">
+      <c r="A677" t="n">
         <v>675</v>
       </c>
       <c r="B677" t="n">
@@ -41374,7 +41362,7 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" s="1" t="n">
+      <c r="A678" t="n">
         <v>676</v>
       </c>
       <c r="B678" t="n">
@@ -41434,7 +41422,7 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" s="1" t="n">
+      <c r="A679" t="n">
         <v>677</v>
       </c>
       <c r="B679" t="n">
@@ -41494,7 +41482,7 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" s="1" t="n">
+      <c r="A680" t="n">
         <v>678</v>
       </c>
       <c r="B680" t="n">
@@ -41554,7 +41542,7 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" s="1" t="n">
+      <c r="A681" t="n">
         <v>679</v>
       </c>
       <c r="B681" t="n">
@@ -41618,7 +41606,7 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" s="1" t="n">
+      <c r="A682" t="n">
         <v>680</v>
       </c>
       <c r="B682" t="n">
@@ -41676,7 +41664,7 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" s="1" t="n">
+      <c r="A683" t="n">
         <v>681</v>
       </c>
       <c r="B683" t="n">
@@ -41740,7 +41728,7 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" s="1" t="n">
+      <c r="A684" t="n">
         <v>682</v>
       </c>
       <c r="B684" t="n">
@@ -41800,7 +41788,7 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" s="1" t="n">
+      <c r="A685" t="n">
         <v>683</v>
       </c>
       <c r="B685" t="n">
@@ -41860,7 +41848,7 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" s="1" t="n">
+      <c r="A686" t="n">
         <v>684</v>
       </c>
       <c r="B686" t="n">
@@ -41920,7 +41908,7 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" s="1" t="n">
+      <c r="A687" t="n">
         <v>685</v>
       </c>
       <c r="B687" t="n">
@@ -41980,7 +41968,7 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" s="1" t="n">
+      <c r="A688" t="n">
         <v>686</v>
       </c>
       <c r="B688" t="n">
@@ -42040,7 +42028,7 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" s="1" t="n">
+      <c r="A689" t="n">
         <v>687</v>
       </c>
       <c r="B689" t="n">
@@ -42100,7 +42088,7 @@
       </c>
     </row>
     <row r="690">
-      <c r="A690" s="1" t="n">
+      <c r="A690" t="n">
         <v>688</v>
       </c>
       <c r="B690" t="n">
@@ -42160,7 +42148,7 @@
       </c>
     </row>
     <row r="691">
-      <c r="A691" s="1" t="n">
+      <c r="A691" t="n">
         <v>689</v>
       </c>
       <c r="B691" t="n">
@@ -42224,7 +42212,7 @@
       </c>
     </row>
     <row r="692">
-      <c r="A692" s="1" t="n">
+      <c r="A692" t="n">
         <v>690</v>
       </c>
       <c r="B692" t="n">
@@ -42288,7 +42276,7 @@
       </c>
     </row>
     <row r="693">
-      <c r="A693" s="1" t="n">
+      <c r="A693" t="n">
         <v>691</v>
       </c>
       <c r="B693" t="n">
@@ -42348,7 +42336,7 @@
       </c>
     </row>
     <row r="694">
-      <c r="A694" s="1" t="n">
+      <c r="A694" t="n">
         <v>692</v>
       </c>
       <c r="B694" t="n">
@@ -42406,7 +42394,7 @@
       </c>
     </row>
     <row r="695">
-      <c r="A695" s="1" t="n">
+      <c r="A695" t="n">
         <v>693</v>
       </c>
       <c r="B695" t="n">
@@ -42466,7 +42454,7 @@
       </c>
     </row>
     <row r="696">
-      <c r="A696" s="1" t="n">
+      <c r="A696" t="n">
         <v>694</v>
       </c>
       <c r="B696" t="n">
@@ -42526,7 +42514,7 @@
       </c>
     </row>
     <row r="697">
-      <c r="A697" s="1" t="n">
+      <c r="A697" t="n">
         <v>695</v>
       </c>
       <c r="B697" t="n">
@@ -42586,7 +42574,7 @@
       </c>
     </row>
     <row r="698">
-      <c r="A698" s="1" t="n">
+      <c r="A698" t="n">
         <v>696</v>
       </c>
       <c r="B698" t="n">
@@ -42646,7 +42634,7 @@
       </c>
     </row>
     <row r="699">
-      <c r="A699" s="1" t="n">
+      <c r="A699" t="n">
         <v>697</v>
       </c>
       <c r="B699" t="n">
@@ -42704,7 +42692,7 @@
       </c>
     </row>
     <row r="700">
-      <c r="A700" s="1" t="n">
+      <c r="A700" t="n">
         <v>698</v>
       </c>
       <c r="B700" t="n">
@@ -42768,7 +42756,7 @@
       </c>
     </row>
     <row r="701">
-      <c r="A701" s="1" t="n">
+      <c r="A701" t="n">
         <v>699</v>
       </c>
       <c r="B701" t="n">
@@ -42832,7 +42820,7 @@
       </c>
     </row>
     <row r="702">
-      <c r="A702" s="1" t="n">
+      <c r="A702" t="n">
         <v>700</v>
       </c>
       <c r="B702" t="n">
@@ -42896,7 +42884,7 @@
       </c>
     </row>
     <row r="703">
-      <c r="A703" s="1" t="n">
+      <c r="A703" t="n">
         <v>701</v>
       </c>
       <c r="B703" t="n">
@@ -42960,7 +42948,7 @@
       </c>
     </row>
     <row r="704">
-      <c r="A704" s="1" t="n">
+      <c r="A704" t="n">
         <v>702</v>
       </c>
       <c r="B704" t="n">
@@ -43020,7 +43008,7 @@
       </c>
     </row>
     <row r="705">
-      <c r="A705" s="1" t="n">
+      <c r="A705" t="n">
         <v>703</v>
       </c>
       <c r="B705" t="n">
@@ -43080,7 +43068,7 @@
       </c>
     </row>
     <row r="706">
-      <c r="A706" s="1" t="n">
+      <c r="A706" t="n">
         <v>704</v>
       </c>
       <c r="B706" t="n">
@@ -43140,7 +43128,7 @@
       </c>
     </row>
     <row r="707">
-      <c r="A707" s="1" t="n">
+      <c r="A707" t="n">
         <v>705</v>
       </c>
       <c r="B707" t="n">
@@ -43200,7 +43188,7 @@
       </c>
     </row>
     <row r="708">
-      <c r="A708" s="1" t="n">
+      <c r="A708" t="n">
         <v>706</v>
       </c>
       <c r="B708" t="n">
@@ -43260,7 +43248,7 @@
       </c>
     </row>
     <row r="709">
-      <c r="A709" s="1" t="n">
+      <c r="A709" t="n">
         <v>707</v>
       </c>
       <c r="B709" t="n">
@@ -43324,7 +43312,7 @@
       </c>
     </row>
     <row r="710">
-      <c r="A710" s="1" t="n">
+      <c r="A710" t="n">
         <v>708</v>
       </c>
       <c r="B710" t="n">
@@ -43384,7 +43372,7 @@
       </c>
     </row>
     <row r="711">
-      <c r="A711" s="1" t="n">
+      <c r="A711" t="n">
         <v>709</v>
       </c>
       <c r="B711" t="n">
@@ -43442,7 +43430,7 @@
       </c>
     </row>
     <row r="712">
-      <c r="A712" s="1" t="n">
+      <c r="A712" t="n">
         <v>710</v>
       </c>
       <c r="B712" t="n">
@@ -43506,7 +43494,7 @@
       </c>
     </row>
     <row r="713">
-      <c r="A713" s="1" t="n">
+      <c r="A713" t="n">
         <v>711</v>
       </c>
       <c r="B713" t="n">
@@ -43568,7 +43556,7 @@
       </c>
     </row>
     <row r="714">
-      <c r="A714" s="1" t="n">
+      <c r="A714" t="n">
         <v>712</v>
       </c>
       <c r="B714" t="n">
@@ -43632,7 +43620,7 @@
       </c>
     </row>
     <row r="715">
-      <c r="A715" s="1" t="n">
+      <c r="A715" t="n">
         <v>713</v>
       </c>
       <c r="B715" t="n">
@@ -43692,7 +43680,7 @@
       </c>
     </row>
     <row r="716">
-      <c r="A716" s="1" t="n">
+      <c r="A716" t="n">
         <v>714</v>
       </c>
       <c r="B716" t="n">
@@ -43752,7 +43740,7 @@
       </c>
     </row>
     <row r="717">
-      <c r="A717" s="1" t="n">
+      <c r="A717" t="n">
         <v>715</v>
       </c>
       <c r="B717" t="n">
@@ -43816,7 +43804,7 @@
       </c>
     </row>
     <row r="718">
-      <c r="A718" s="1" t="n">
+      <c r="A718" t="n">
         <v>716</v>
       </c>
       <c r="B718" t="n">
@@ -43880,7 +43868,7 @@
       </c>
     </row>
     <row r="719">
-      <c r="A719" s="1" t="n">
+      <c r="A719" t="n">
         <v>717</v>
       </c>
       <c r="B719" t="n">
@@ -43944,7 +43932,7 @@
       </c>
     </row>
     <row r="720">
-      <c r="A720" s="1" t="n">
+      <c r="A720" t="n">
         <v>718</v>
       </c>
       <c r="B720" t="n">
@@ -44002,7 +43990,7 @@
       </c>
     </row>
     <row r="721">
-      <c r="A721" s="1" t="n">
+      <c r="A721" t="n">
         <v>719</v>
       </c>
       <c r="B721" t="n">
@@ -44062,7 +44050,7 @@
       </c>
     </row>
     <row r="722">
-      <c r="A722" s="1" t="n">
+      <c r="A722" t="n">
         <v>720</v>
       </c>
       <c r="B722" t="n">
@@ -44122,7 +44110,7 @@
       </c>
     </row>
     <row r="723">
-      <c r="A723" s="1" t="n">
+      <c r="A723" t="n">
         <v>721</v>
       </c>
       <c r="B723" t="n">
@@ -44182,7 +44170,7 @@
       </c>
     </row>
     <row r="724">
-      <c r="A724" s="1" t="n">
+      <c r="A724" t="n">
         <v>722</v>
       </c>
       <c r="B724" t="n">
@@ -44242,7 +44230,7 @@
       </c>
     </row>
     <row r="725">
-      <c r="A725" s="1" t="n">
+      <c r="A725" t="n">
         <v>723</v>
       </c>
       <c r="B725" t="n">
@@ -44302,7 +44290,7 @@
       </c>
     </row>
     <row r="726">
-      <c r="A726" s="1" t="n">
+      <c r="A726" t="n">
         <v>724</v>
       </c>
       <c r="B726" t="n">
@@ -44366,7 +44354,7 @@
       </c>
     </row>
     <row r="727">
-      <c r="A727" s="1" t="n">
+      <c r="A727" t="n">
         <v>725</v>
       </c>
       <c r="B727" t="n">
@@ -44426,7 +44414,7 @@
       </c>
     </row>
     <row r="728">
-      <c r="A728" s="1" t="n">
+      <c r="A728" t="n">
         <v>726</v>
       </c>
       <c r="B728" t="n">
@@ -44486,7 +44474,7 @@
       </c>
     </row>
     <row r="729">
-      <c r="A729" s="1" t="n">
+      <c r="A729" t="n">
         <v>727</v>
       </c>
       <c r="B729" t="n">
@@ -44544,7 +44532,7 @@
       </c>
     </row>
     <row r="730">
-      <c r="A730" s="1" t="n">
+      <c r="A730" t="n">
         <v>728</v>
       </c>
       <c r="B730" t="n">
@@ -44604,7 +44592,7 @@
       </c>
     </row>
     <row r="731">
-      <c r="A731" s="1" t="n">
+      <c r="A731" t="n">
         <v>729</v>
       </c>
       <c r="B731" t="n">
@@ -44664,7 +44652,7 @@
       </c>
     </row>
     <row r="732">
-      <c r="A732" s="1" t="n">
+      <c r="A732" t="n">
         <v>730</v>
       </c>
       <c r="B732" t="n">
@@ -44728,7 +44716,7 @@
       </c>
     </row>
     <row r="733">
-      <c r="A733" s="1" t="n">
+      <c r="A733" t="n">
         <v>731</v>
       </c>
       <c r="B733" t="n">
@@ -44788,7 +44776,7 @@
       </c>
     </row>
     <row r="734">
-      <c r="A734" s="1" t="n">
+      <c r="A734" t="n">
         <v>732</v>
       </c>
       <c r="B734" t="n">
@@ -44846,7 +44834,7 @@
       </c>
     </row>
     <row r="735">
-      <c r="A735" s="1" t="n">
+      <c r="A735" t="n">
         <v>733</v>
       </c>
       <c r="B735" t="n">
@@ -44906,7 +44894,7 @@
       </c>
     </row>
     <row r="736">
-      <c r="A736" s="1" t="n">
+      <c r="A736" t="n">
         <v>734</v>
       </c>
       <c r="B736" t="n">
@@ -44966,7 +44954,7 @@
       </c>
     </row>
     <row r="737">
-      <c r="A737" s="1" t="n">
+      <c r="A737" t="n">
         <v>735</v>
       </c>
       <c r="B737" t="n">
@@ -45026,7 +45014,7 @@
       </c>
     </row>
     <row r="738">
-      <c r="A738" s="1" t="n">
+      <c r="A738" t="n">
         <v>736</v>
       </c>
       <c r="B738" t="n">
@@ -45086,7 +45074,7 @@
       </c>
     </row>
     <row r="739">
-      <c r="A739" s="1" t="n">
+      <c r="A739" t="n">
         <v>737</v>
       </c>
       <c r="B739" t="n">
@@ -45150,7 +45138,7 @@
       </c>
     </row>
     <row r="740">
-      <c r="A740" s="1" t="n">
+      <c r="A740" t="n">
         <v>738</v>
       </c>
       <c r="B740" t="n">
@@ -45208,7 +45196,7 @@
       </c>
     </row>
     <row r="741">
-      <c r="A741" s="1" t="n">
+      <c r="A741" t="n">
         <v>739</v>
       </c>
       <c r="B741" t="n">
@@ -45266,7 +45254,7 @@
       </c>
     </row>
     <row r="742">
-      <c r="A742" s="1" t="n">
+      <c r="A742" t="n">
         <v>740</v>
       </c>
       <c r="B742" t="n">
@@ -45328,7 +45316,7 @@
       </c>
     </row>
     <row r="743">
-      <c r="A743" s="1" t="n">
+      <c r="A743" t="n">
         <v>741</v>
       </c>
       <c r="B743" t="n">
@@ -45392,7 +45380,7 @@
       </c>
     </row>
     <row r="744">
-      <c r="A744" s="1" t="n">
+      <c r="A744" t="n">
         <v>742</v>
       </c>
       <c r="B744" t="n">
@@ -45456,7 +45444,7 @@
       </c>
     </row>
     <row r="745">
-      <c r="A745" s="1" t="n">
+      <c r="A745" t="n">
         <v>743</v>
       </c>
       <c r="B745" t="n">
@@ -45516,7 +45504,7 @@
       </c>
     </row>
     <row r="746">
-      <c r="A746" s="1" t="n">
+      <c r="A746" t="n">
         <v>744</v>
       </c>
       <c r="B746" t="n">
@@ -45576,7 +45564,7 @@
       </c>
     </row>
     <row r="747">
-      <c r="A747" s="1" t="n">
+      <c r="A747" t="n">
         <v>745</v>
       </c>
       <c r="B747" t="n">
@@ -45640,7 +45628,7 @@
       </c>
     </row>
     <row r="748">
-      <c r="A748" s="1" t="n">
+      <c r="A748" t="n">
         <v>746</v>
       </c>
       <c r="B748" t="n">
@@ -45700,7 +45688,7 @@
       </c>
     </row>
     <row r="749">
-      <c r="A749" s="1" t="n">
+      <c r="A749" t="n">
         <v>747</v>
       </c>
       <c r="B749" t="n">
@@ -45760,7 +45748,7 @@
       </c>
     </row>
     <row r="750">
-      <c r="A750" s="1" t="n">
+      <c r="A750" t="n">
         <v>748</v>
       </c>
       <c r="B750" t="n">
@@ -45824,7 +45812,7 @@
       </c>
     </row>
     <row r="751">
-      <c r="A751" s="1" t="n">
+      <c r="A751" t="n">
         <v>749</v>
       </c>
       <c r="B751" t="n">
@@ -45884,7 +45872,7 @@
       </c>
     </row>
     <row r="752">
-      <c r="A752" s="1" t="n">
+      <c r="A752" t="n">
         <v>750</v>
       </c>
       <c r="B752" t="n">
@@ -45944,7 +45932,7 @@
       </c>
     </row>
     <row r="753">
-      <c r="A753" s="1" t="n">
+      <c r="A753" t="n">
         <v>751</v>
       </c>
       <c r="B753" t="n">
@@ -46008,7 +45996,7 @@
       </c>
     </row>
     <row r="754">
-      <c r="A754" s="1" t="n">
+      <c r="A754" t="n">
         <v>752</v>
       </c>
       <c r="B754" t="n">
@@ -46068,7 +46056,7 @@
       </c>
     </row>
     <row r="755">
-      <c r="A755" s="1" t="n">
+      <c r="A755" t="n">
         <v>753</v>
       </c>
       <c r="B755" t="n">
@@ -46128,7 +46116,7 @@
       </c>
     </row>
     <row r="756">
-      <c r="A756" s="1" t="n">
+      <c r="A756" t="n">
         <v>754</v>
       </c>
       <c r="B756" t="n">
@@ -46188,7 +46176,7 @@
       </c>
     </row>
     <row r="757">
-      <c r="A757" s="1" t="n">
+      <c r="A757" t="n">
         <v>755</v>
       </c>
       <c r="B757" t="n">
@@ -46248,7 +46236,7 @@
       </c>
     </row>
     <row r="758">
-      <c r="A758" s="1" t="n">
+      <c r="A758" t="n">
         <v>756</v>
       </c>
       <c r="B758" t="n">
@@ -46308,7 +46296,7 @@
       </c>
     </row>
     <row r="759">
-      <c r="A759" s="1" t="n">
+      <c r="A759" t="n">
         <v>757</v>
       </c>
       <c r="B759" t="n">
@@ -46368,7 +46356,7 @@
       </c>
     </row>
     <row r="760">
-      <c r="A760" s="1" t="n">
+      <c r="A760" t="n">
         <v>758</v>
       </c>
       <c r="B760" t="n">
@@ -46428,7 +46416,7 @@
       </c>
     </row>
     <row r="761">
-      <c r="A761" s="1" t="n">
+      <c r="A761" t="n">
         <v>759</v>
       </c>
       <c r="B761" t="n">
@@ -46492,7 +46480,7 @@
       </c>
     </row>
     <row r="762">
-      <c r="A762" s="1" t="n">
+      <c r="A762" t="n">
         <v>760</v>
       </c>
       <c r="B762" t="n">
@@ -46550,7 +46538,7 @@
       </c>
     </row>
     <row r="763">
-      <c r="A763" s="1" t="n">
+      <c r="A763" t="n">
         <v>761</v>
       </c>
       <c r="B763" t="n">
@@ -46610,7 +46598,7 @@
       </c>
     </row>
     <row r="764">
-      <c r="A764" s="1" t="n">
+      <c r="A764" t="n">
         <v>762</v>
       </c>
       <c r="B764" t="n">
@@ -46670,7 +46658,7 @@
       </c>
     </row>
     <row r="765">
-      <c r="A765" s="1" t="n">
+      <c r="A765" t="n">
         <v>763</v>
       </c>
       <c r="B765" t="n">
@@ -46734,7 +46722,7 @@
       </c>
     </row>
     <row r="766">
-      <c r="A766" s="1" t="n">
+      <c r="A766" t="n">
         <v>764</v>
       </c>
       <c r="B766" t="n">
@@ -46794,7 +46782,7 @@
       </c>
     </row>
     <row r="767">
-      <c r="A767" s="1" t="n">
+      <c r="A767" t="n">
         <v>765</v>
       </c>
       <c r="B767" t="n">
@@ -46858,7 +46846,7 @@
       </c>
     </row>
     <row r="768">
-      <c r="A768" s="1" t="n">
+      <c r="A768" t="n">
         <v>766</v>
       </c>
       <c r="B768" t="n">
@@ -46916,7 +46904,7 @@
       </c>
     </row>
     <row r="769">
-      <c r="A769" s="1" t="n">
+      <c r="A769" t="n">
         <v>767</v>
       </c>
       <c r="B769" t="n">
@@ -46976,7 +46964,7 @@
       </c>
     </row>
     <row r="770">
-      <c r="A770" s="1" t="n">
+      <c r="A770" t="n">
         <v>768</v>
       </c>
       <c r="B770" t="n">
@@ -47034,7 +47022,7 @@
       </c>
     </row>
     <row r="771">
-      <c r="A771" s="1" t="n">
+      <c r="A771" t="n">
         <v>769</v>
       </c>
       <c r="B771" t="n">
@@ -47094,7 +47082,7 @@
       </c>
     </row>
     <row r="772">
-      <c r="A772" s="1" t="n">
+      <c r="A772" t="n">
         <v>770</v>
       </c>
       <c r="B772" t="n">
@@ -47154,7 +47142,7 @@
       </c>
     </row>
     <row r="773">
-      <c r="A773" s="1" t="n">
+      <c r="A773" t="n">
         <v>771</v>
       </c>
       <c r="B773" t="n">
@@ -47214,7 +47202,7 @@
       </c>
     </row>
     <row r="774">
-      <c r="A774" s="1" t="n">
+      <c r="A774" t="n">
         <v>772</v>
       </c>
       <c r="B774" t="n">
@@ -47278,7 +47266,7 @@
       </c>
     </row>
     <row r="775">
-      <c r="A775" s="1" t="n">
+      <c r="A775" t="n">
         <v>773</v>
       </c>
       <c r="B775" t="n">
@@ -47336,7 +47324,7 @@
       </c>
     </row>
     <row r="776">
-      <c r="A776" s="1" t="n">
+      <c r="A776" t="n">
         <v>774</v>
       </c>
       <c r="B776" t="n">
@@ -47396,7 +47384,7 @@
       </c>
     </row>
     <row r="777">
-      <c r="A777" s="1" t="n">
+      <c r="A777" t="n">
         <v>775</v>
       </c>
       <c r="B777" t="n">
@@ -47456,7 +47444,7 @@
       </c>
     </row>
     <row r="778">
-      <c r="A778" s="1" t="n">
+      <c r="A778" t="n">
         <v>776</v>
       </c>
       <c r="B778" t="n">
@@ -47518,7 +47506,7 @@
       </c>
     </row>
     <row r="779">
-      <c r="A779" s="1" t="n">
+      <c r="A779" t="n">
         <v>777</v>
       </c>
       <c r="B779" t="n">
@@ -47578,7 +47566,7 @@
       </c>
     </row>
     <row r="780">
-      <c r="A780" s="1" t="n">
+      <c r="A780" t="n">
         <v>778</v>
       </c>
       <c r="B780" t="n">
@@ -47636,7 +47624,7 @@
       </c>
     </row>
     <row r="781">
-      <c r="A781" s="1" t="n">
+      <c r="A781" t="n">
         <v>779</v>
       </c>
       <c r="B781" t="n">
@@ -47700,7 +47688,7 @@
       </c>
     </row>
     <row r="782">
-      <c r="A782" s="1" t="n">
+      <c r="A782" t="n">
         <v>780</v>
       </c>
       <c r="B782" t="n">
@@ -47760,7 +47748,7 @@
       </c>
     </row>
     <row r="783">
-      <c r="A783" s="1" t="n">
+      <c r="A783" t="n">
         <v>781</v>
       </c>
       <c r="B783" t="n">
@@ -47824,7 +47812,7 @@
       </c>
     </row>
     <row r="784">
-      <c r="A784" s="1" t="n">
+      <c r="A784" t="n">
         <v>782</v>
       </c>
       <c r="B784" t="n">
@@ -47888,7 +47876,7 @@
       </c>
     </row>
     <row r="785">
-      <c r="A785" s="1" t="n">
+      <c r="A785" t="n">
         <v>783</v>
       </c>
       <c r="B785" t="n">
@@ -47946,7 +47934,7 @@
       </c>
     </row>
     <row r="786">
-      <c r="A786" s="1" t="n">
+      <c r="A786" t="n">
         <v>784</v>
       </c>
       <c r="B786" t="n">
@@ -48006,7 +47994,7 @@
       </c>
     </row>
     <row r="787">
-      <c r="A787" s="1" t="n">
+      <c r="A787" t="n">
         <v>785</v>
       </c>
       <c r="B787" t="n">
@@ -48066,7 +48054,7 @@
       </c>
     </row>
     <row r="788">
-      <c r="A788" s="1" t="n">
+      <c r="A788" t="n">
         <v>786</v>
       </c>
       <c r="B788" t="n">
@@ -48126,7 +48114,7 @@
       </c>
     </row>
     <row r="789">
-      <c r="A789" s="1" t="n">
+      <c r="A789" t="n">
         <v>787</v>
       </c>
       <c r="B789" t="n">
@@ -48186,7 +48174,7 @@
       </c>
     </row>
     <row r="790">
-      <c r="A790" s="1" t="n">
+      <c r="A790" t="n">
         <v>788</v>
       </c>
       <c r="B790" t="n">
@@ -48246,7 +48234,7 @@
       </c>
     </row>
     <row r="791">
-      <c r="A791" s="1" t="n">
+      <c r="A791" t="n">
         <v>789</v>
       </c>
       <c r="B791" t="n">
@@ -48310,7 +48298,7 @@
       </c>
     </row>
     <row r="792">
-      <c r="A792" s="1" t="n">
+      <c r="A792" t="n">
         <v>790</v>
       </c>
       <c r="B792" t="n">
@@ -48368,7 +48356,7 @@
       </c>
     </row>
     <row r="793">
-      <c r="A793" s="1" t="n">
+      <c r="A793" t="n">
         <v>791</v>
       </c>
       <c r="B793" t="n">
@@ -48428,7 +48416,7 @@
       </c>
     </row>
     <row r="794">
-      <c r="A794" s="1" t="n">
+      <c r="A794" t="n">
         <v>792</v>
       </c>
       <c r="B794" t="n">
@@ -48486,7 +48474,7 @@
       </c>
     </row>
     <row r="795">
-      <c r="A795" s="1" t="n">
+      <c r="A795" t="n">
         <v>793</v>
       </c>
       <c r="B795" t="n">
@@ -48544,7 +48532,7 @@
       </c>
     </row>
     <row r="796">
-      <c r="A796" s="1" t="n">
+      <c r="A796" t="n">
         <v>794</v>
       </c>
       <c r="B796" t="n">
@@ -48604,7 +48592,7 @@
       </c>
     </row>
     <row r="797">
-      <c r="A797" s="1" t="n">
+      <c r="A797" t="n">
         <v>795</v>
       </c>
       <c r="B797" t="n">
@@ -48664,7 +48652,7 @@
       </c>
     </row>
     <row r="798">
-      <c r="A798" s="1" t="n">
+      <c r="A798" t="n">
         <v>796</v>
       </c>
       <c r="B798" t="n">
@@ -48728,7 +48716,7 @@
       </c>
     </row>
     <row r="799">
-      <c r="A799" s="1" t="n">
+      <c r="A799" t="n">
         <v>797</v>
       </c>
       <c r="B799" t="n">
@@ -48788,7 +48776,7 @@
       </c>
     </row>
     <row r="800">
-      <c r="A800" s="1" t="n">
+      <c r="A800" t="n">
         <v>798</v>
       </c>
       <c r="B800" t="n">
@@ -48848,7 +48836,7 @@
       </c>
     </row>
     <row r="801">
-      <c r="A801" s="1" t="n">
+      <c r="A801" t="n">
         <v>799</v>
       </c>
       <c r="B801" t="n">
@@ -48908,7 +48896,7 @@
       </c>
     </row>
     <row r="802">
-      <c r="A802" s="1" t="n">
+      <c r="A802" t="n">
         <v>800</v>
       </c>
       <c r="B802" t="n">
@@ -48968,7 +48956,7 @@
       </c>
     </row>
     <row r="803">
-      <c r="A803" s="1" t="n">
+      <c r="A803" t="n">
         <v>801</v>
       </c>
       <c r="B803" t="n">
@@ -49028,7 +49016,7 @@
       </c>
     </row>
     <row r="804">
-      <c r="A804" s="1" t="n">
+      <c r="A804" t="n">
         <v>802</v>
       </c>
       <c r="B804" t="n">
@@ -49092,7 +49080,7 @@
       </c>
     </row>
     <row r="805">
-      <c r="A805" s="1" t="n">
+      <c r="A805" t="n">
         <v>803</v>
       </c>
       <c r="B805" t="n">
@@ -49152,7 +49140,7 @@
       </c>
     </row>
     <row r="806">
-      <c r="A806" s="1" t="n">
+      <c r="A806" t="n">
         <v>804</v>
       </c>
       <c r="B806" t="n">
@@ -49212,7 +49200,7 @@
       </c>
     </row>
     <row r="807">
-      <c r="A807" s="1" t="n">
+      <c r="A807" t="n">
         <v>805</v>
       </c>
       <c r="B807" t="n">
@@ -49272,7 +49260,7 @@
       </c>
     </row>
     <row r="808">
-      <c r="A808" s="1" t="n">
+      <c r="A808" t="n">
         <v>806</v>
       </c>
       <c r="B808" t="n">
@@ -49336,7 +49324,7 @@
       </c>
     </row>
     <row r="809">
-      <c r="A809" s="1" t="n">
+      <c r="A809" t="n">
         <v>807</v>
       </c>
       <c r="B809" t="n">
@@ -49396,7 +49384,7 @@
       </c>
     </row>
     <row r="810">
-      <c r="A810" s="1" t="n">
+      <c r="A810" t="n">
         <v>808</v>
       </c>
       <c r="B810" t="n">
@@ -49456,7 +49444,7 @@
       </c>
     </row>
     <row r="811">
-      <c r="A811" s="1" t="n">
+      <c r="A811" t="n">
         <v>809</v>
       </c>
       <c r="B811" t="n">
@@ -49520,7 +49508,7 @@
       </c>
     </row>
     <row r="812">
-      <c r="A812" s="1" t="n">
+      <c r="A812" t="n">
         <v>810</v>
       </c>
       <c r="B812" t="n">
@@ -49580,7 +49568,7 @@
       </c>
     </row>
     <row r="813">
-      <c r="A813" s="1" t="n">
+      <c r="A813" t="n">
         <v>811</v>
       </c>
       <c r="B813" t="n">
@@ -49640,7 +49628,7 @@
       </c>
     </row>
     <row r="814">
-      <c r="A814" s="1" t="n">
+      <c r="A814" t="n">
         <v>812</v>
       </c>
       <c r="B814" t="n">
@@ -49700,7 +49688,7 @@
       </c>
     </row>
     <row r="815">
-      <c r="A815" s="1" t="n">
+      <c r="A815" t="n">
         <v>813</v>
       </c>
       <c r="B815" t="n">
@@ -49760,7 +49748,7 @@
       </c>
     </row>
     <row r="816">
-      <c r="A816" s="1" t="n">
+      <c r="A816" t="n">
         <v>814</v>
       </c>
       <c r="B816" t="n">
@@ -49820,7 +49808,7 @@
       </c>
     </row>
     <row r="817">
-      <c r="A817" s="1" t="n">
+      <c r="A817" t="n">
         <v>815</v>
       </c>
       <c r="B817" t="n">
@@ -49882,7 +49870,7 @@
       </c>
     </row>
     <row r="818">
-      <c r="A818" s="1" t="n">
+      <c r="A818" t="n">
         <v>816</v>
       </c>
       <c r="B818" t="n">
@@ -49942,7 +49930,7 @@
       </c>
     </row>
     <row r="819">
-      <c r="A819" s="1" t="n">
+      <c r="A819" t="n">
         <v>817</v>
       </c>
       <c r="B819" t="n">
@@ -50002,7 +49990,7 @@
       </c>
     </row>
     <row r="820">
-      <c r="A820" s="1" t="n">
+      <c r="A820" t="n">
         <v>818</v>
       </c>
       <c r="B820" t="n">
@@ -50062,7 +50050,7 @@
       </c>
     </row>
     <row r="821">
-      <c r="A821" s="1" t="n">
+      <c r="A821" t="n">
         <v>819</v>
       </c>
       <c r="B821" t="n">
@@ -50122,7 +50110,7 @@
       </c>
     </row>
     <row r="822">
-      <c r="A822" s="1" t="n">
+      <c r="A822" t="n">
         <v>820</v>
       </c>
       <c r="B822" t="n">
@@ -50186,7 +50174,7 @@
       </c>
     </row>
     <row r="823">
-      <c r="A823" s="1" t="n">
+      <c r="A823" t="n">
         <v>821</v>
       </c>
       <c r="B823" t="n">
@@ -50246,7 +50234,7 @@
       </c>
     </row>
     <row r="824">
-      <c r="A824" s="1" t="n">
+      <c r="A824" t="n">
         <v>822</v>
       </c>
       <c r="B824" t="n">
@@ -50306,7 +50294,7 @@
       </c>
     </row>
     <row r="825">
-      <c r="A825" s="1" t="n">
+      <c r="A825" t="n">
         <v>823</v>
       </c>
       <c r="B825" t="n">
@@ -50370,7 +50358,7 @@
       </c>
     </row>
     <row r="826">
-      <c r="A826" s="1" t="n">
+      <c r="A826" t="n">
         <v>824</v>
       </c>
       <c r="B826" t="n">
@@ -50430,7 +50418,7 @@
       </c>
     </row>
     <row r="827">
-      <c r="A827" s="1" t="n">
+      <c r="A827" t="n">
         <v>825</v>
       </c>
       <c r="B827" t="n">
@@ -50488,7 +50476,7 @@
       </c>
     </row>
     <row r="828">
-      <c r="A828" s="1" t="n">
+      <c r="A828" t="n">
         <v>826</v>
       </c>
       <c r="B828" t="n">
@@ -50546,7 +50534,7 @@
       </c>
     </row>
     <row r="829">
-      <c r="A829" s="1" t="n">
+      <c r="A829" t="n">
         <v>827</v>
       </c>
       <c r="B829" t="n">
@@ -50606,7 +50594,7 @@
       </c>
     </row>
     <row r="830">
-      <c r="A830" s="1" t="n">
+      <c r="A830" t="n">
         <v>828</v>
       </c>
       <c r="B830" t="n">
@@ -50664,7 +50652,7 @@
       </c>
     </row>
     <row r="831">
-      <c r="A831" s="1" t="n">
+      <c r="A831" t="n">
         <v>829</v>
       </c>
       <c r="B831" t="n">
@@ -50720,7 +50708,7 @@
       </c>
     </row>
     <row r="832">
-      <c r="A832" s="1" t="n">
+      <c r="A832" t="n">
         <v>830</v>
       </c>
       <c r="B832" t="n">
@@ -50780,7 +50768,7 @@
       </c>
     </row>
     <row r="833">
-      <c r="A833" s="1" t="n">
+      <c r="A833" t="n">
         <v>831</v>
       </c>
       <c r="B833" t="n">
@@ -50840,7 +50828,7 @@
       </c>
     </row>
     <row r="834">
-      <c r="A834" s="1" t="n">
+      <c r="A834" t="n">
         <v>832</v>
       </c>
       <c r="B834" t="n">
@@ -50898,7 +50886,7 @@
       </c>
     </row>
     <row r="835">
-      <c r="A835" s="1" t="n">
+      <c r="A835" t="n">
         <v>833</v>
       </c>
       <c r="B835" t="n">
@@ -50958,7 +50946,7 @@
       </c>
     </row>
     <row r="836">
-      <c r="A836" s="1" t="n">
+      <c r="A836" t="n">
         <v>834</v>
       </c>
       <c r="B836" t="n">
@@ -51018,7 +51006,7 @@
       </c>
     </row>
     <row r="837">
-      <c r="A837" s="1" t="n">
+      <c r="A837" t="n">
         <v>835</v>
       </c>
       <c r="B837" t="n">
@@ -51082,7 +51070,7 @@
       </c>
     </row>
     <row r="838">
-      <c r="A838" s="1" t="n">
+      <c r="A838" t="n">
         <v>836</v>
       </c>
       <c r="B838" t="n">
@@ -51142,7 +51130,7 @@
       </c>
     </row>
     <row r="839">
-      <c r="A839" s="1" t="n">
+      <c r="A839" t="n">
         <v>837</v>
       </c>
       <c r="B839" t="n">
@@ -51200,7 +51188,7 @@
       </c>
     </row>
     <row r="840">
-      <c r="A840" s="1" t="n">
+      <c r="A840" t="n">
         <v>838</v>
       </c>
       <c r="B840" t="n">
@@ -51260,7 +51248,7 @@
       </c>
     </row>
     <row r="841">
-      <c r="A841" s="1" t="n">
+      <c r="A841" t="n">
         <v>839</v>
       </c>
       <c r="B841" t="n">
@@ -51322,7 +51310,7 @@
       </c>
     </row>
     <row r="842">
-      <c r="A842" s="1" t="n">
+      <c r="A842" t="n">
         <v>840</v>
       </c>
       <c r="B842" t="n">
@@ -51382,7 +51370,7 @@
       </c>
     </row>
     <row r="843">
-      <c r="A843" s="1" t="n">
+      <c r="A843" t="n">
         <v>841</v>
       </c>
       <c r="B843" t="n">
@@ -51442,7 +51430,7 @@
       </c>
     </row>
     <row r="844">
-      <c r="A844" s="1" t="n">
+      <c r="A844" t="n">
         <v>842</v>
       </c>
       <c r="B844" t="n">
@@ -51502,7 +51490,7 @@
       </c>
     </row>
     <row r="845">
-      <c r="A845" s="1" t="n">
+      <c r="A845" t="n">
         <v>843</v>
       </c>
       <c r="B845" t="n">
@@ -51562,7 +51550,7 @@
       </c>
     </row>
     <row r="846">
-      <c r="A846" s="1" t="n">
+      <c r="A846" t="n">
         <v>844</v>
       </c>
       <c r="B846" t="n">
@@ -51622,7 +51610,7 @@
       </c>
     </row>
     <row r="847">
-      <c r="A847" s="1" t="n">
+      <c r="A847" t="n">
         <v>845</v>
       </c>
       <c r="B847" t="n">
@@ -51682,7 +51670,7 @@
       </c>
     </row>
     <row r="848">
-      <c r="A848" s="1" t="n">
+      <c r="A848" t="n">
         <v>846</v>
       </c>
       <c r="B848" t="n">
@@ -51740,7 +51728,7 @@
       </c>
     </row>
     <row r="849">
-      <c r="A849" s="1" t="n">
+      <c r="A849" t="n">
         <v>847</v>
       </c>
       <c r="B849" t="n">
@@ -51800,7 +51788,7 @@
       </c>
     </row>
     <row r="850">
-      <c r="A850" s="1" t="n">
+      <c r="A850" t="n">
         <v>848</v>
       </c>
       <c r="B850" t="n">
@@ -51860,7 +51848,7 @@
       </c>
     </row>
     <row r="851">
-      <c r="A851" s="1" t="n">
+      <c r="A851" t="n">
         <v>849</v>
       </c>
       <c r="B851" t="n">
@@ -51922,7 +51910,7 @@
       </c>
     </row>
     <row r="852">
-      <c r="A852" s="1" t="n">
+      <c r="A852" t="n">
         <v>850</v>
       </c>
       <c r="B852" t="n">
@@ -51982,7 +51970,7 @@
       </c>
     </row>
     <row r="853">
-      <c r="A853" s="1" t="n">
+      <c r="A853" t="n">
         <v>851</v>
       </c>
       <c r="B853" t="n">
@@ -52042,7 +52030,7 @@
       </c>
     </row>
     <row r="854">
-      <c r="A854" s="1" t="n">
+      <c r="A854" t="n">
         <v>852</v>
       </c>
       <c r="B854" t="n">
@@ -52102,7 +52090,7 @@
       </c>
     </row>
     <row r="855">
-      <c r="A855" s="1" t="n">
+      <c r="A855" t="n">
         <v>853</v>
       </c>
       <c r="B855" t="n">
@@ -52166,7 +52154,7 @@
       </c>
     </row>
     <row r="856">
-      <c r="A856" s="1" t="n">
+      <c r="A856" t="n">
         <v>854</v>
       </c>
       <c r="B856" t="n">
@@ -52226,7 +52214,7 @@
       </c>
     </row>
     <row r="857">
-      <c r="A857" s="1" t="n">
+      <c r="A857" t="n">
         <v>855</v>
       </c>
       <c r="B857" t="n">
@@ -52286,7 +52274,7 @@
       </c>
     </row>
     <row r="858">
-      <c r="A858" s="1" t="n">
+      <c r="A858" t="n">
         <v>856</v>
       </c>
       <c r="B858" t="n">
@@ -52346,7 +52334,7 @@
       </c>
     </row>
     <row r="859">
-      <c r="A859" s="1" t="n">
+      <c r="A859" t="n">
         <v>857</v>
       </c>
       <c r="B859" t="n">
@@ -52410,7 +52398,7 @@
       </c>
     </row>
     <row r="860">
-      <c r="A860" s="1" t="n">
+      <c r="A860" t="n">
         <v>858</v>
       </c>
       <c r="B860" t="n">
@@ -52470,7 +52458,7 @@
       </c>
     </row>
     <row r="861">
-      <c r="A861" s="1" t="n">
+      <c r="A861" t="n">
         <v>859</v>
       </c>
       <c r="B861" t="n">
@@ -52528,7 +52516,7 @@
       </c>
     </row>
     <row r="862">
-      <c r="A862" s="1" t="n">
+      <c r="A862" t="n">
         <v>860</v>
       </c>
       <c r="B862" t="n">
@@ -52588,7 +52576,7 @@
       </c>
     </row>
     <row r="863">
-      <c r="A863" s="1" t="n">
+      <c r="A863" t="n">
         <v>861</v>
       </c>
       <c r="B863" t="n">
@@ -52648,7 +52636,7 @@
       </c>
     </row>
     <row r="864">
-      <c r="A864" s="1" t="n">
+      <c r="A864" t="n">
         <v>862</v>
       </c>
       <c r="B864" t="n">
@@ -52712,7 +52700,7 @@
       </c>
     </row>
     <row r="865">
-      <c r="A865" s="1" t="n">
+      <c r="A865" t="n">
         <v>863</v>
       </c>
       <c r="B865" t="n">
@@ -52770,7 +52758,7 @@
       </c>
     </row>
     <row r="866">
-      <c r="A866" s="1" t="n">
+      <c r="A866" t="n">
         <v>864</v>
       </c>
       <c r="B866" t="n">
@@ -52830,7 +52818,7 @@
       </c>
     </row>
     <row r="867">
-      <c r="A867" s="1" t="n">
+      <c r="A867" t="n">
         <v>865</v>
       </c>
       <c r="B867" t="n">
@@ -52890,7 +52878,7 @@
       </c>
     </row>
     <row r="868">
-      <c r="A868" s="1" t="n">
+      <c r="A868" t="n">
         <v>866</v>
       </c>
       <c r="B868" t="n">
@@ -52950,7 +52938,7 @@
       </c>
     </row>
     <row r="869">
-      <c r="A869" s="1" t="n">
+      <c r="A869" t="n">
         <v>867</v>
       </c>
       <c r="B869" t="n">
@@ -53014,7 +53002,7 @@
       </c>
     </row>
     <row r="870">
-      <c r="A870" s="1" t="n">
+      <c r="A870" t="n">
         <v>868</v>
       </c>
       <c r="B870" t="n">
@@ -53072,7 +53060,7 @@
       </c>
     </row>
     <row r="871">
-      <c r="A871" s="1" t="n">
+      <c r="A871" t="n">
         <v>869</v>
       </c>
       <c r="B871" t="n">
@@ -53132,7 +53120,7 @@
       </c>
     </row>
     <row r="872">
-      <c r="A872" s="1" t="n">
+      <c r="A872" t="n">
         <v>870</v>
       </c>
       <c r="B872" t="n">
@@ -53192,7 +53180,7 @@
       </c>
     </row>
     <row r="873">
-      <c r="A873" s="1" t="n">
+      <c r="A873" t="n">
         <v>871</v>
       </c>
       <c r="B873" t="n">
@@ -53256,7 +53244,7 @@
       </c>
     </row>
     <row r="874">
-      <c r="A874" s="1" t="n">
+      <c r="A874" t="n">
         <v>872</v>
       </c>
       <c r="B874" t="n">
@@ -53320,7 +53308,7 @@
       </c>
     </row>
     <row r="875">
-      <c r="A875" s="1" t="n">
+      <c r="A875" t="n">
         <v>873</v>
       </c>
       <c r="B875" t="n">
@@ -53380,7 +53368,7 @@
       </c>
     </row>
     <row r="876">
-      <c r="A876" s="1" t="n">
+      <c r="A876" t="n">
         <v>874</v>
       </c>
       <c r="B876" t="n">
@@ -53440,7 +53428,7 @@
       </c>
     </row>
     <row r="877">
-      <c r="A877" s="1" t="n">
+      <c r="A877" t="n">
         <v>875</v>
       </c>
       <c r="B877" t="n">
@@ -53500,7 +53488,7 @@
       </c>
     </row>
     <row r="878">
-      <c r="A878" s="1" t="n">
+      <c r="A878" t="n">
         <v>876</v>
       </c>
       <c r="B878" t="n">
@@ -53560,7 +53548,7 @@
       </c>
     </row>
     <row r="879">
-      <c r="A879" s="1" t="n">
+      <c r="A879" t="n">
         <v>877</v>
       </c>
       <c r="B879" t="n">
@@ -53620,7 +53608,7 @@
       </c>
     </row>
     <row r="880">
-      <c r="A880" s="1" t="n">
+      <c r="A880" t="n">
         <v>878</v>
       </c>
       <c r="B880" t="n">
@@ -53678,7 +53666,7 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" s="1" t="n">
+      <c r="A881" t="n">
         <v>879</v>
       </c>
       <c r="B881" t="n">
@@ -53742,7 +53730,7 @@
       </c>
     </row>
     <row r="882">
-      <c r="A882" s="1" t="n">
+      <c r="A882" t="n">
         <v>880</v>
       </c>
       <c r="B882" t="n">
@@ -53802,7 +53790,7 @@
       </c>
     </row>
     <row r="883">
-      <c r="A883" s="1" t="n">
+      <c r="A883" t="n">
         <v>881</v>
       </c>
       <c r="B883" t="n">
@@ -53862,7 +53850,7 @@
       </c>
     </row>
     <row r="884">
-      <c r="A884" s="1" t="n">
+      <c r="A884" t="n">
         <v>882</v>
       </c>
       <c r="B884" t="n">
@@ -53922,7 +53910,7 @@
       </c>
     </row>
     <row r="885">
-      <c r="A885" s="1" t="n">
+      <c r="A885" t="n">
         <v>883</v>
       </c>
       <c r="B885" t="n">
@@ -53982,7 +53970,7 @@
       </c>
     </row>
     <row r="886">
-      <c r="A886" s="1" t="n">
+      <c r="A886" t="n">
         <v>884</v>
       </c>
       <c r="B886" t="n">
@@ -54042,7 +54030,7 @@
       </c>
     </row>
     <row r="887">
-      <c r="A887" s="1" t="n">
+      <c r="A887" t="n">
         <v>885</v>
       </c>
       <c r="B887" t="n">
@@ -54102,7 +54090,7 @@
       </c>
     </row>
     <row r="888">
-      <c r="A888" s="1" t="n">
+      <c r="A888" t="n">
         <v>886</v>
       </c>
       <c r="B888" t="n">
@@ -54162,7 +54150,7 @@
       </c>
     </row>
     <row r="889">
-      <c r="A889" s="1" t="n">
+      <c r="A889" t="n">
         <v>887</v>
       </c>
       <c r="B889" t="n">
@@ -54226,7 +54214,7 @@
       </c>
     </row>
     <row r="890">
-      <c r="A890" s="1" t="n">
+      <c r="A890" t="n">
         <v>888</v>
       </c>
       <c r="B890" t="n">
@@ -54284,7 +54272,7 @@
       </c>
     </row>
     <row r="891">
-      <c r="A891" s="1" t="n">
+      <c r="A891" t="n">
         <v>889</v>
       </c>
       <c r="B891" t="n">
@@ -54348,7 +54336,7 @@
       </c>
     </row>
     <row r="892">
-      <c r="A892" s="1" t="n">
+      <c r="A892" t="n">
         <v>890</v>
       </c>
       <c r="B892" t="n">
